--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="74">
   <si>
     <t>variable_id</t>
   </si>
@@ -55,46 +55,106 @@
     <t>CORDEX</t>
   </si>
   <si>
-    <t>DD</t>
-  </si>
-  <si>
-    <t>EUR-12</t>
-  </si>
-  <si>
-    <t>CLMcom-Hereon</t>
+    <t>output</t>
+  </si>
+  <si>
+    <t>EUR-11</t>
+  </si>
+  <si>
+    <t>CLMcom</t>
+  </si>
+  <si>
+    <t>CLMcom-ETH</t>
+  </si>
+  <si>
+    <t>CNRM</t>
+  </si>
+  <si>
+    <t>DHMZ</t>
+  </si>
+  <si>
+    <t>DMI</t>
   </si>
   <si>
     <t>GERICS</t>
   </si>
   <si>
-    <t>HCLIMcom-SMHI</t>
+    <t>ICTP</t>
+  </si>
+  <si>
+    <t>IPSL</t>
   </si>
   <si>
     <t>KNMI</t>
   </si>
   <si>
-    <t>ERA5</t>
+    <t>MOHC</t>
+  </si>
+  <si>
+    <t>MPI-CSC</t>
+  </si>
+  <si>
+    <t>RMIB-UGent</t>
+  </si>
+  <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>ECMWF-ERAINT</t>
   </si>
   <si>
     <t>evaluation</t>
   </si>
   <si>
-    <t>r1i1p1f1</t>
-  </si>
-  <si>
-    <t>ICON-CLM-202407-1-1</t>
-  </si>
-  <si>
-    <t>REMO2020</t>
-  </si>
-  <si>
-    <t>HCLIM43-ALADIN</t>
-  </si>
-  <si>
-    <t>RACMO23E</t>
-  </si>
-  <si>
-    <t>v1-r1</t>
+    <t>r0i0p0</t>
+  </si>
+  <si>
+    <t>r1i1p1</t>
+  </si>
+  <si>
+    <t>CCLM4-8-17</t>
+  </si>
+  <si>
+    <t>COSMO-crCLIM-v1-1</t>
+  </si>
+  <si>
+    <t>ALADIN53</t>
+  </si>
+  <si>
+    <t>ALADIN63</t>
+  </si>
+  <si>
+    <t>RegCM4-2</t>
+  </si>
+  <si>
+    <t>HIRHAM5</t>
+  </si>
+  <si>
+    <t>REMO2015</t>
+  </si>
+  <si>
+    <t>RegCM4-6</t>
+  </si>
+  <si>
+    <t>WRF381P</t>
+  </si>
+  <si>
+    <t>RACMO22E</t>
+  </si>
+  <si>
+    <t>HadREM3-GA7-05</t>
+  </si>
+  <si>
+    <t>REMO2009</t>
+  </si>
+  <si>
+    <t>ALARO-0</t>
+  </si>
+  <si>
+    <t>RCA4</t>
+  </si>
+  <si>
+    <t>v1</t>
   </si>
   <si>
     <t>fx</t>
@@ -103,40 +163,61 @@
     <t>mon</t>
   </si>
   <si>
-    <t>1hr</t>
-  </si>
-  <si>
     <t>day</t>
   </si>
   <si>
-    <t>v20240920</t>
-  </si>
-  <si>
-    <t>v20241120</t>
-  </si>
-  <si>
-    <t>v20241205</t>
-  </si>
-  <si>
-    <t>v20241216</t>
-  </si>
-  <si>
-    <t>['areacella', 'sftlaf', 'mrsofc', 'rootd', 'sftlf', 'sftgif', 'orog', 'sfturf']</t>
-  </si>
-  <si>
-    <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
-  </si>
-  <si>
-    <t>['hurs', 'pr', 'prw', 'tas']</t>
-  </si>
-  <si>
-    <t>['pr', 'sfcWindmax', 'snc', 'snd', 'snw', 'tasmax']</t>
-  </si>
-  <si>
-    <t>['areacella', 'orog', 'sftlf', 'sftlaf']</t>
-  </si>
-  <si>
-    <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr']</t>
+    <t>v20140515</t>
+  </si>
+  <si>
+    <t>v20191210</t>
+  </si>
+  <si>
+    <t>v20150127</t>
+  </si>
+  <si>
+    <t>v20191118</t>
+  </si>
+  <si>
+    <t>v20160112</t>
+  </si>
+  <si>
+    <t>v20150527</t>
+  </si>
+  <si>
+    <t>v20140620</t>
+  </si>
+  <si>
+    <t>v20180813</t>
+  </si>
+  <si>
+    <t>v20190502</t>
+  </si>
+  <si>
+    <t>v20190919</t>
+  </si>
+  <si>
+    <t>v20140218</t>
+  </si>
+  <si>
+    <t>v20140319</t>
+  </si>
+  <si>
+    <t>v20200706</t>
+  </si>
+  <si>
+    <t>v20200330</t>
+  </si>
+  <si>
+    <t>v20160525</t>
+  </si>
+  <si>
+    <t>v20170523</t>
+  </si>
+  <si>
+    <t>v20170207</t>
+  </si>
+  <si>
+    <t>v20131026</t>
   </si>
   <si>
     <t>['orog', 'sftlf']</t>
@@ -145,7 +226,16 @@
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
-    <t>['areacella', 'orog', 'sftlf']</t>
+    <t>['pr', 'tas', 'tasmax', 'tasmin']</t>
+  </si>
+  <si>
+    <t>['pr', 'psl']</t>
+  </si>
+  <si>
+    <t>['tas', 'tasmax', 'tasmin']</t>
+  </si>
+  <si>
+    <t>['pr', 'tas']</t>
   </si>
 </sst>
 </file>
@@ -503,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -512,9 +602,10 @@
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="7" width="23.7109375" customWidth="1"/>
-    <col min="8" max="9" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="11" width="11.7109375" customWidth="1"/>
-    <col min="12" max="12" width="112.7109375" customWidth="1"/>
+    <col min="12" max="12" width="42.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -569,28 +660,28 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -600,17 +691,23 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="J3" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -621,28 +718,28 @@
         <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -652,37 +749,55 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="J5" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L5" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="J6" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -696,45 +811,37 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -748,13 +855,13 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -765,28 +872,28 @@
         <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="L10" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -800,44 +907,564 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="I22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="C2:C11"/>
+  <mergeCells count="63">
+    <mergeCell ref="A2:A29"/>
+    <mergeCell ref="B2:B29"/>
+    <mergeCell ref="C2:C29"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D6:D9"/>
     <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E9"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E28:E29"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F9"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G6:G9"/>
     <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J20:J21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="100">
   <si>
     <t>variable_id</t>
   </si>
@@ -22,6 +22,9 @@
     <t>project_id</t>
   </si>
   <si>
+    <t>mip_era</t>
+  </si>
+  <si>
     <t>activity_id</t>
   </si>
   <si>
@@ -55,12 +58,24 @@
     <t>CORDEX</t>
   </si>
   <si>
+    <t>CMIP5</t>
+  </si>
+  <si>
+    <t>CMIP6</t>
+  </si>
+  <si>
     <t>output</t>
   </si>
   <si>
+    <t>DD</t>
+  </si>
+  <si>
     <t>EUR-11</t>
   </si>
   <si>
+    <t>EUR-12</t>
+  </si>
+  <si>
     <t>CLMcom</t>
   </si>
   <si>
@@ -100,9 +115,18 @@
     <t>SMHI</t>
   </si>
   <si>
+    <t>CLMcom-Hereon</t>
+  </si>
+  <si>
+    <t>HCLIMcom-SMHI</t>
+  </si>
+  <si>
     <t>ECMWF-ERAINT</t>
   </si>
   <si>
+    <t>ERA5</t>
+  </si>
+  <si>
     <t>evaluation</t>
   </si>
   <si>
@@ -112,6 +136,9 @@
     <t>r1i1p1</t>
   </si>
   <si>
+    <t>r1i1p1f1</t>
+  </si>
+  <si>
     <t>CCLM4-8-17</t>
   </si>
   <si>
@@ -154,9 +181,24 @@
     <t>RCA4</t>
   </si>
   <si>
+    <t>ICON-CLM-202407-1-1</t>
+  </si>
+  <si>
+    <t>REMO2020</t>
+  </si>
+  <si>
+    <t>HCLIM43-ALADIN</t>
+  </si>
+  <si>
+    <t>RACMO23E</t>
+  </si>
+  <si>
     <t>v1</t>
   </si>
   <si>
+    <t>v1-r1</t>
+  </si>
+  <si>
     <t>fx</t>
   </si>
   <si>
@@ -166,6 +208,9 @@
     <t>day</t>
   </si>
   <si>
+    <t>1hr</t>
+  </si>
+  <si>
     <t>v20140515</t>
   </si>
   <si>
@@ -220,6 +265,18 @@
     <t>v20131026</t>
   </si>
   <si>
+    <t>v20240920</t>
+  </si>
+  <si>
+    <t>v20241120</t>
+  </si>
+  <si>
+    <t>v20241205</t>
+  </si>
+  <si>
+    <t>v20241216</t>
+  </si>
+  <si>
     <t>['orog', 'sftlf']</t>
   </si>
   <si>
@@ -236,6 +293,27 @@
   </si>
   <si>
     <t>['pr', 'tas']</t>
+  </si>
+  <si>
+    <t>['areacella', 'sftlaf', 'mrsofc', 'rootd', 'sftlf', 'sftgif', 'orog', 'sfturf']</t>
+  </si>
+  <si>
+    <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['hurs', 'pr', 'prw', 'tas']</t>
+  </si>
+  <si>
+    <t>['pr', 'sfcWindmax', 'snc', 'snd', 'snw', 'tasmax']</t>
+  </si>
+  <si>
+    <t>['areacella', 'orog', 'sftlf', 'sftlaf']</t>
+  </si>
+  <si>
+    <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr']</t>
+  </si>
+  <si>
+    <t>['areacella', 'orog', 'sftlf']</t>
   </si>
 </sst>
 </file>
@@ -593,22 +671,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="7" width="23.7109375" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="11" width="11.7109375" customWidth="1"/>
-    <col min="12" max="12" width="42.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="10" width="21.7109375" customWidth="1"/>
+    <col min="11" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="112.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -643,164 +721,174 @@
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -810,17 +898,18 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -828,23 +917,24 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -854,49 +944,51 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -906,49 +998,51 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -958,107 +1052,111 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1068,81 +1166,84 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>63</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1152,17 +1253,18 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1173,46 +1275,48 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1222,107 +1326,111 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1332,91 +1440,350 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>62</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>61</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L29" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M36" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M39" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="A2:A29"/>
+  <mergeCells count="91">
+    <mergeCell ref="A2:A39"/>
     <mergeCell ref="B2:B29"/>
+    <mergeCell ref="B30:B39"/>
     <mergeCell ref="C2:C29"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="C30:C39"/>
+    <mergeCell ref="D2:D29"/>
+    <mergeCell ref="D30:D39"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -1429,6 +1796,10 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E38:E39"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -1441,21 +1812,37 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="G19:G21"/>
     <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G24:G25"/>
     <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="H19:H21"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H38:H39"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -1464,7 +1851,23 @@
     <mergeCell ref="I19:I21"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I32:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K20:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="106">
   <si>
     <t>variable_id</t>
   </si>
@@ -118,6 +118,9 @@
     <t>CLMcom-Hereon</t>
   </si>
   <si>
+    <t>CNRM-MF</t>
+  </si>
+  <si>
     <t>HCLIMcom-SMHI</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
     <t>ICON-CLM-202407-1-1</t>
   </si>
   <si>
+    <t>CNRM-ALADIN64E1</t>
+  </si>
+  <si>
     <t>REMO2020</t>
   </si>
   <si>
@@ -268,6 +274,9 @@
     <t>v20240920</t>
   </si>
   <si>
+    <t>v20250116</t>
+  </si>
+  <si>
     <t>v20241120</t>
   </si>
   <si>
@@ -286,6 +295,9 @@
     <t>['pr', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
+    <t>['pr', 'psl', 'tasmax', 'tasmin']</t>
+  </si>
+  <si>
     <t>['pr', 'psl']</t>
   </si>
   <si>
@@ -299,6 +311,12 @@
   </si>
   <si>
     <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'tas']</t>
@@ -671,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -683,7 +701,7 @@
     <col min="7" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="112.7109375" customWidth="1"/>
+    <col min="13" max="13" width="128.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -744,28 +762,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -777,22 +795,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -804,28 +822,28 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -837,22 +855,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -864,28 +882,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -900,13 +918,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -919,19 +937,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -946,13 +964,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -964,28 +982,28 @@
         <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1000,13 +1018,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1018,28 +1036,28 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1054,13 +1072,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1072,28 +1090,28 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1105,22 +1123,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1132,28 +1150,28 @@
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1168,13 +1186,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1186,28 +1204,28 @@
         <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1219,28 +1237,28 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1255,13 +1273,13 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M20" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1277,10 +1295,10 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1292,28 +1310,28 @@
         <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1328,13 +1346,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1346,28 +1364,28 @@
         <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1379,22 +1397,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1406,28 +1424,28 @@
         <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1442,13 +1460,13 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M27" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1460,28 +1478,28 @@
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1493,22 +1511,22 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1526,28 +1544,28 @@
         <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1562,13 +1580,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1577,31 +1595,31 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1616,13 +1634,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1630,20 +1648,32 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="K34" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1658,13 +1688,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1672,32 +1702,20 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M36" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1712,13 +1730,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M37" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1727,31 +1745,31 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M38" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1766,24 +1784,78 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M39" t="s">
-        <v>88</v>
+      <c r="K40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M41" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="A2:A39"/>
+  <mergeCells count="97">
+    <mergeCell ref="A2:A41"/>
     <mergeCell ref="B2:B29"/>
-    <mergeCell ref="B30:B39"/>
+    <mergeCell ref="B30:B41"/>
     <mergeCell ref="C2:C29"/>
-    <mergeCell ref="C30:C39"/>
+    <mergeCell ref="C30:C41"/>
     <mergeCell ref="D2:D29"/>
-    <mergeCell ref="D30:D39"/>
+    <mergeCell ref="D30:D41"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -1797,9 +1869,10 @@
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E37"/>
     <mergeCell ref="E38:E39"/>
+    <mergeCell ref="E40:E41"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -1813,9 +1886,10 @@
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="F28:F29"/>
     <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F34:F37"/>
     <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -1829,9 +1903,10 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G34:G37"/>
     <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G40:G41"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
@@ -1840,9 +1915,10 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H35"/>
-    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H37"/>
     <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H41"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -1852,9 +1928,10 @@
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I26:I27"/>
     <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I32:I35"/>
-    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="I34:I37"/>
     <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -1864,9 +1941,10 @@
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="J30:J31"/>
-    <mergeCell ref="J32:J35"/>
-    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J34:J37"/>
     <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J40:J41"/>
     <mergeCell ref="K20:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1078,7 +1078,7 @@
         <v>73</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:13">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -295,7 +295,7 @@
     <t>['pr', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
-    <t>['pr', 'psl', 'tasmax', 'tasmin']</t>
+    <t>['psl', 'tasmax', 'tasmin']</t>
   </si>
   <si>
     <t>['pr', 'psl']</t>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="115">
   <si>
     <t>variable_id</t>
   </si>
@@ -115,6 +115,9 @@
     <t>SMHI</t>
   </si>
   <si>
+    <t>CLMcom-CMCC</t>
+  </si>
+  <si>
     <t>CLMcom-Hereon</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
     <t>RCA4</t>
   </si>
   <si>
+    <t>CCLM6-0-1-URB</t>
+  </si>
+  <si>
     <t>ICON-CLM-202407-1-1</t>
   </si>
   <si>
@@ -199,6 +205,9 @@
     <t>RACMO23E</t>
   </si>
   <si>
+    <t>ALARO1-SFX</t>
+  </si>
+  <si>
     <t>v1</t>
   </si>
   <si>
@@ -271,6 +280,9 @@
     <t>v20131026</t>
   </si>
   <si>
+    <t>v20250201</t>
+  </si>
+  <si>
     <t>v20240920</t>
   </si>
   <si>
@@ -286,6 +298,9 @@
     <t>v20241216</t>
   </si>
   <si>
+    <t>v20241009</t>
+  </si>
+  <si>
     <t>['orog', 'sftlf']</t>
   </si>
   <si>
@@ -307,10 +322,19 @@
     <t>['pr', 'tas']</t>
   </si>
   <si>
+    <t>['tas', 'pr', 'hurs', 'prw', 'sfcWind']</t>
+  </si>
+  <si>
+    <t>['hurs', 'pr', 'tasmax', 'clt', 'tasmin', 'psl']</t>
+  </si>
+  <si>
+    <t>['clt', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'sfcWind']</t>
+  </si>
+  <si>
     <t>['areacella', 'sftlaf', 'mrsofc', 'rootd', 'sftlf', 'sftgif', 'orog', 'sfturf']</t>
   </si>
   <si>
-    <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+    <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'mrro', 'mrros', 'snw', 'evspsbl']</t>
   </si>
   <si>
     <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
@@ -332,6 +356,9 @@
   </si>
   <si>
     <t>['areacella', 'orog', 'sftlf']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlf', 'sfturf', 'sftlaf']</t>
   </si>
 </sst>
 </file>
@@ -689,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -762,28 +789,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -795,22 +822,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -822,28 +849,28 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -855,22 +882,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -882,28 +909,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -918,13 +945,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -937,19 +964,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -964,13 +991,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -982,28 +1009,28 @@
         <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1018,13 +1045,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1036,28 +1063,28 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1072,13 +1099,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M13" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1090,28 +1117,28 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M14" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1123,22 +1150,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1150,28 +1177,28 @@
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1186,13 +1213,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1204,28 +1231,28 @@
         <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1237,28 +1264,28 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M19" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1273,13 +1300,13 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1295,10 +1322,10 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M21" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1310,28 +1337,28 @@
         <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M22" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1346,13 +1373,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M23" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1364,28 +1391,28 @@
         <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1397,22 +1424,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M25" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1424,28 +1451,28 @@
         <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M26" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1460,13 +1487,13 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1478,28 +1505,28 @@
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1511,22 +1538,22 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M29" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1544,28 +1571,28 @@
         <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1580,13 +1607,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1594,32 +1621,20 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1627,20 +1642,32 @@
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K33" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M33" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1648,32 +1675,20 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1681,20 +1696,32 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K35" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1709,13 +1736,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M36" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1723,20 +1750,32 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K37" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M37" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1744,32 +1783,20 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1784,13 +1811,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M39" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1798,32 +1825,20 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M40" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1831,31 +1846,172 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K41" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M41" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M46" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="97">
-    <mergeCell ref="A2:A41"/>
+  <mergeCells count="109">
+    <mergeCell ref="A2:A46"/>
     <mergeCell ref="B2:B29"/>
-    <mergeCell ref="B30:B41"/>
+    <mergeCell ref="B30:B46"/>
     <mergeCell ref="C2:C29"/>
-    <mergeCell ref="C30:C41"/>
+    <mergeCell ref="C30:C46"/>
     <mergeCell ref="D2:D29"/>
-    <mergeCell ref="D30:D41"/>
+    <mergeCell ref="D30:D46"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -1868,11 +2024,13 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E37:E40"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E45:E46"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -1885,11 +2043,13 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="F45:F46"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -1902,11 +2062,13 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G45:G46"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
@@ -1914,11 +2076,13 @@
     <mergeCell ref="H19:H21"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H37:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -1927,11 +2091,13 @@
     <mergeCell ref="I19:I21"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="I34:I37"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="I37:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -1940,11 +2106,13 @@
     <mergeCell ref="J19:J21"/>
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J34:J37"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J30:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J37:J40"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="J45:J46"/>
     <mergeCell ref="K20:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="111">
   <si>
     <t>variable_id</t>
   </si>
@@ -115,9 +115,6 @@
     <t>SMHI</t>
   </si>
   <si>
-    <t>CLMcom-CMCC</t>
-  </si>
-  <si>
     <t>CLMcom-Hereon</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>RCA4</t>
   </si>
   <si>
-    <t>CCLM6-0-1-URB</t>
-  </si>
-  <si>
     <t>ICON-CLM-202407-1-1</t>
   </si>
   <si>
@@ -280,9 +274,6 @@
     <t>v20131026</t>
   </si>
   <si>
-    <t>v20250201</t>
-  </si>
-  <si>
     <t>v20240920</t>
   </si>
   <si>
@@ -322,15 +313,6 @@
     <t>['pr', 'tas']</t>
   </si>
   <si>
-    <t>['tas', 'pr', 'hurs', 'prw', 'sfcWind']</t>
-  </si>
-  <si>
-    <t>['hurs', 'pr', 'tasmax', 'clt', 'tasmin', 'psl']</t>
-  </si>
-  <si>
-    <t>['clt', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'sfcWind']</t>
-  </si>
-  <si>
     <t>['areacella', 'sftlaf', 'mrsofc', 'rootd', 'sftlf', 'sftgif', 'orog', 'sfturf']</t>
   </si>
   <si>
@@ -355,7 +337,13 @@
     <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr']</t>
   </si>
   <si>
+    <t>['pr', 'tas', 'zg500']</t>
+  </si>
+  <si>
     <t>['areacella', 'orog', 'sftlf']</t>
+  </si>
+  <si>
+    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'sfcWind']</t>
   </si>
   <si>
     <t>['orog', 'sftlf', 'sfturf', 'sftlaf']</t>
@@ -716,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -789,28 +777,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -822,22 +810,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -849,28 +837,28 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -882,22 +870,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -909,28 +897,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -945,13 +933,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -964,19 +952,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -991,13 +979,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1009,28 +997,28 @@
         <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1045,13 +1033,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1063,28 +1051,28 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1099,13 +1087,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1117,28 +1105,28 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1150,22 +1138,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1177,28 +1165,28 @@
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L16" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1213,13 +1201,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1231,28 +1219,28 @@
         <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1264,28 +1252,28 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1300,13 +1288,13 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1322,10 +1310,10 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1337,28 +1325,28 @@
         <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1373,13 +1361,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M23" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1391,28 +1379,28 @@
         <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L24" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1424,22 +1412,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M25" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1451,28 +1439,28 @@
         <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L26" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M26" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1487,13 +1475,13 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1505,28 +1493,28 @@
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L28" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1538,22 +1526,22 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1571,28 +1559,28 @@
         <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1607,13 +1595,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1621,20 +1609,32 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K32" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M32" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1642,32 +1642,20 @@
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J33" s="1" t="s">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L33" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1675,20 +1663,32 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K34" s="1" t="s">
         <v>67</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1696,32 +1696,20 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
         <v>66</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M35" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1736,13 +1724,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1750,32 +1738,20 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J37" s="1" t="s">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="L37" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M37" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1783,20 +1759,32 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K38" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M38" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1811,13 +1799,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M39" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1825,20 +1813,32 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M40" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1846,32 +1846,20 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M41" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1886,13 +1874,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M42" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1901,31 +1889,31 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M43" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1940,78 +1928,24 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M44" t="s">
         <v>93</v>
       </c>
-      <c r="M44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M45" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M46" t="s">
-        <v>96</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="109">
-    <mergeCell ref="A2:A46"/>
+  <mergeCells count="103">
+    <mergeCell ref="A2:A44"/>
     <mergeCell ref="B2:B29"/>
-    <mergeCell ref="B30:B46"/>
+    <mergeCell ref="B30:B44"/>
     <mergeCell ref="C2:C29"/>
-    <mergeCell ref="C30:C46"/>
+    <mergeCell ref="C30:C44"/>
     <mergeCell ref="D2:D29"/>
-    <mergeCell ref="D30:D46"/>
+    <mergeCell ref="D30:D44"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -2024,13 +1958,12 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="E37:E40"/>
-    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="E40:E42"/>
     <mergeCell ref="E43:E44"/>
-    <mergeCell ref="E45:E46"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -2043,13 +1976,12 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="F37:F40"/>
-    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F40:F42"/>
     <mergeCell ref="F43:F44"/>
-    <mergeCell ref="F45:F46"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -2062,13 +1994,12 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G37:G40"/>
-    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G40:G42"/>
     <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G45:G46"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
@@ -2076,13 +2007,12 @@
     <mergeCell ref="H19:H21"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H37:H40"/>
-    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H42"/>
     <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -2091,13 +2021,12 @@
     <mergeCell ref="I19:I21"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="I37:I40"/>
-    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I42"/>
     <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -2106,13 +2035,12 @@
     <mergeCell ref="J19:J21"/>
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J30:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J37:J40"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J40:J42"/>
     <mergeCell ref="J43:J44"/>
-    <mergeCell ref="J45:J46"/>
     <mergeCell ref="K20:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="123">
   <si>
     <t>variable_id</t>
   </si>
@@ -94,9 +94,6 @@
     <t>GERICS</t>
   </si>
   <si>
-    <t>ICTP</t>
-  </si>
-  <si>
     <t>IPSL</t>
   </si>
   <si>
@@ -115,9 +112,15 @@
     <t>SMHI</t>
   </si>
   <si>
+    <t>CLMcom-CMCC</t>
+  </si>
+  <si>
     <t>CLMcom-Hereon</t>
   </si>
   <si>
+    <t>CLMcom-KUL</t>
+  </si>
+  <si>
     <t>CNRM-MF</t>
   </si>
   <si>
@@ -163,9 +166,6 @@
     <t>REMO2015</t>
   </si>
   <si>
-    <t>RegCM4-6</t>
-  </si>
-  <si>
     <t>WRF381P</t>
   </si>
   <si>
@@ -184,9 +184,15 @@
     <t>RCA4</t>
   </si>
   <si>
+    <t>CCLM6-0-1-URB</t>
+  </si>
+  <si>
     <t>ICON-CLM-202407-1-1</t>
   </si>
   <si>
+    <t>CCLM6-0-1-URB-ESG</t>
+  </si>
+  <si>
     <t>CNRM-ALADIN64E1</t>
   </si>
   <si>
@@ -220,6 +226,9 @@
     <t>1hr</t>
   </si>
   <si>
+    <t>6hr</t>
+  </si>
+  <si>
     <t>v20140515</t>
   </si>
   <si>
@@ -244,9 +253,6 @@
     <t>v20180813</t>
   </si>
   <si>
-    <t>v20190502</t>
-  </si>
-  <si>
     <t>v20190919</t>
   </si>
   <si>
@@ -274,9 +280,18 @@
     <t>v20131026</t>
   </si>
   <si>
+    <t>v20250201</t>
+  </si>
+  <si>
     <t>v20240920</t>
   </si>
   <si>
+    <t>v20250130</t>
+  </si>
+  <si>
+    <t>v20250304</t>
+  </si>
+  <si>
     <t>v20250116</t>
   </si>
   <si>
@@ -301,9 +316,6 @@
     <t>['pr', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
-    <t>['psl', 'tasmax', 'tasmin']</t>
-  </si>
-  <si>
     <t>['pr', 'psl']</t>
   </si>
   <si>
@@ -313,12 +325,33 @@
     <t>['pr', 'tas']</t>
   </si>
   <si>
+    <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
+  </si>
+  <si>
+    <t>['hus1000', 'hus200', 'hus250', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta1000', 'ta200', 'ta250', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ua1000', 'ua200', 'ua250', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925']</t>
+  </si>
+  <si>
+    <t>['clt', 'hurs', 'pr', 'psl', 'tasmax', 'tasmin', 'zg500', 'sfcWindmax', 'snw']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlf', 'sfturf']</t>
+  </si>
+  <si>
+    <t>['clt', 'hfls', 'pr', 'psl', 'rlut', 'rlutcs', 'rsds', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500', 'snw']</t>
+  </si>
+  <si>
     <t>['areacella', 'sftlaf', 'mrsofc', 'rootd', 'sftlf', 'sftgif', 'orog', 'sfturf']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'mrro', 'mrros', 'snw', 'evspsbl']</t>
   </si>
   <si>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['pr']</t>
+  </si>
+  <si>
     <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
   </si>
   <si>
@@ -334,7 +367,7 @@
     <t>['areacella', 'orog', 'sftlf', 'sftlaf']</t>
   </si>
   <si>
-    <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr']</t>
+    <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr', 'psl']</t>
   </si>
   <si>
     <t>['pr', 'tas', 'zg500']</t>
@@ -347,6 +380,9 @@
   </si>
   <si>
     <t>['orog', 'sftlf', 'sfturf', 'sftlaf']</t>
+  </si>
+  <si>
+    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'rsds', 'rlds']</t>
   </si>
 </sst>
 </file>
@@ -704,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -716,7 +752,7 @@
     <col min="7" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="128.7109375" customWidth="1"/>
+    <col min="13" max="13" width="285.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -777,28 +813,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -810,22 +846,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -837,28 +873,28 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -870,22 +906,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -897,28 +933,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -933,13 +969,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -952,19 +988,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -979,13 +1015,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -997,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1033,13 +1069,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1051,28 +1087,28 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1087,13 +1123,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1105,28 +1141,28 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1138,22 +1174,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1165,28 +1201,28 @@
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1194,20 +1230,32 @@
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="K17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1215,32 +1263,20 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M18" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1248,32 +1284,18 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1281,20 +1303,32 @@
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="K20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1308,12 +1342,14 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="L21" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1325,28 +1361,28 @@
         <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1357,17 +1393,23 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="H23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="K23" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1379,28 +1421,28 @@
         <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M24" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1411,23 +1453,17 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1439,28 +1475,28 @@
         <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M26" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1471,14 +1507,20 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="H27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M27" t="s">
         <v>98</v>
@@ -1486,35 +1528,41 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M28" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1525,62 +1573,38 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M29" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M30" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1595,13 +1619,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1609,32 +1633,20 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M32" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1642,20 +1654,32 @@
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K33" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M33" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1663,32 +1687,20 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
         <v>67</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1696,20 +1708,32 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K35" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M35" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1724,13 +1748,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M36" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1738,20 +1762,32 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K37" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M37" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1759,32 +1795,20 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M38" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1799,13 +1823,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M39" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1814,31 +1838,31 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>60</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M40" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1853,13 +1877,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M41" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1874,13 +1898,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M42" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1888,32 +1912,20 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>63</v>
-      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M43" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1921,127 +1933,295 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M44" t="s">
-        <v>93</v>
+      <c r="K46" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M47" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M48" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M49" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M50" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="103">
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B29"/>
-    <mergeCell ref="B30:B44"/>
-    <mergeCell ref="C2:C29"/>
-    <mergeCell ref="C30:C44"/>
-    <mergeCell ref="D2:D29"/>
-    <mergeCell ref="D30:D44"/>
+  <mergeCells count="109">
+    <mergeCell ref="A2:A50"/>
+    <mergeCell ref="B2:B27"/>
+    <mergeCell ref="B28:B50"/>
+    <mergeCell ref="C2:C27"/>
+    <mergeCell ref="C28:C50"/>
+    <mergeCell ref="D2:D27"/>
+    <mergeCell ref="D28:D50"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E40:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="E49:E50"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="F28:F32"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="F40:F43"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F49:F50"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G28:G32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="G49:G50"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="H28:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="H40:H43"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="H49:H50"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="I34:I37"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I42"/>
-    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="I28:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="I37:I39"/>
+    <mergeCell ref="I40:I43"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="I46:I48"/>
+    <mergeCell ref="I49:I50"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J34:J37"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J28:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K18:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="123">
   <si>
     <t>variable_id</t>
   </si>
@@ -740,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1952,13 +1952,13 @@
         <v>65</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>94</v>
       </c>
       <c r="M44" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1973,13 +1973,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>94</v>
       </c>
       <c r="M45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1987,32 +1987,20 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M46" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2020,20 +2008,32 @@
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K47" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>95</v>
       </c>
       <c r="M47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2048,13 +2048,13 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>95</v>
       </c>
       <c r="M48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2062,32 +2062,20 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M49" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2095,31 +2083,64 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K50" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>96</v>
       </c>
       <c r="M50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M51" t="s">
         <v>122</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="109">
-    <mergeCell ref="A2:A50"/>
+    <mergeCell ref="A2:A51"/>
     <mergeCell ref="B2:B27"/>
-    <mergeCell ref="B28:B50"/>
+    <mergeCell ref="B28:B51"/>
     <mergeCell ref="C2:C27"/>
-    <mergeCell ref="C28:C50"/>
+    <mergeCell ref="C28:C51"/>
     <mergeCell ref="D2:D27"/>
-    <mergeCell ref="D28:D50"/>
+    <mergeCell ref="D28:D51"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -2136,9 +2157,9 @@
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="E37:E39"/>
     <mergeCell ref="E40:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="E50:E51"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -2155,9 +2176,9 @@
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="F37:F39"/>
     <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="F50:F51"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -2174,9 +2195,9 @@
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="G37:G39"/>
     <mergeCell ref="G40:G43"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="G50:G51"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
@@ -2188,9 +2209,9 @@
     <mergeCell ref="H35:H36"/>
     <mergeCell ref="H37:H39"/>
     <mergeCell ref="H40:H43"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="H50:H51"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -2203,9 +2224,9 @@
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="I37:I39"/>
     <mergeCell ref="I40:I43"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="I46:I48"/>
-    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="I47:I49"/>
+    <mergeCell ref="I50:I51"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -2218,9 +2239,9 @@
     <mergeCell ref="J35:J36"/>
     <mergeCell ref="J37:J39"/>
     <mergeCell ref="J40:J43"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="J46:J48"/>
-    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J44:J46"/>
+    <mergeCell ref="J47:J49"/>
+    <mergeCell ref="J50:J51"/>
     <mergeCell ref="K18:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="132">
   <si>
     <t>variable_id</t>
   </si>
@@ -133,9 +133,24 @@
     <t>ERA5</t>
   </si>
   <si>
+    <t>CNRM-ESM2-1</t>
+  </si>
+  <si>
+    <t>EC-Earth3-Veg</t>
+  </si>
+  <si>
+    <t>MIROC6</t>
+  </si>
+  <si>
     <t>evaluation</t>
   </si>
   <si>
+    <t>historical</t>
+  </si>
+  <si>
+    <t>ssp370</t>
+  </si>
+  <si>
     <t>r0i0p0</t>
   </si>
   <si>
@@ -145,6 +160,15 @@
     <t>r1i1p1f1</t>
   </si>
   <si>
+    <t>r1i1p1f2</t>
+  </si>
+  <si>
+    <t>r2i1p1f1</t>
+  </si>
+  <si>
+    <t>r3i1p1f1</t>
+  </si>
+  <si>
     <t>CCLM4-8-17</t>
   </si>
   <si>
@@ -368,6 +392,9 @@
   </si>
   <si>
     <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr', 'psl']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['pr', 'tas', 'zg500']</t>
@@ -740,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -816,25 +843,25 @@
         <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -846,22 +873,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -876,25 +903,25 @@
         <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="M4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -906,22 +933,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -936,25 +963,25 @@
         <v>37</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -969,13 +996,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M7" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -988,19 +1015,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1015,13 +1042,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1036,25 +1063,25 @@
         <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M10" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1069,13 +1096,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1090,25 +1117,25 @@
         <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M12" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1123,13 +1150,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1144,25 +1171,25 @@
         <v>37</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1174,22 +1201,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1204,25 +1231,25 @@
         <v>37</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="M16" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1237,25 +1264,25 @@
         <v>37</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1270,13 +1297,13 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1292,10 +1319,10 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="M19" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1310,25 +1337,25 @@
         <v>37</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1343,13 +1370,13 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M21" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1364,25 +1391,25 @@
         <v>37</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M22" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1394,22 +1421,22 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M23" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1424,25 +1451,25 @@
         <v>37</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="M24" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1457,13 +1484,13 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="M25" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1478,25 +1505,25 @@
         <v>37</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="M26" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1508,22 +1535,22 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="M27" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1544,25 +1571,25 @@
         <v>38</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M28" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1577,13 +1604,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1598,13 +1625,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M30" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1619,13 +1646,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M31" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1640,13 +1667,13 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M32" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1661,25 +1688,25 @@
         <v>38</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M33" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1694,13 +1721,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M34" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1715,25 +1742,25 @@
         <v>38</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M35" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1748,13 +1775,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M36" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1769,25 +1796,25 @@
         <v>38</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="M37" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1802,13 +1829,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M38" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1823,13 +1850,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M39" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1844,25 +1871,25 @@
         <v>38</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M40" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1877,13 +1904,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M41" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1898,13 +1925,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M42" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1919,13 +1946,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M43" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1937,28 +1964,28 @@
         <v>36</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="M44" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1968,18 +1995,26 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="G45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K45" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="M45" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1988,19 +2023,29 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="M46" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2008,32 +2053,26 @@
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
       <c r="H47" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="M47" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2044,17 +2083,23 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="H48" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K48" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="M48" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2063,19 +2108,29 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K49" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="M49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2083,32 +2138,20 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2123,24 +2166,213 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M51" t="s">
-        <v>122</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="M52" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="M53" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M55" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M58" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="109">
-    <mergeCell ref="A2:A51"/>
+  <mergeCells count="113">
+    <mergeCell ref="A2:A58"/>
     <mergeCell ref="B2:B27"/>
-    <mergeCell ref="B28:B51"/>
+    <mergeCell ref="B28:B58"/>
     <mergeCell ref="C2:C27"/>
-    <mergeCell ref="C28:C51"/>
+    <mergeCell ref="C28:C58"/>
     <mergeCell ref="D2:D27"/>
-    <mergeCell ref="D28:D51"/>
+    <mergeCell ref="D28:D58"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -2157,9 +2389,9 @@
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="E37:E39"/>
     <mergeCell ref="E40:E43"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="E44:E53"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="E57:E58"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -2176,9 +2408,12 @@
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="F37:F39"/>
     <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F49:F51"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="F57:F58"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -2195,9 +2430,10 @@
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="G37:G39"/>
     <mergeCell ref="G40:G43"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="G57:G58"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
@@ -2209,9 +2445,9 @@
     <mergeCell ref="H35:H36"/>
     <mergeCell ref="H37:H39"/>
     <mergeCell ref="H40:H43"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="H47:H49"/>
-    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="H57:H58"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -2224,9 +2460,9 @@
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="I37:I39"/>
     <mergeCell ref="I40:I43"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="I47:I49"/>
-    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I49:I51"/>
+    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="I57:I58"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -2239,9 +2475,9 @@
     <mergeCell ref="J35:J36"/>
     <mergeCell ref="J37:J39"/>
     <mergeCell ref="J40:J43"/>
-    <mergeCell ref="J44:J46"/>
-    <mergeCell ref="J47:J49"/>
-    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="J49:J51"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="J57:J58"/>
     <mergeCell ref="K18:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="139">
   <si>
     <t>variable_id</t>
   </si>
@@ -124,6 +124,9 @@
     <t>CNRM-MF</t>
   </si>
   <si>
+    <t>HCLIMcom-METNo</t>
+  </si>
+  <si>
     <t>HCLIMcom-SMHI</t>
   </si>
   <si>
@@ -136,12 +139,18 @@
     <t>CNRM-ESM2-1</t>
   </si>
   <si>
+    <t>NorESM2-MM</t>
+  </si>
+  <si>
     <t>EC-Earth3-Veg</t>
   </si>
   <si>
     <t>MIROC6</t>
   </si>
   <si>
+    <t>MPI-ESM1-2-HR</t>
+  </si>
+  <si>
     <t>evaluation</t>
   </si>
   <si>
@@ -313,6 +322,9 @@
     <t>v20250130</t>
   </si>
   <si>
+    <t>v20250327</t>
+  </si>
+  <si>
     <t>v20250304</t>
   </si>
   <si>
@@ -373,6 +385,9 @@
     <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
   </si>
   <si>
+    <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
+  </si>
+  <si>
     <t>['pr']</t>
   </si>
   <si>
@@ -394,7 +409,13 @@
     <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr', 'psl']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
+    <t>['sfcWind']</t>
+  </si>
+  <si>
+    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'rlds', 'rsds', 'uas', 'vas', 'sfcWind']</t>
   </si>
   <si>
     <t>['pr', 'tas', 'zg500']</t>
@@ -767,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -840,28 +861,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -873,22 +894,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -900,28 +921,28 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -933,22 +954,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -960,28 +981,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -996,13 +1017,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1015,19 +1036,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1042,13 +1063,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1060,28 +1081,28 @@
         <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1096,13 +1117,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1114,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1150,13 +1171,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1168,28 +1189,28 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1201,22 +1222,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1228,28 +1249,28 @@
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1261,28 +1282,28 @@
         <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M17" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1297,13 +1318,13 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1319,10 +1340,10 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1334,28 +1355,28 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M20" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1370,13 +1391,13 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1388,28 +1409,28 @@
         <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1421,22 +1442,22 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1448,28 +1469,28 @@
         <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1484,13 +1505,13 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1502,28 +1523,28 @@
         <v>31</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M26" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1535,22 +1556,22 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1568,28 +1589,28 @@
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1604,13 +1625,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M29" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1625,13 +1646,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1646,13 +1667,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1667,13 +1688,13 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1685,28 +1706,28 @@
         <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1721,13 +1742,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1739,28 +1760,28 @@
         <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1775,13 +1796,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1793,28 +1814,28 @@
         <v>35</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1824,18 +1845,26 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K38" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1844,19 +1873,29 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K39" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M39" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1864,32 +1903,20 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M40" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1904,13 +1931,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M41" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1918,20 +1945,32 @@
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K42" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1946,13 +1985,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1960,32 +1999,20 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M44" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1995,26 +2022,18 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M45" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2022,30 +2041,32 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="F46" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M46" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2056,23 +2077,17 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M47" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2082,24 +2097,26 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
+      <c r="G48" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H48" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M48" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2108,29 +2125,19 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M49" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2138,20 +2145,32 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K50" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M50" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2166,13 +2185,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M51" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2181,29 +2200,27 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M52" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2213,26 +2230,18 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M53" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2240,32 +2249,30 @@
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M54" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2280,13 +2287,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M55" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2297,17 +2304,23 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
+      <c r="H56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K56" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M56" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2315,32 +2328,20 @@
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M57" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2351,28 +2352,628 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="H58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="K58" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M58" t="s">
         <v>131</v>
       </c>
     </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M59" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M60" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M61" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M62" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M63" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M64" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M66" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M67" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M68" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M69" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M70" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M71" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M72" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M73" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M74" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M75" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M76" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M77" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M78" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M79" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M80" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M81" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M82" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="A2:A58"/>
+  <mergeCells count="168">
+    <mergeCell ref="A2:A82"/>
     <mergeCell ref="B2:B27"/>
-    <mergeCell ref="B28:B58"/>
+    <mergeCell ref="B28:B82"/>
     <mergeCell ref="C2:C27"/>
-    <mergeCell ref="C28:C58"/>
+    <mergeCell ref="C28:C82"/>
     <mergeCell ref="D2:D27"/>
-    <mergeCell ref="D28:D58"/>
+    <mergeCell ref="D28:D82"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -2387,11 +2988,12 @@
     <mergeCell ref="E28:E32"/>
     <mergeCell ref="E33:E34"/>
     <mergeCell ref="E35:E36"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E40:E43"/>
-    <mergeCell ref="E44:E53"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E50:E77"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="E81:E82"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -2406,14 +3008,17 @@
     <mergeCell ref="F28:F32"/>
     <mergeCell ref="F33:F34"/>
     <mergeCell ref="F35:F36"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F54:F65"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="F81:F82"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -2428,12 +3033,21 @@
     <mergeCell ref="G28:G32"/>
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G43"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G54:G59"/>
+    <mergeCell ref="G60:G65"/>
+    <mergeCell ref="G66:G69"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="G81:G82"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H12:H13"/>
@@ -2443,11 +3057,25 @@
     <mergeCell ref="H28:H32"/>
     <mergeCell ref="H33:H34"/>
     <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H37:H39"/>
-    <mergeCell ref="H40:H43"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="H81:H82"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -2458,11 +3086,25 @@
     <mergeCell ref="I28:I32"/>
     <mergeCell ref="I33:I34"/>
     <mergeCell ref="I35:I36"/>
-    <mergeCell ref="I37:I39"/>
-    <mergeCell ref="I40:I43"/>
-    <mergeCell ref="I49:I51"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="I42:I45"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="I66:I69"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="I81:I82"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -2473,11 +3115,25 @@
     <mergeCell ref="J28:J32"/>
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J37:J39"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="J49:J51"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="J42:J45"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="J64:J65"/>
+    <mergeCell ref="J66:J69"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="J81:J82"/>
     <mergeCell ref="K18:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -322,7 +322,7 @@
     <t>v20250130</t>
   </si>
   <si>
-    <t>v20250327</t>
+    <t>v20240122</t>
   </si>
   <si>
     <t>v20250304</t>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -322,7 +322,7 @@
     <t>v20250130</t>
   </si>
   <si>
-    <t>v20240122</t>
+    <t>v20250328</t>
   </si>
   <si>
     <t>v20250304</t>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="137">
   <si>
     <t>variable_id</t>
   </si>
@@ -88,9 +88,6 @@
     <t>DHMZ</t>
   </si>
   <si>
-    <t>DMI</t>
-  </si>
-  <si>
     <t>GERICS</t>
   </si>
   <si>
@@ -193,9 +190,6 @@
     <t>RegCM4-2</t>
   </si>
   <si>
-    <t>HIRHAM5</t>
-  </si>
-  <si>
     <t>REMO2015</t>
   </si>
   <si>
@@ -280,9 +274,6 @@
     <t>v20150527</t>
   </si>
   <si>
-    <t>v20140620</t>
-  </si>
-  <si>
     <t>v20180813</t>
   </si>
   <si>
@@ -319,12 +310,12 @@
     <t>v20240920</t>
   </si>
   <si>
+    <t>v20250328</t>
+  </si>
+  <si>
     <t>v20250130</t>
   </si>
   <si>
-    <t>v20250328</t>
-  </si>
-  <si>
     <t>v20250304</t>
   </si>
   <si>
@@ -382,13 +373,16 @@
     <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'mrro', 'mrros', 'snw', 'evspsbl']</t>
   </si>
   <si>
+    <t>['pr']</t>
+  </si>
+  <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
   </si>
   <si>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas']</t>
+  </si>
+  <si>
     <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
-  </si>
-  <si>
-    <t>['pr']</t>
   </si>
   <si>
     <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
@@ -788,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -861,28 +855,28 @@
         <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -894,22 +888,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -921,28 +915,28 @@
         <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -954,22 +948,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -981,28 +975,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1017,13 +1011,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1036,19 +1030,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1063,13 +1057,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1081,28 +1075,28 @@
         <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1117,13 +1111,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1135,28 +1129,28 @@
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1167,17 +1161,23 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1189,28 +1189,28 @@
         <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1218,26 +1218,32 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>60</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="L15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1245,32 +1251,20 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1278,32 +1272,18 @@
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1311,20 +1291,32 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K18" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1338,12 +1330,14 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="L19" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M19" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1355,28 +1349,28 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L20" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1387,17 +1381,23 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K21" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1409,28 +1409,28 @@
         <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L22" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1441,23 +1441,17 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1469,28 +1463,28 @@
         <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1501,24 +1495,36 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="H25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="K25" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M25" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E26" s="1" t="s">
         <v>31</v>
       </c>
@@ -1526,25 +1532,25 @@
         <v>38</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M26" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1555,62 +1561,38 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M27" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1"/>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1625,13 +1607,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1646,13 +1628,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1660,20 +1642,32 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K31" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1688,13 +1682,13 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1706,28 +1700,28 @@
         <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1742,13 +1736,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1756,32 +1750,18 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1796,13 +1776,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M36" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1810,32 +1790,20 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M37" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1845,26 +1813,16 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1872,7 +1830,9 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="F39" s="1" t="s">
         <v>39</v>
       </c>
@@ -1883,19 +1843,19 @@
         <v>50</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1905,18 +1865,26 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="G40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K40" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="M40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1925,19 +1893,29 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K41" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M41" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1945,32 +1923,20 @@
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M42" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1985,13 +1951,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M43" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1999,20 +1965,32 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M44" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2027,13 +2005,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M45" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2041,32 +2019,20 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M46" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2081,13 +2047,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M47" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2095,28 +2061,32 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G48" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2131,13 +2101,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2145,32 +2115,28 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M50" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2185,13 +2151,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2199,28 +2165,32 @@
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="G52" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2235,13 +2205,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M53" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2250,9 +2220,7 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
         <v>46</v>
       </c>
@@ -2260,19 +2228,19 @@
         <v>50</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M54" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2287,13 +2255,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2302,25 +2270,29 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H56" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M56" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2335,13 +2307,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M57" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2353,22 +2325,22 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2383,13 +2355,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M59" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2399,26 +2371,24 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="G60" s="1"/>
       <c r="H60" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M60" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2433,13 +2403,13 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M61" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2449,24 +2419,26 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H62" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M62" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2481,13 +2453,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M63" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2499,22 +2471,22 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M64" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2529,13 +2501,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M65" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2544,29 +2516,25 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
       <c r="H66" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M66" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2581,13 +2549,13 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M67" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2596,19 +2564,29 @@
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="F68" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K68" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M68" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2623,13 +2601,13 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M69" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2638,29 +2616,19 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L70" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M70" t="s">
         <v>106</v>
-      </c>
-      <c r="M70" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2675,13 +2643,13 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M71" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2690,27 +2658,29 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G72" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M72" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2725,13 +2695,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M73" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2740,29 +2710,27 @@
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M74" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2777,13 +2745,13 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M75" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2792,27 +2760,29 @@
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G76" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M76" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2827,13 +2797,13 @@
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M77" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2841,32 +2811,28 @@
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
-      <c r="E78" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M78" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2881,13 +2847,13 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M79" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2895,20 +2861,32 @@
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="E80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K80" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M80" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2916,32 +2894,20 @@
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M81" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2956,110 +2922,159 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M82" t="s">
-        <v>138</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M83" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M84" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="168">
-    <mergeCell ref="A2:A82"/>
-    <mergeCell ref="B2:B27"/>
-    <mergeCell ref="B28:B82"/>
-    <mergeCell ref="C2:C27"/>
-    <mergeCell ref="C28:C82"/>
-    <mergeCell ref="D2:D27"/>
-    <mergeCell ref="D28:D82"/>
+  <mergeCells count="164">
+    <mergeCell ref="A2:A84"/>
+    <mergeCell ref="B2:B25"/>
+    <mergeCell ref="B26:B84"/>
+    <mergeCell ref="C2:C25"/>
+    <mergeCell ref="C26:C84"/>
+    <mergeCell ref="D2:D25"/>
+    <mergeCell ref="D26:D84"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E18:E19"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E28:E32"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E50:E77"/>
-    <mergeCell ref="E78:E80"/>
-    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E33:E38"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="E52:E79"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="E83:E84"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F32"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F54:F65"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="F78:F80"/>
-    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="F26:F30"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="F33:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="F44:F47"/>
+    <mergeCell ref="F48:F51"/>
+    <mergeCell ref="F52:F55"/>
+    <mergeCell ref="F56:F67"/>
+    <mergeCell ref="F68:F71"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="F76:F79"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="F83:F84"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G18:G19"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="G28:G32"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G33:G38"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="G44:G47"/>
     <mergeCell ref="G48:G49"/>
     <mergeCell ref="G50:G51"/>
     <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G59"/>
-    <mergeCell ref="G60:G65"/>
-    <mergeCell ref="G66:G69"/>
-    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="G56:G61"/>
+    <mergeCell ref="G62:G67"/>
+    <mergeCell ref="G68:G71"/>
     <mergeCell ref="G72:G73"/>
     <mergeCell ref="G74:G75"/>
     <mergeCell ref="G76:G77"/>
-    <mergeCell ref="G78:G80"/>
-    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="G83:G84"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="H28:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H38"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="H44:H47"/>
     <mergeCell ref="H48:H49"/>
     <mergeCell ref="H50:H51"/>
     <mergeCell ref="H52:H53"/>
@@ -3069,26 +3084,25 @@
     <mergeCell ref="H60:H61"/>
     <mergeCell ref="H62:H63"/>
     <mergeCell ref="H64:H65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="H68:H71"/>
     <mergeCell ref="H72:H73"/>
     <mergeCell ref="H74:H75"/>
     <mergeCell ref="H76:H77"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="H83:H84"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="I28:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="I42:I45"/>
-    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I26:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I38"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="I44:I47"/>
     <mergeCell ref="I48:I49"/>
     <mergeCell ref="I50:I51"/>
     <mergeCell ref="I52:I53"/>
@@ -3098,26 +3112,25 @@
     <mergeCell ref="I60:I61"/>
     <mergeCell ref="I62:I63"/>
     <mergeCell ref="I64:I65"/>
-    <mergeCell ref="I66:I69"/>
-    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="I68:I71"/>
     <mergeCell ref="I72:I73"/>
     <mergeCell ref="I74:I75"/>
     <mergeCell ref="I76:I77"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="I83:I84"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J28:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="J42:J45"/>
-    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J26:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J38"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="J44:J47"/>
     <mergeCell ref="J48:J49"/>
     <mergeCell ref="J50:J51"/>
     <mergeCell ref="J52:J53"/>
@@ -3127,14 +3140,17 @@
     <mergeCell ref="J60:J61"/>
     <mergeCell ref="J62:J63"/>
     <mergeCell ref="J64:J65"/>
-    <mergeCell ref="J66:J69"/>
-    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="J68:J71"/>
     <mergeCell ref="J72:J73"/>
     <mergeCell ref="J74:J75"/>
     <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="J81:J82"/>
-    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="J83:J84"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="K37:K38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="135">
   <si>
     <t>variable_id</t>
   </si>
@@ -313,9 +313,6 @@
     <t>v20250328</t>
   </si>
   <si>
-    <t>v20250130</t>
-  </si>
-  <si>
     <t>v20250304</t>
   </si>
   <si>
@@ -374,9 +371,6 @@
   </si>
   <si>
     <t>['pr']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas']</t>
@@ -782,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -876,7 +870,7 @@
         <v>80</v>
       </c>
       <c r="M2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -903,7 +897,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -936,7 +930,7 @@
         <v>81</v>
       </c>
       <c r="M4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -963,7 +957,7 @@
         <v>81</v>
       </c>
       <c r="M5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -996,7 +990,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1017,7 +1011,7 @@
         <v>82</v>
       </c>
       <c r="M7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1042,7 +1036,7 @@
         <v>83</v>
       </c>
       <c r="M8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1063,7 +1057,7 @@
         <v>83</v>
       </c>
       <c r="M9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1096,7 +1090,7 @@
         <v>84</v>
       </c>
       <c r="M10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1117,7 +1111,7 @@
         <v>85</v>
       </c>
       <c r="M11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1150,7 +1144,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1177,7 +1171,7 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1210,7 +1204,7 @@
         <v>87</v>
       </c>
       <c r="M14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1243,7 +1237,7 @@
         <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1264,7 +1258,7 @@
         <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1283,7 +1277,7 @@
         <v>89</v>
       </c>
       <c r="M17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1316,7 +1310,7 @@
         <v>90</v>
       </c>
       <c r="M18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1337,7 +1331,7 @@
         <v>91</v>
       </c>
       <c r="M19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1370,7 +1364,7 @@
         <v>92</v>
       </c>
       <c r="M20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1397,7 +1391,7 @@
         <v>92</v>
       </c>
       <c r="M21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1430,7 +1424,7 @@
         <v>93</v>
       </c>
       <c r="M22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1451,7 +1445,7 @@
         <v>94</v>
       </c>
       <c r="M23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1484,7 +1478,7 @@
         <v>95</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1511,7 +1505,7 @@
         <v>95</v>
       </c>
       <c r="M25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1550,7 +1544,7 @@
         <v>96</v>
       </c>
       <c r="M26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1571,7 +1565,7 @@
         <v>96</v>
       </c>
       <c r="M27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1592,7 +1586,7 @@
         <v>96</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1613,7 +1607,7 @@
         <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1634,7 +1628,7 @@
         <v>96</v>
       </c>
       <c r="M30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1667,7 +1661,7 @@
         <v>97</v>
       </c>
       <c r="M31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1688,7 +1682,7 @@
         <v>97</v>
       </c>
       <c r="M32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1721,7 +1715,7 @@
         <v>98</v>
       </c>
       <c r="M33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1739,10 +1733,10 @@
         <v>77</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1756,12 +1750,14 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="L35" s="1" t="s">
         <v>98</v>
       </c>
       <c r="M35" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1776,13 +1772,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>98</v>
       </c>
       <c r="M36" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1790,17 +1786,29 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K37" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M37" t="s">
         <v>120</v>
@@ -1813,16 +1821,26 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="L38" s="1" t="s">
         <v>98</v>
       </c>
       <c r="M38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1830,17 +1848,15 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>68</v>
@@ -1849,13 +1865,13 @@
         <v>74</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M39" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1865,26 +1881,18 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1893,29 +1901,19 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>100</v>
       </c>
       <c r="M41" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1923,14 +1921,26 @@
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K42" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>101</v>
@@ -1951,7 +1961,7 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>101</v>
@@ -1965,29 +1975,17 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M44" t="s">
         <v>125</v>
@@ -2005,10 +2003,10 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M45" t="s">
         <v>126</v>
@@ -2019,14 +2017,26 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>102</v>
@@ -2061,14 +2071,10 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>49</v>
@@ -2083,10 +2089,10 @@
         <v>77</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2104,10 +2110,10 @@
         <v>76</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2115,13 +2121,17 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="G50" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>70</v>
@@ -2133,10 +2143,10 @@
         <v>77</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2154,10 +2164,10 @@
         <v>76</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M51" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2165,14 +2175,10 @@
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>50</v>
@@ -2187,10 +2193,10 @@
         <v>77</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2208,10 +2214,10 @@
         <v>76</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M53" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2220,12 +2226,14 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G54" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>70</v>
@@ -2237,10 +2245,10 @@
         <v>77</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2258,10 +2266,10 @@
         <v>76</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M55" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2270,14 +2278,10 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
       <c r="H56" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>70</v>
@@ -2289,10 +2293,10 @@
         <v>77</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2310,10 +2314,10 @@
         <v>76</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2325,7 +2329,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>70</v>
@@ -2337,10 +2341,10 @@
         <v>77</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2358,10 +2362,10 @@
         <v>76</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M59" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2371,9 +2375,11 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H60" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>70</v>
@@ -2385,10 +2391,10 @@
         <v>77</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2406,10 +2412,10 @@
         <v>76</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M61" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2419,11 +2425,9 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>70</v>
@@ -2435,10 +2439,10 @@
         <v>77</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2456,10 +2460,10 @@
         <v>76</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M63" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2471,7 +2475,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>70</v>
@@ -2483,10 +2487,10 @@
         <v>77</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M64" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2504,10 +2508,10 @@
         <v>76</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2516,10 +2520,14 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H66" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>70</v>
@@ -2528,13 +2536,13 @@
         <v>74</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M66" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2549,13 +2557,13 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M67" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2564,29 +2572,19 @@
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M68" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2601,10 +2599,10 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M69" t="s">
         <v>129</v>
@@ -2616,19 +2614,29 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M70" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2646,10 +2654,10 @@
         <v>76</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M71" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2658,11 +2666,9 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="F72" s="1"/>
       <c r="G72" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>49</v>
@@ -2677,10 +2683,10 @@
         <v>77</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M72" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2698,10 +2704,10 @@
         <v>76</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M73" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2710,9 +2716,11 @@
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G74" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>49</v>
@@ -2727,10 +2735,10 @@
         <v>77</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M74" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2748,10 +2756,10 @@
         <v>76</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M75" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2760,11 +2768,9 @@
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>49</v>
@@ -2779,10 +2785,10 @@
         <v>77</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M76" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2800,10 +2806,10 @@
         <v>76</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M77" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2811,16 +2817,20 @@
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+      <c r="E78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G78" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>74</v>
@@ -2832,7 +2842,7 @@
         <v>103</v>
       </c>
       <c r="M78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2847,13 +2857,13 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>103</v>
       </c>
       <c r="M79" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2861,29 +2871,17 @@
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
-      <c r="E80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M80" t="s">
         <v>132</v>
@@ -2894,12 +2892,24 @@
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="E81" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K81" s="1" t="s">
         <v>75</v>
       </c>
@@ -2931,69 +2941,15 @@
         <v>134</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M83" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M84" t="s">
-        <v>136</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="164">
-    <mergeCell ref="A2:A84"/>
+  <mergeCells count="162">
+    <mergeCell ref="A2:A82"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B84"/>
+    <mergeCell ref="B26:B82"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C84"/>
+    <mergeCell ref="C26:C82"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D84"/>
+    <mergeCell ref="D26:D82"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -3006,13 +2962,13 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E26:E30"/>
     <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E33:E38"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="E44:E47"/>
-    <mergeCell ref="E48:E51"/>
-    <mergeCell ref="E52:E79"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E50:E77"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="E81:E82"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -3025,18 +2981,18 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F26:F30"/>
     <mergeCell ref="F31:F32"/>
-    <mergeCell ref="F33:F38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="F44:F47"/>
-    <mergeCell ref="F48:F51"/>
-    <mergeCell ref="F52:F55"/>
-    <mergeCell ref="F56:F67"/>
-    <mergeCell ref="F68:F71"/>
-    <mergeCell ref="F72:F75"/>
-    <mergeCell ref="F76:F79"/>
-    <mergeCell ref="F80:F82"/>
-    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F54:F65"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="F81:F82"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -3049,22 +3005,22 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G26:G30"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G33:G38"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="G44:G47"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="G46:G47"/>
     <mergeCell ref="G48:G49"/>
     <mergeCell ref="G50:G51"/>
     <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="G56:G61"/>
-    <mergeCell ref="G62:G67"/>
-    <mergeCell ref="G68:G71"/>
+    <mergeCell ref="G54:G59"/>
+    <mergeCell ref="G60:G65"/>
+    <mergeCell ref="G66:G69"/>
+    <mergeCell ref="G70:G71"/>
     <mergeCell ref="G72:G73"/>
     <mergeCell ref="G74:G75"/>
     <mergeCell ref="G76:G77"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="G81:G82"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -3072,9 +3028,10 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H26:H30"/>
     <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H38"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="H46:H47"/>
     <mergeCell ref="H48:H49"/>
     <mergeCell ref="H50:H51"/>
     <mergeCell ref="H52:H53"/>
@@ -3084,14 +3041,13 @@
     <mergeCell ref="H60:H61"/>
     <mergeCell ref="H62:H63"/>
     <mergeCell ref="H64:H65"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="H68:H71"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="H70:H71"/>
     <mergeCell ref="H72:H73"/>
     <mergeCell ref="H74:H75"/>
     <mergeCell ref="H76:H77"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="H81:H82"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -3100,9 +3056,10 @@
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I26:I30"/>
     <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I38"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="I33:I36"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="I42:I45"/>
+    <mergeCell ref="I46:I47"/>
     <mergeCell ref="I48:I49"/>
     <mergeCell ref="I50:I51"/>
     <mergeCell ref="I52:I53"/>
@@ -3112,14 +3069,13 @@
     <mergeCell ref="I60:I61"/>
     <mergeCell ref="I62:I63"/>
     <mergeCell ref="I64:I65"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="I68:I71"/>
+    <mergeCell ref="I66:I69"/>
+    <mergeCell ref="I70:I71"/>
     <mergeCell ref="I72:I73"/>
     <mergeCell ref="I74:I75"/>
     <mergeCell ref="I76:I77"/>
-    <mergeCell ref="I78:I79"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="I81:I82"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -3128,9 +3084,10 @@
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="J26:J30"/>
     <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J38"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="J44:J47"/>
+    <mergeCell ref="J33:J36"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="J42:J45"/>
+    <mergeCell ref="J46:J47"/>
     <mergeCell ref="J48:J49"/>
     <mergeCell ref="J50:J51"/>
     <mergeCell ref="J52:J53"/>
@@ -3140,17 +3097,14 @@
     <mergeCell ref="J60:J61"/>
     <mergeCell ref="J62:J63"/>
     <mergeCell ref="J64:J65"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="J68:J71"/>
+    <mergeCell ref="J66:J69"/>
+    <mergeCell ref="J70:J71"/>
     <mergeCell ref="J72:J73"/>
     <mergeCell ref="J74:J75"/>
     <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="J83:J84"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="J81:J82"/>
     <mergeCell ref="K16:K17"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="K37:K38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="117">
   <si>
     <t>variable_id</t>
   </si>
@@ -58,6 +58,9 @@
     <t>CORDEX</t>
   </si>
   <si>
+    <t>CORDEX-CMIP6</t>
+  </si>
+  <si>
     <t>CMIP5</t>
   </si>
   <si>
@@ -76,18 +79,9 @@
     <t>EUR-12</t>
   </si>
   <si>
-    <t>CLMcom</t>
-  </si>
-  <si>
-    <t>CLMcom-ETH</t>
-  </si>
-  <si>
     <t>CNRM</t>
   </si>
   <si>
-    <t>DHMZ</t>
-  </si>
-  <si>
     <t>GERICS</t>
   </si>
   <si>
@@ -97,37 +91,34 @@
     <t>KNMI</t>
   </si>
   <si>
-    <t>MOHC</t>
-  </si>
-  <si>
     <t>MPI-CSC</t>
   </si>
   <si>
+    <t>SMHI</t>
+  </si>
+  <si>
+    <t>CLMcom-CMCC</t>
+  </si>
+  <si>
+    <t>CLMcom-Hereon</t>
+  </si>
+  <si>
+    <t>CLMcom-KUL</t>
+  </si>
+  <si>
+    <t>CNRM-MF</t>
+  </si>
+  <si>
+    <t>HCLIMcom-METNo</t>
+  </si>
+  <si>
+    <t>HCLIMcom-SMHI</t>
+  </si>
+  <si>
     <t>RMIB-UGent</t>
   </si>
   <si>
-    <t>SMHI</t>
-  </si>
-  <si>
-    <t>CLMcom-CMCC</t>
-  </si>
-  <si>
-    <t>CLMcom-Hereon</t>
-  </si>
-  <si>
-    <t>CLMcom-KUL</t>
-  </si>
-  <si>
-    <t>CNRM-MF</t>
-  </si>
-  <si>
-    <t>HCLIMcom-METNo</t>
-  </si>
-  <si>
-    <t>HCLIMcom-SMHI</t>
-  </si>
-  <si>
-    <t>ECMWF-ERAINT</t>
+    <t>ERAINT</t>
   </si>
   <si>
     <t>ERA5</t>
@@ -157,12 +148,12 @@
     <t>ssp370</t>
   </si>
   <si>
+    <t>r1i1p1</t>
+  </si>
+  <si>
     <t>r0i0p0</t>
   </si>
   <si>
-    <t>r1i1p1</t>
-  </si>
-  <si>
     <t>r1i1p1f1</t>
   </si>
   <si>
@@ -175,21 +166,12 @@
     <t>r3i1p1f1</t>
   </si>
   <si>
-    <t>CCLM4-8-17</t>
-  </si>
-  <si>
-    <t>COSMO-crCLIM-v1-1</t>
-  </si>
-  <si>
     <t>ALADIN53</t>
   </si>
   <si>
     <t>ALADIN63</t>
   </si>
   <si>
-    <t>RegCM4-2</t>
-  </si>
-  <si>
     <t>REMO2015</t>
   </si>
   <si>
@@ -199,15 +181,9 @@
     <t>RACMO22E</t>
   </si>
   <si>
-    <t>HadREM3-GA7-05</t>
-  </si>
-  <si>
     <t>REMO2009</t>
   </si>
   <si>
-    <t>ALARO-0</t>
-  </si>
-  <si>
     <t>RCA4</t>
   </si>
   <si>
@@ -256,24 +232,12 @@
     <t>6hr</t>
   </si>
   <si>
-    <t>v20140515</t>
-  </si>
-  <si>
-    <t>v20191210</t>
-  </si>
-  <si>
     <t>v20150127</t>
   </si>
   <si>
     <t>v20191118</t>
   </si>
   <si>
-    <t>v20160112</t>
-  </si>
-  <si>
-    <t>v20150527</t>
-  </si>
-  <si>
     <t>v20180813</t>
   </si>
   <si>
@@ -286,21 +250,9 @@
     <t>v20140319</t>
   </si>
   <si>
-    <t>v20200706</t>
-  </si>
-  <si>
-    <t>v20200330</t>
-  </si>
-  <si>
     <t>v20160525</t>
   </si>
   <si>
-    <t>v20170523</t>
-  </si>
-  <si>
-    <t>v20170207</t>
-  </si>
-  <si>
     <t>v20131026</t>
   </si>
   <si>
@@ -337,16 +289,10 @@
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
-    <t>['pr', 'tas', 'tasmax', 'tasmin']</t>
-  </si>
-  <si>
     <t>['pr', 'psl']</t>
   </si>
   <si>
     <t>['tas', 'tasmax', 'tasmin']</t>
-  </si>
-  <si>
-    <t>['pr', 'tas']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
@@ -776,10 +722,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
@@ -837,40 +783,40 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="M2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -881,23 +827,17 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="M3" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -905,32 +845,24 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="M4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -941,23 +873,17 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="M5" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -969,28 +895,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M6" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1001,17 +927,23 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K7" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M7" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1019,24 +951,32 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="I8" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="M8" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1044,20 +984,32 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="M9" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1065,32 +1017,20 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="M10" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1104,14 +1044,12 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M11" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1120,31 +1058,31 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1156,22 +1094,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1180,31 +1118,31 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="M14" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1212,53 +1150,67 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="M15" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K16" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1272,12 +1224,14 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="L17" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M17" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1285,32 +1239,20 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1325,13 +1267,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1339,32 +1281,20 @@
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1372,26 +1302,32 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1399,32 +1335,20 @@
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="M22" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1432,20 +1356,32 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K23" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1453,32 +1389,20 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1489,62 +1413,38 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="M25" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1"/>
-      <c r="B26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
       <c r="K26" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="M26" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1552,20 +1452,32 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1575,18 +1487,26 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K28" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="M28" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1595,19 +1515,29 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K29" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="M29" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1622,13 +1552,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M30" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1636,32 +1566,20 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="M31" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1669,20 +1587,32 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K32" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="M32" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1690,32 +1620,20 @@
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="M33" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1730,13 +1648,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="M34" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1751,13 +1669,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="M35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1765,20 +1683,32 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K36" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1786,32 +1716,20 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L37" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1822,25 +1740,25 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="I38" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1849,29 +1767,19 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I39" s="1" t="s">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="L39" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1879,20 +1787,32 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1907,13 +1827,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1921,32 +1841,28 @@
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
       <c r="G42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="L42" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1961,13 +1877,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1976,19 +1892,29 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2003,13 +1929,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2017,32 +1943,26 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
       <c r="H46" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2057,13 +1977,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2073,26 +1993,24 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2107,13 +2025,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2121,32 +2039,28 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2161,13 +2075,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2177,26 +2091,24 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2211,13 +2123,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2226,29 +2138,25 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
       <c r="H54" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2263,13 +2171,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2278,25 +2186,29 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H56" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="L56" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2311,13 +2223,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2328,23 +2240,17 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2359,13 +2265,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2374,27 +2280,29 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="G60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="I60" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2409,13 +2317,13 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2425,24 +2333,26 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H62" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2457,13 +2367,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M63" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2472,25 +2382,29 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="H64" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M64" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2505,13 +2419,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M65" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2520,29 +2434,27 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M66" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2557,13 +2469,13 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="M67" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2571,20 +2483,32 @@
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="E68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K68" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="M68" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2599,13 +2523,13 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="M69" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2614,29 +2538,19 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="M70" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2644,20 +2558,32 @@
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="E71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K71" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="M71" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2667,444 +2593,161 @@
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="M72" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M73" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M74" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M75" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M76" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="M77" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M78" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M79" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="M80" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M81" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M82" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="162">
-    <mergeCell ref="A2:A82"/>
-    <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B82"/>
-    <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C82"/>
-    <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D82"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="E10:E11"/>
+  <mergeCells count="139">
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A16:A72"/>
+    <mergeCell ref="B2:B15"/>
+    <mergeCell ref="B16:B72"/>
+    <mergeCell ref="C2:C15"/>
+    <mergeCell ref="C16:C72"/>
+    <mergeCell ref="D2:D15"/>
+    <mergeCell ref="D16:D72"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E9:E11"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E50:E77"/>
-    <mergeCell ref="E78:E80"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="E40:E67"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F9:F11"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F26:F30"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F54:F65"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="F78:F80"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G6:G9"/>
-    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="F36:F39"/>
+    <mergeCell ref="F40:F43"/>
+    <mergeCell ref="F44:F55"/>
+    <mergeCell ref="F56:F59"/>
+    <mergeCell ref="F60:F63"/>
+    <mergeCell ref="F64:F67"/>
+    <mergeCell ref="F68:F70"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G9:G11"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G33:G36"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="G54:G59"/>
-    <mergeCell ref="G60:G65"/>
-    <mergeCell ref="G66:G69"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="G78:G80"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G26"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="G44:G49"/>
+    <mergeCell ref="G50:G55"/>
+    <mergeCell ref="G56:G59"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="G68:G70"/>
+    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H26"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="H32:H35"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H44:H45"/>
     <mergeCell ref="H46:H47"/>
     <mergeCell ref="H48:H49"/>
     <mergeCell ref="H50:H51"/>
     <mergeCell ref="H52:H53"/>
     <mergeCell ref="H54:H55"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H56:H59"/>
     <mergeCell ref="H60:H61"/>
     <mergeCell ref="H62:H63"/>
     <mergeCell ref="H64:H65"/>
-    <mergeCell ref="H66:H69"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I26:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I36"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="I42:I45"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="I16:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I26"/>
+    <mergeCell ref="I29:I31"/>
+    <mergeCell ref="I32:I35"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I44:I45"/>
     <mergeCell ref="I46:I47"/>
     <mergeCell ref="I48:I49"/>
     <mergeCell ref="I50:I51"/>
     <mergeCell ref="I52:I53"/>
     <mergeCell ref="I54:I55"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="I56:I59"/>
     <mergeCell ref="I60:I61"/>
     <mergeCell ref="I62:I63"/>
     <mergeCell ref="I64:I65"/>
-    <mergeCell ref="I66:I69"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="I76:I77"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J26:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J36"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="J42:J45"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="J16:J20"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J26"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="J44:J45"/>
     <mergeCell ref="J46:J47"/>
     <mergeCell ref="J48:J49"/>
     <mergeCell ref="J50:J51"/>
     <mergeCell ref="J52:J53"/>
     <mergeCell ref="J54:J55"/>
-    <mergeCell ref="J56:J57"/>
-    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="J56:J59"/>
     <mergeCell ref="J60:J61"/>
     <mergeCell ref="J62:J63"/>
     <mergeCell ref="J64:J65"/>
-    <mergeCell ref="J66:J69"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="J81:J82"/>
-    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="K10:K11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="120">
   <si>
     <t>variable_id</t>
   </si>
@@ -310,10 +310,19 @@
     <t>['clt', 'hfls', 'pr', 'psl', 'rlut', 'rlutcs', 'rsds', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500', 'snw']</t>
   </si>
   <si>
-    <t>['areacella', 'sftlaf', 'mrsofc', 'rootd', 'sftlf', 'sftgif', 'orog', 'sfturf']</t>
-  </si>
-  <si>
-    <t>['hurs', 'pr', 'prsn', 'ps', 'psl', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'mrro', 'mrros', 'snw', 'evspsbl']</t>
+    <t>['hurs', 'pr', 'prw', 'psl', 'rlut']</t>
+  </si>
+  <si>
+    <t>['hus1000', 'hus200', 'hus250', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds']</t>
+  </si>
+  <si>
+    <t>['orog']</t>
+  </si>
+  <si>
+    <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs']</t>
   </si>
   <si>
     <t>['pr']</t>
@@ -722,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1321,7 +1330,7 @@
         <v>66</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>81</v>
@@ -1342,7 +1351,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>81</v>
@@ -1356,29 +1365,17 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M23" t="s">
         <v>100</v>
@@ -1396,10 +1393,10 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M24" t="s">
         <v>101</v>
@@ -1417,13 +1414,13 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M25" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1431,20 +1428,32 @@
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K26" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>82</v>
       </c>
       <c r="M26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1452,24 +1461,12 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
         <v>69</v>
       </c>
@@ -1477,7 +1474,7 @@
         <v>82</v>
       </c>
       <c r="M27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1487,26 +1484,18 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>82</v>
       </c>
       <c r="M28" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1515,29 +1504,19 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1545,20 +1524,32 @@
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K30" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1568,18 +1559,26 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1587,9 +1586,7 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
         <v>35</v>
       </c>
@@ -1600,7 +1597,7 @@
         <v>46</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>66</v>
@@ -1609,10 +1606,10 @@
         <v>70</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1627,10 +1624,10 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M33" t="s">
         <v>106</v>
@@ -1648,10 +1645,10 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M34" t="s">
         <v>107</v>
@@ -1662,14 +1659,26 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K35" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>85</v>
@@ -1683,29 +1692,17 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M36" t="s">
         <v>109</v>
@@ -1723,10 +1720,10 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s">
         <v>110</v>
@@ -1739,26 +1736,18 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1766,20 +1755,32 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K39" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1787,32 +1788,20 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1822,18 +1811,26 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K41" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1843,26 +1840,18 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1870,20 +1859,32 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K43" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1892,29 +1893,19 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1924,18 +1915,26 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="G45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1946,23 +1945,17 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -1971,19 +1964,29 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K47" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -1994,23 +1997,17 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2021,17 +2018,23 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+      <c r="H49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K49" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2041,26 +2044,18 @@
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2071,17 +2066,23 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
+      <c r="H51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K51" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2092,23 +2093,17 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2118,18 +2113,26 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2140,23 +2143,17 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2167,17 +2164,23 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K55" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2186,29 +2189,19 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2219,9 +2212,15 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
+      <c r="H57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K57" s="1" t="s">
         <v>69</v>
       </c>
@@ -2229,7 +2228,7 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2244,13 +2243,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2259,19 +2258,29 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M59" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2280,21 +2289,11 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
         <v>69</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>86</v>
       </c>
       <c r="M60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2317,13 +2316,13 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M61" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2333,26 +2332,18 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M62" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2361,19 +2352,29 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K63" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M63" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2382,29 +2383,19 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M64" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2414,18 +2405,26 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K65" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M65" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2435,26 +2434,18 @@
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M66" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2463,19 +2454,29 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K67" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M67" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2483,32 +2484,20 @@
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2518,18 +2507,26 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K69" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2547,10 +2544,10 @@
         <v>68</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2559,7 +2556,7 @@
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>35</v>
@@ -2571,16 +2568,16 @@
         <v>46</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>66</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M71" t="s">
         <v>115</v>
@@ -2598,155 +2595,230 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M72" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M73" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M74" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M75" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="139">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A72"/>
+    <mergeCell ref="A16:A75"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B72"/>
+    <mergeCell ref="B16:B75"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C72"/>
+    <mergeCell ref="C16:C75"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D72"/>
+    <mergeCell ref="D16:D75"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="E16:E20"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="E36:E39"/>
-    <mergeCell ref="E40:E67"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="E30:E34"/>
+    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="E43:E70"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="E74:E75"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="F16:F20"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="F36:F39"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F55"/>
-    <mergeCell ref="F56:F59"/>
-    <mergeCell ref="F60:F63"/>
-    <mergeCell ref="F64:F67"/>
-    <mergeCell ref="F68:F70"/>
-    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="F35:F38"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="F47:F58"/>
+    <mergeCell ref="F59:F62"/>
+    <mergeCell ref="F63:F66"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="F71:F73"/>
+    <mergeCell ref="F74:F75"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G26"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="G44:G49"/>
-    <mergeCell ref="G50:G55"/>
-    <mergeCell ref="G56:G59"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="G68:G70"/>
-    <mergeCell ref="G71:G72"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="G35:G38"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G52"/>
+    <mergeCell ref="G53:G58"/>
+    <mergeCell ref="G59:G62"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="G74:G75"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H26"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="H32:H35"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="H56:H59"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="H35:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="H74:H75"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="I16:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I26"/>
-    <mergeCell ref="I29:I31"/>
-    <mergeCell ref="I32:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="I56:I59"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="I64:I65"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="I68:I70"/>
-    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I21:I25"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="I35:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="I74:I75"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="J16:J20"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J26"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="J32:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="J48:J49"/>
-    <mergeCell ref="J50:J51"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="J54:J55"/>
-    <mergeCell ref="J56:J59"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="J62:J63"/>
-    <mergeCell ref="J64:J65"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="J68:J70"/>
-    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="J21:J25"/>
+    <mergeCell ref="J26:J29"/>
+    <mergeCell ref="J32:J34"/>
+    <mergeCell ref="J35:J38"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="J59:J62"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="J67:J68"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="J74:J75"/>
     <mergeCell ref="K10:K11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -310,19 +310,19 @@
     <t>['clt', 'hfls', 'pr', 'psl', 'rlut', 'rlutcs', 'rsds', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500', 'snw']</t>
   </si>
   <si>
-    <t>['hurs', 'pr', 'prw', 'psl', 'rlut']</t>
-  </si>
-  <si>
-    <t>['hus1000', 'hus200', 'hus250', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds']</t>
-  </si>
-  <si>
-    <t>['orog']</t>
-  </si>
-  <si>
-    <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs']</t>
+    <t>['hurs', 'pr', 'prw', 'psl', 'rlut', 'sfcWind', 'tas']</t>
+  </si>
+  <si>
+    <t>['hus1000', 'hus200', 'hus250', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta850', 'ua1000', 'ua200', 'ua250', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va1000', 'va200', 'va250', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zg500']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlaf', 'sftlf', 'sfturf']</t>
+  </si>
+  <si>
+    <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['pr']</t>
@@ -743,7 +743,7 @@
     <col min="7" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="285.7109375" customWidth="1"/>
+    <col min="13" max="13" width="303.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="126">
   <si>
     <t>variable_id</t>
   </si>
@@ -115,6 +115,9 @@
     <t>HCLIMcom-SMHI</t>
   </si>
   <si>
+    <t>ICTP</t>
+  </si>
+  <si>
     <t>RMIB-UGent</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
     <t>HCLIM43-ALADIN</t>
   </si>
   <si>
+    <t>RegCM5-0</t>
+  </si>
+  <si>
     <t>RACMO23E</t>
   </si>
   <si>
@@ -262,6 +268,9 @@
     <t>v20240920</t>
   </si>
   <si>
+    <t>v20250409</t>
+  </si>
+  <si>
     <t>v20250328</t>
   </si>
   <si>
@@ -277,6 +286,9 @@
     <t>v20241205</t>
   </si>
   <si>
+    <t>v20250415</t>
+  </si>
+  <si>
     <t>v20241216</t>
   </si>
   <si>
@@ -325,15 +337,15 @@
     <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
+  </si>
+  <si>
     <t>['pr']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas']</t>
-  </si>
-  <si>
-    <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
-  </si>
-  <si>
     <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
   </si>
   <si>
@@ -361,10 +373,16 @@
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'rlds', 'rsds', 'uas', 'vas', 'sfcWind']</t>
   </si>
   <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'sfcWind', 'sfcWindmax', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
+    <t>['areacella', 'orog', 'sftlf']</t>
+  </si>
+  <si>
+    <t>['pr', 'tas', 'clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
     <t>['pr', 'tas', 'zg500']</t>
-  </si>
-  <si>
-    <t>['areacella', 'orog', 'sftlf']</t>
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'sfcWind']</t>
@@ -731,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -804,28 +822,28 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -840,13 +858,13 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -859,19 +877,19 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -886,13 +904,13 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -904,28 +922,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -937,22 +955,22 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -964,28 +982,28 @@
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -997,28 +1015,28 @@
         <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1033,13 +1051,13 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1055,10 +1073,10 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1070,28 +1088,28 @@
         <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1103,22 +1121,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1130,28 +1148,28 @@
         <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1163,22 +1181,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1198,28 +1216,28 @@
         <v>27</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1234,13 +1252,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1255,13 +1273,13 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M18" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1276,13 +1294,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1297,13 +1315,13 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1315,28 +1333,28 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1351,13 +1369,13 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1372,13 +1390,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M23" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1393,13 +1411,13 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1414,13 +1432,13 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1432,28 +1450,28 @@
         <v>29</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1471,10 +1489,10 @@
         <v>69</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M27" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1489,13 +1507,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M28" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1503,20 +1521,32 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K29" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1524,32 +1554,28 @@
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M30" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1558,27 +1584,29 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>47</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1587,29 +1615,19 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M32" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1624,13 +1642,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M33" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1638,20 +1656,32 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K34" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1659,32 +1689,20 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M35" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1702,10 +1720,10 @@
         <v>69</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1720,13 +1738,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M37" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1734,20 +1752,32 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K38" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M38" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1755,32 +1785,20 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M39" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1795,13 +1813,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M40" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1812,25 +1830,25 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M41" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1845,13 +1863,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M42" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1863,28 +1881,28 @@
         <v>32</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M43" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1899,13 +1917,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M44" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1915,26 +1933,18 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M45" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1944,18 +1954,26 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M46" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -1964,29 +1982,19 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M47" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -1995,19 +2003,29 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K48" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M48" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2018,23 +2036,17 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M49" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2049,13 +2061,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M50" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2070,19 +2082,19 @@
         <v>49</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M51" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2097,13 +2109,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M52" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2113,26 +2125,18 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M53" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2143,17 +2147,23 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="H54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K54" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M54" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2164,23 +2174,17 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M55" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2195,13 +2199,13 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M56" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2211,24 +2215,26 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H57" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M57" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2243,13 +2249,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M58" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2258,29 +2264,25 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M59" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2295,13 +2297,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M60" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2312,17 +2314,23 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
+      <c r="H61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K61" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M61" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2337,13 +2345,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M62" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2353,28 +2361,28 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M63" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2389,13 +2397,13 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2405,26 +2413,18 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M65" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2439,13 +2439,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M66" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2458,25 +2458,25 @@
         <v>40</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M67" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2491,13 +2491,13 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M68" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2507,26 +2507,18 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M69" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2536,18 +2528,26 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="G70" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M70" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2555,32 +2555,20 @@
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M71" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2589,16 +2577,26 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K72" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M72" t="s">
         <v>116</v>
@@ -2616,13 +2614,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M73" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2630,32 +2628,20 @@
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
-      <c r="E74" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2665,30 +2651,263 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K75" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M75" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M75" t="s">
+      <c r="K77" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M77" t="s">
         <v>119</v>
       </c>
     </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M79" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M81" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M83" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M84" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="139">
+  <mergeCells count="145">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A75"/>
+    <mergeCell ref="A16:A84"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B75"/>
+    <mergeCell ref="B16:B84"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C75"/>
+    <mergeCell ref="C16:C84"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D75"/>
+    <mergeCell ref="D16:D84"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
@@ -2696,13 +2915,14 @@
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="E16:E20"/>
     <mergeCell ref="E21:E25"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="E30:E34"/>
-    <mergeCell ref="E35:E38"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="E43:E70"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="E38:E42"/>
+    <mergeCell ref="E43:E76"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="E83:E84"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
@@ -2710,18 +2930,19 @@
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="F16:F20"/>
     <mergeCell ref="F21:F25"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="F35:F38"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="F47:F58"/>
-    <mergeCell ref="F59:F62"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F38:F42"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="F48:F62"/>
     <mergeCell ref="F63:F66"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="F71:F73"/>
-    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="F67:F71"/>
+    <mergeCell ref="F72:F76"/>
+    <mergeCell ref="F77:F79"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="F83:F84"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
@@ -2729,96 +2950,100 @@
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="G16:G20"/>
     <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G26:G29"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="G35:G38"/>
-    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="G38:G40"/>
     <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G47:G52"/>
-    <mergeCell ref="G53:G58"/>
-    <mergeCell ref="G59:G62"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="G43:G45"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G48:G56"/>
+    <mergeCell ref="G57:G62"/>
+    <mergeCell ref="G63:G66"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="G77:G79"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="G83:G84"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
     <mergeCell ref="H21:H25"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="H32:H34"/>
-    <mergeCell ref="H35:H38"/>
-    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="H38:H40"/>
     <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H43:H45"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H54:H56"/>
     <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H66"/>
+    <mergeCell ref="H67:H69"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="H83:H84"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="I16:I20"/>
     <mergeCell ref="I21:I25"/>
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="I35:I38"/>
-    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I26:I28"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="I38:I40"/>
     <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I43:I45"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I50"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="I54:I56"/>
     <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I66"/>
+    <mergeCell ref="I67:I69"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="I72:I74"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I77:I79"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="I83:I84"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="J16:J20"/>
     <mergeCell ref="J21:J25"/>
-    <mergeCell ref="J26:J29"/>
-    <mergeCell ref="J32:J34"/>
-    <mergeCell ref="J35:J38"/>
-    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="J38:J40"/>
     <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="J53:J54"/>
-    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="J43:J45"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="J48:J50"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="J54:J56"/>
     <mergeCell ref="J57:J58"/>
-    <mergeCell ref="J59:J62"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="J65:J66"/>
-    <mergeCell ref="J67:J68"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="J63:J66"/>
+    <mergeCell ref="J67:J69"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="J75:J76"/>
+    <mergeCell ref="J77:J79"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="J83:J84"/>
     <mergeCell ref="K10:K11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="129">
   <si>
     <t>variable_id</t>
   </si>
@@ -202,7 +202,10 @@
     <t>CNRM-ALADIN64E1</t>
   </si>
   <si>
-    <t>REMO2020</t>
+    <t>REMO2020-2-2</t>
+  </si>
+  <si>
+    <t>REMO2020-2-2-MR2</t>
   </si>
   <si>
     <t>HCLIM43-ALADIN</t>
@@ -289,6 +292,9 @@
     <t>v20250415</t>
   </si>
   <si>
+    <t>temp</t>
+  </si>
+  <si>
     <t>v20241216</t>
   </si>
   <si>
@@ -352,16 +358,10 @@
     <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
-    <t>['hurs', 'pr', 'prw', 'tas']</t>
-  </si>
-  <si>
-    <t>['pr', 'sfcWindmax', 'snc', 'snd', 'snw', 'tasmax']</t>
-  </si>
-  <si>
-    <t>['areacella', 'orog', 'sftlf', 'sftlaf']</t>
-  </si>
-  <si>
-    <t>['clt', 'rlds', 'rlut', 'rsds', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'pr', 'psl']</t>
+    <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlaf', 'sftlf']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
@@ -371,6 +371,15 @@
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'rlds', 'rsds', 'uas', 'vas', 'sfcWind']</t>
+  </si>
+  <si>
+    <t>['pr', 'hurs', 'prw', 'psl', 'rlut', 'sfcWind', 'tas']</t>
+  </si>
+  <si>
+    <t>['va400']</t>
+  </si>
+  <si>
+    <t>['hus1000', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta850', 'ua1000', 'ua200', 'ua250', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va1000', 'va200', 'va250', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zg500']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'sfcWind', 'sfcWindmax', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
@@ -749,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -834,16 +843,16 @@
         <v>51</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -858,13 +867,13 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -880,16 +889,16 @@
         <v>52</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -904,13 +913,13 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -934,16 +943,16 @@
         <v>53</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -961,16 +970,16 @@
         <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -994,16 +1003,16 @@
         <v>54</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1027,16 +1036,16 @@
         <v>55</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1051,13 +1060,13 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1073,10 +1082,10 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1100,16 +1109,16 @@
         <v>56</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1127,16 +1136,16 @@
         <v>56</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1160,16 +1169,16 @@
         <v>57</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1187,16 +1196,16 @@
         <v>57</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1228,16 +1237,16 @@
         <v>58</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1252,13 +1261,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1273,13 +1282,13 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1294,13 +1303,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1315,13 +1324,13 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1345,16 +1354,16 @@
         <v>59</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1369,13 +1378,13 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1390,13 +1399,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1411,13 +1420,13 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1432,13 +1441,13 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1462,16 +1471,16 @@
         <v>60</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1486,13 +1495,13 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1507,13 +1516,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1537,16 +1546,16 @@
         <v>61</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1566,16 +1575,16 @@
         <v>61</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1597,16 +1606,16 @@
         <v>61</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1621,13 +1630,13 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1642,13 +1651,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1672,16 +1681,16 @@
         <v>62</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1699,10 +1708,10 @@
         <v>71</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1714,16 +1723,20 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K36" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1738,13 +1751,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1765,16 +1778,16 @@
         <v>47</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M38" t="s">
         <v>116</v>
@@ -1792,13 +1805,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M39" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1813,10 +1826,10 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M40" t="s">
         <v>117</v>
@@ -1836,16 +1849,16 @@
         <v>47</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M41" t="s">
         <v>116</v>
@@ -1863,10 +1876,10 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M42" t="s">
         <v>117</v>
@@ -1890,16 +1903,16 @@
         <v>48</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M43" t="s">
         <v>116</v>
@@ -1917,13 +1930,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1938,10 +1951,10 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M45" t="s">
         <v>117</v>
@@ -1961,16 +1974,16 @@
         <v>48</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M46" t="s">
         <v>116</v>
@@ -1988,10 +2001,10 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M47" t="s">
         <v>117</v>
@@ -2013,16 +2026,16 @@
         <v>47</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M48" t="s">
         <v>116</v>
@@ -2040,13 +2053,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M49" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2061,10 +2074,10 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M50" t="s">
         <v>117</v>
@@ -2082,16 +2095,16 @@
         <v>49</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M51" t="s">
         <v>116</v>
@@ -2109,13 +2122,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M52" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2130,10 +2143,10 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M53" t="s">
         <v>117</v>
@@ -2151,16 +2164,16 @@
         <v>50</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M54" t="s">
         <v>116</v>
@@ -2178,13 +2191,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2199,10 +2212,10 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M56" t="s">
         <v>117</v>
@@ -2222,16 +2235,16 @@
         <v>47</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M57" t="s">
         <v>116</v>
@@ -2249,10 +2262,10 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M58" t="s">
         <v>117</v>
@@ -2270,16 +2283,16 @@
         <v>49</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M59" t="s">
         <v>116</v>
@@ -2297,10 +2310,10 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M60" t="s">
         <v>117</v>
@@ -2318,16 +2331,16 @@
         <v>50</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M61" t="s">
         <v>116</v>
@@ -2345,10 +2358,10 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M62" t="s">
         <v>117</v>
@@ -2370,19 +2383,19 @@
         <v>47</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M63" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2397,10 +2410,10 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M64" t="s">
         <v>116</v>
@@ -2418,13 +2431,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2439,10 +2452,10 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M66" t="s">
         <v>118</v>
@@ -2464,16 +2477,16 @@
         <v>47</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M67" t="s">
         <v>116</v>
@@ -2491,13 +2504,13 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M68" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2512,10 +2525,10 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M69" t="s">
         <v>117</v>
@@ -2535,16 +2548,16 @@
         <v>47</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M70" t="s">
         <v>116</v>
@@ -2562,10 +2575,10 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M71" t="s">
         <v>117</v>
@@ -2587,16 +2600,16 @@
         <v>47</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M72" t="s">
         <v>116</v>
@@ -2614,13 +2627,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M73" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2635,10 +2648,10 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M74" t="s">
         <v>117</v>
@@ -2658,16 +2671,16 @@
         <v>47</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M75" t="s">
         <v>116</v>
@@ -2685,10 +2698,10 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M76" t="s">
         <v>117</v>
@@ -2712,16 +2725,16 @@
         <v>47</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M77" t="s">
         <v>119</v>
@@ -2739,10 +2752,10 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M78" t="s">
         <v>120</v>
@@ -2759,11 +2772,9 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
-      <c r="K79" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M79" t="s">
         <v>121</v>
@@ -2774,26 +2785,14 @@
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
-      <c r="E80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>91</v>
@@ -2814,13 +2813,13 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M81" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2835,13 +2834,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2850,7 +2849,7 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>36</v>
@@ -2865,16 +2864,16 @@
         <v>66</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M83" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2892,22 +2891,97 @@
         <v>70</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M84" t="s">
-        <v>125</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M85" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M86" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M87" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="145">
+  <mergeCells count="148">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A84"/>
+    <mergeCell ref="A16:A87"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B84"/>
+    <mergeCell ref="B16:B87"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C84"/>
+    <mergeCell ref="C16:C87"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D84"/>
+    <mergeCell ref="D16:D87"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
@@ -2920,9 +2994,9 @@
     <mergeCell ref="E34:E37"/>
     <mergeCell ref="E38:E42"/>
     <mergeCell ref="E43:E76"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="E77:E82"/>
+    <mergeCell ref="E83:E85"/>
+    <mergeCell ref="E86:E87"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
@@ -2940,9 +3014,9 @@
     <mergeCell ref="F63:F66"/>
     <mergeCell ref="F67:F71"/>
     <mergeCell ref="F72:F76"/>
-    <mergeCell ref="F77:F79"/>
-    <mergeCell ref="F80:F82"/>
-    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="F77:F82"/>
+    <mergeCell ref="F83:F85"/>
+    <mergeCell ref="F86:F87"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
@@ -2964,9 +3038,9 @@
     <mergeCell ref="G70:G71"/>
     <mergeCell ref="G72:G74"/>
     <mergeCell ref="G75:G76"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="G77:G82"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="G86:G87"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
@@ -2989,9 +3063,9 @@
     <mergeCell ref="H70:H71"/>
     <mergeCell ref="H72:H74"/>
     <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H77:H79"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H77:H82"/>
+    <mergeCell ref="H83:H85"/>
+    <mergeCell ref="H86:H87"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
@@ -2999,7 +3073,8 @@
     <mergeCell ref="I21:I25"/>
     <mergeCell ref="I26:I28"/>
     <mergeCell ref="I31:I33"/>
-    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I37"/>
     <mergeCell ref="I38:I40"/>
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="I43:I45"/>
@@ -3015,9 +3090,9 @@
     <mergeCell ref="I70:I71"/>
     <mergeCell ref="I72:I74"/>
     <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I77:I79"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I77:I82"/>
+    <mergeCell ref="I83:I85"/>
+    <mergeCell ref="I86:I87"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
@@ -3025,7 +3100,8 @@
     <mergeCell ref="J21:J25"/>
     <mergeCell ref="J26:J28"/>
     <mergeCell ref="J31:J33"/>
-    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="J36:J37"/>
     <mergeCell ref="J38:J40"/>
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="J43:J45"/>
@@ -3041,10 +3117,11 @@
     <mergeCell ref="J70:J71"/>
     <mergeCell ref="J72:J74"/>
     <mergeCell ref="J75:J76"/>
-    <mergeCell ref="J77:J79"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="J83:J84"/>
+    <mergeCell ref="J77:J82"/>
+    <mergeCell ref="J83:J85"/>
+    <mergeCell ref="J86:J87"/>
     <mergeCell ref="K10:K11"/>
+    <mergeCell ref="K78:K79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="129">
   <si>
     <t>variable_id</t>
   </si>
@@ -343,7 +343,7 @@
     <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds']</t>
   </si>
   <si>
     <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
@@ -758,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1488,20 +1488,32 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1511,18 +1523,26 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1530,17 +1550,15 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>61</v>
@@ -1549,13 +1567,13 @@
         <v>69</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1565,26 +1583,18 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1593,29 +1603,19 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1623,20 +1623,32 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K32" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M32" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1654,10 +1666,10 @@
         <v>71</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1665,20 +1677,12 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>69</v>
@@ -1690,7 +1694,7 @@
         <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1719,24 +1723,32 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I36" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M36" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1751,13 +1763,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M37" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1765,32 +1777,20 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1800,18 +1800,26 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="G39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K39" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M39" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1840,13 +1848,17 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="G41" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>64</v>
@@ -1876,13 +1888,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M42" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1890,32 +1902,20 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1925,18 +1925,26 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="G44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M44" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1966,12 +1974,14 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="G46" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>64</v>
@@ -2001,13 +2011,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M47" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2016,29 +2026,19 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2049,17 +2049,23 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+      <c r="H49" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K49" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M49" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2074,13 +2080,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M50" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2091,23 +2097,17 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M51" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2118,17 +2118,23 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K52" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M52" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2143,13 +2149,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M53" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2160,23 +2166,17 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2186,18 +2186,26 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K55" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M55" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2228,11 +2236,9 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="G57" s="1"/>
       <c r="H57" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>64</v>
@@ -2280,7 +2286,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>64</v>
@@ -2325,10 +2331,14 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="H61" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>64</v>
@@ -2337,13 +2347,13 @@
         <v>69</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M61" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2358,13 +2368,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2373,29 +2383,19 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M63" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2410,13 +2410,13 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2425,19 +2425,29 @@
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K65" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M65" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2452,13 +2462,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M66" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2467,29 +2477,19 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M67" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2499,18 +2499,26 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K68" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M68" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2540,9 +2548,11 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G70" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>47</v>
@@ -2575,13 +2585,13 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M71" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2590,29 +2600,19 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M72" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2622,18 +2622,26 @@
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="G73" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K73" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M73" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2662,28 +2670,32 @@
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
+      <c r="E75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G75" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>47</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M75" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2698,13 +2710,13 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M76" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2712,32 +2724,18 @@
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
-      <c r="E77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M77" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2752,13 +2750,13 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M78" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2772,12 +2770,14 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
+      <c r="K79" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="L79" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M79" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2792,13 +2792,13 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M80" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2806,20 +2806,32 @@
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="E81" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K81" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M81" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2834,13 +2846,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2848,32 +2860,20 @@
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
-      <c r="E83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>93</v>
       </c>
       <c r="M83" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2881,20 +2881,32 @@
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="E84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K84" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M84" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -2912,76 +2924,22 @@
         <v>71</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M85" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M86" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M87" t="s">
         <v>128</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="148">
+  <mergeCells count="142">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A87"/>
+    <mergeCell ref="A16:A85"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B87"/>
+    <mergeCell ref="B16:B85"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C87"/>
+    <mergeCell ref="C16:C85"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D87"/>
+    <mergeCell ref="D16:D85"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
@@ -2989,14 +2947,13 @@
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="E16:E20"/>
     <mergeCell ref="E21:E25"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="E38:E42"/>
-    <mergeCell ref="E43:E76"/>
-    <mergeCell ref="E77:E82"/>
-    <mergeCell ref="E83:E85"/>
-    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="E36:E40"/>
+    <mergeCell ref="E41:E74"/>
+    <mergeCell ref="E75:E80"/>
+    <mergeCell ref="E81:E83"/>
+    <mergeCell ref="E84:E85"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
@@ -3004,19 +2961,18 @@
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="F16:F20"/>
     <mergeCell ref="F21:F25"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F38:F42"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="F48:F62"/>
-    <mergeCell ref="F63:F66"/>
-    <mergeCell ref="F67:F71"/>
-    <mergeCell ref="F72:F76"/>
-    <mergeCell ref="F77:F82"/>
-    <mergeCell ref="F83:F85"/>
-    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="F36:F40"/>
+    <mergeCell ref="F41:F45"/>
+    <mergeCell ref="F46:F60"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="F65:F69"/>
+    <mergeCell ref="F70:F74"/>
+    <mergeCell ref="F75:F80"/>
+    <mergeCell ref="F81:F83"/>
+    <mergeCell ref="F84:F85"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
@@ -3024,104 +2980,100 @@
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="G16:G20"/>
     <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G43:G45"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="G48:G56"/>
-    <mergeCell ref="G57:G62"/>
-    <mergeCell ref="G63:G66"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="G72:G74"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="G77:G82"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G46:G54"/>
+    <mergeCell ref="G55:G60"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="G70:G72"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="G75:G80"/>
+    <mergeCell ref="G81:G83"/>
+    <mergeCell ref="G84:G85"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
     <mergeCell ref="H21:H25"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="H38:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H43:H45"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="H48:H50"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="H32:H35"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="H49:H51"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="H55:H56"/>
     <mergeCell ref="H57:H58"/>
     <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H66"/>
-    <mergeCell ref="H67:H69"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H77:H82"/>
-    <mergeCell ref="H83:H85"/>
-    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="H61:H64"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="H70:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H75:H80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="H84:H85"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="I16:I20"/>
     <mergeCell ref="I21:I25"/>
-    <mergeCell ref="I26:I28"/>
-    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="I29:I31"/>
+    <mergeCell ref="I32:I33"/>
     <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="I38:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I45"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I50"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="I46:I48"/>
+    <mergeCell ref="I49:I51"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="I55:I56"/>
     <mergeCell ref="I57:I58"/>
     <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I66"/>
-    <mergeCell ref="I67:I69"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="I72:I74"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I77:I82"/>
-    <mergeCell ref="I83:I85"/>
-    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="I61:I64"/>
+    <mergeCell ref="I65:I67"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I70:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I75:I80"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="I84:I85"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="J16:J20"/>
     <mergeCell ref="J21:J25"/>
-    <mergeCell ref="J26:J28"/>
-    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="J32:J33"/>
     <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="J38:J40"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J43:J45"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="J48:J50"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="J36:J38"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="J49:J51"/>
+    <mergeCell ref="J52:J54"/>
+    <mergeCell ref="J55:J56"/>
     <mergeCell ref="J57:J58"/>
     <mergeCell ref="J59:J60"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="J63:J66"/>
-    <mergeCell ref="J67:J69"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="J72:J74"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="J77:J82"/>
-    <mergeCell ref="J83:J85"/>
-    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="J65:J67"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="J70:J72"/>
+    <mergeCell ref="J73:J74"/>
+    <mergeCell ref="J75:J80"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="J84:J85"/>
     <mergeCell ref="K10:K11"/>
-    <mergeCell ref="K78:K79"/>
+    <mergeCell ref="K76:K77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -343,7 +343,7 @@
     <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds']</t>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
   </si>
   <si>
     <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="130">
   <si>
     <t>variable_id</t>
   </si>
@@ -151,6 +151,9 @@
     <t>ssp370</t>
   </si>
   <si>
+    <t>ssp126</t>
+  </si>
+  <si>
     <t>r1i1p1</t>
   </si>
   <si>
@@ -343,7 +346,7 @@
     <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
@@ -758,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -837,22 +840,22 @@
         <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -867,13 +870,13 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -886,19 +889,19 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -913,13 +916,13 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -937,22 +940,22 @@
         <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -964,22 +967,22 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -997,22 +1000,22 @@
         <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1030,22 +1033,22 @@
         <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1060,13 +1063,13 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1082,10 +1085,10 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1103,22 +1106,22 @@
         <v>42</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1130,22 +1133,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1163,22 +1166,22 @@
         <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1190,22 +1193,22 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1231,22 +1234,22 @@
         <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1261,13 +1264,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1282,13 +1285,13 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1303,13 +1306,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1324,13 +1327,13 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1348,22 +1351,22 @@
         <v>42</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1378,13 +1381,13 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1399,13 +1402,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1420,13 +1423,13 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1441,13 +1444,13 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1465,22 +1468,22 @@
         <v>42</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1488,32 +1491,20 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1523,18 +1514,10 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
         <v>72</v>
       </c>
@@ -1550,21 +1533,23 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>73</v>
@@ -1583,18 +1568,26 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K30" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1603,19 +1596,29 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K31" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1623,32 +1626,20 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>89</v>
       </c>
       <c r="M32" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1663,7 +1654,7 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>89</v>
@@ -1677,24 +1668,32 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I34" s="1" t="s">
         <v>63</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M34" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1709,13 +1708,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1723,26 +1722,18 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
         <v>64</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>90</v>
@@ -1763,13 +1754,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M37" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1777,17 +1768,29 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K38" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s">
         <v>117</v>
@@ -1800,26 +1803,18 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M39" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1834,13 +1829,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M40" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1848,32 +1843,28 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M41" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1883,18 +1874,26 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K42" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M42" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1912,10 +1911,10 @@
         <v>71</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M43" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1925,26 +1924,18 @@
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1952,17 +1943,29 @@
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K45" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M45" t="s">
         <v>117</v>
@@ -1974,29 +1977,19 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M46" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2011,13 +2004,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M47" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2027,18 +2020,26 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="G48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K48" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M48" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2048,24 +2049,26 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
+      <c r="G49" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2080,13 +2083,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2101,13 +2104,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M51" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2116,25 +2119,29 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H52" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M52" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2149,13 +2156,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2170,13 +2177,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2186,26 +2193,24 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="G55" s="1"/>
       <c r="H55" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2223,10 +2228,10 @@
         <v>71</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M56" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2237,23 +2242,17 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M57" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2264,14 +2263,20 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="H58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K58" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M58" t="s">
         <v>117</v>
@@ -2285,23 +2290,17 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M59" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2316,13 +2315,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M60" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2331,29 +2330,27 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M61" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2364,17 +2361,23 @@
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
+      <c r="H62" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K62" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M62" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2385,17 +2388,23 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="H63" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K63" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2405,18 +2414,26 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K64" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2425,29 +2442,19 @@
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M65" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2462,13 +2469,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M66" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2479,14 +2486,20 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="H67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K67" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M67" t="s">
         <v>117</v>
@@ -2499,26 +2512,18 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M68" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2533,13 +2538,13 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M69" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2548,29 +2553,25 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2585,13 +2586,13 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2606,13 +2607,13 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M72" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2621,27 +2622,29 @@
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G73" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M73" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2656,10 +2659,10 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M74" t="s">
         <v>117</v>
@@ -2670,32 +2673,20 @@
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M75" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2710,13 +2701,13 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2725,17 +2716,29 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="L77" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M77" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2750,13 +2753,13 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M78" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2771,13 +2774,13 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M79" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2787,10 +2790,18 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="G80" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K80" s="1" t="s">
         <v>71</v>
       </c>
@@ -2798,7 +2809,7 @@
         <v>91</v>
       </c>
       <c r="M80" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2806,32 +2817,28 @@
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M81" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2846,13 +2853,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M82" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2867,13 +2874,13 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M83" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2881,32 +2888,30 @@
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
-      <c r="E84" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M84" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -2924,22 +2929,408 @@
         <v>71</v>
       </c>
       <c r="L85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M85" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M86" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M87" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M88" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M89" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M90" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M91" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M92" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M93" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M94" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M95" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M96" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M85" t="s">
+      <c r="M97" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M98" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M99" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M100" t="s">
         <v>128</v>
       </c>
     </row>
+    <row r="101" spans="1:13">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M101" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="142">
+  <mergeCells count="149">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A85"/>
+    <mergeCell ref="A16:A101"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B85"/>
+    <mergeCell ref="B16:B101"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C85"/>
+    <mergeCell ref="C16:C101"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D85"/>
+    <mergeCell ref="D16:D101"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
@@ -2947,13 +3338,14 @@
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="E16:E20"/>
     <mergeCell ref="E21:E25"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="E36:E40"/>
-    <mergeCell ref="E41:E74"/>
-    <mergeCell ref="E75:E80"/>
-    <mergeCell ref="E81:E83"/>
-    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="E38:E44"/>
+    <mergeCell ref="E45:E90"/>
+    <mergeCell ref="E91:E96"/>
+    <mergeCell ref="E97:E99"/>
+    <mergeCell ref="E100:E101"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
@@ -2961,18 +3353,19 @@
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="F16:F20"/>
     <mergeCell ref="F21:F25"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="F36:F40"/>
-    <mergeCell ref="F41:F45"/>
-    <mergeCell ref="F46:F60"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="F65:F69"/>
-    <mergeCell ref="F70:F74"/>
-    <mergeCell ref="F75:F80"/>
-    <mergeCell ref="F81:F83"/>
-    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F38:F44"/>
+    <mergeCell ref="F45:F51"/>
+    <mergeCell ref="F52:F72"/>
+    <mergeCell ref="F73:F76"/>
+    <mergeCell ref="F77:F83"/>
+    <mergeCell ref="F84:F90"/>
+    <mergeCell ref="F91:F96"/>
+    <mergeCell ref="F97:F99"/>
+    <mergeCell ref="F100:F101"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
@@ -2980,100 +3373,105 @@
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="G16:G20"/>
     <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="G32:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G46:G54"/>
-    <mergeCell ref="G55:G60"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="G70:G72"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="G75:G80"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G49:G51"/>
+    <mergeCell ref="G52:G60"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="G64:G72"/>
+    <mergeCell ref="G73:G76"/>
+    <mergeCell ref="G77:G79"/>
     <mergeCell ref="G81:G83"/>
-    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G84:G86"/>
+    <mergeCell ref="G88:G90"/>
+    <mergeCell ref="G91:G96"/>
+    <mergeCell ref="G97:G99"/>
+    <mergeCell ref="G100:G101"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
     <mergeCell ref="H21:H25"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="H32:H35"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="H38:H40"/>
+    <mergeCell ref="H42:H44"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="H49:H51"/>
     <mergeCell ref="H52:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H64"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="H58:H60"/>
+    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="H67:H69"/>
     <mergeCell ref="H70:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H75:H80"/>
+    <mergeCell ref="H73:H76"/>
+    <mergeCell ref="H77:H79"/>
     <mergeCell ref="H81:H83"/>
-    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="H88:H90"/>
+    <mergeCell ref="H91:H96"/>
+    <mergeCell ref="H97:H99"/>
+    <mergeCell ref="H100:H101"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="I16:I20"/>
     <mergeCell ref="I21:I25"/>
-    <mergeCell ref="I29:I31"/>
-    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="I26:I28"/>
+    <mergeCell ref="I31:I33"/>
     <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="I46:I48"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="I38:I40"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="I45:I47"/>
     <mergeCell ref="I49:I51"/>
     <mergeCell ref="I52:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I64"/>
-    <mergeCell ref="I65:I67"/>
-    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="I58:I60"/>
+    <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I67:I69"/>
     <mergeCell ref="I70:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I75:I80"/>
+    <mergeCell ref="I73:I76"/>
+    <mergeCell ref="I77:I79"/>
     <mergeCell ref="I81:I83"/>
-    <mergeCell ref="I84:I85"/>
+    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="I91:I96"/>
+    <mergeCell ref="I97:I99"/>
+    <mergeCell ref="I100:I101"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="J16:J20"/>
     <mergeCell ref="J21:J25"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="J31:J33"/>
     <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J38"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="J38:J40"/>
+    <mergeCell ref="J42:J44"/>
+    <mergeCell ref="J45:J47"/>
     <mergeCell ref="J49:J51"/>
     <mergeCell ref="J52:J54"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="J61:J64"/>
-    <mergeCell ref="J65:J67"/>
-    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="J55:J57"/>
+    <mergeCell ref="J58:J60"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J67:J69"/>
     <mergeCell ref="J70:J72"/>
-    <mergeCell ref="J73:J74"/>
-    <mergeCell ref="J75:J80"/>
+    <mergeCell ref="J73:J76"/>
+    <mergeCell ref="J77:J79"/>
     <mergeCell ref="J81:J83"/>
-    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="J88:J90"/>
+    <mergeCell ref="J91:J96"/>
+    <mergeCell ref="J97:J99"/>
+    <mergeCell ref="J100:J101"/>
     <mergeCell ref="K10:K11"/>
-    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="K92:K93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="133">
   <si>
     <t>variable_id</t>
   </si>
@@ -283,6 +283,9 @@
     <t>v20250304</t>
   </si>
   <si>
+    <t>v20250428</t>
+  </si>
+  <si>
     <t>v20250116</t>
   </si>
   <si>
@@ -355,10 +358,16 @@
     <t>['pr']</t>
   </si>
   <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'zg500']</t>
+  </si>
+  <si>
     <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin', 'mrro', 'mrros', 'mrso', 'prsn', 'rldscs', 'rlutcs', 'rsdscs', 'rsutcs', 'snc', 'snd', 'snw', 'zg500']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
@@ -761,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -855,7 +864,7 @@
         <v>76</v>
       </c>
       <c r="M2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -876,7 +885,7 @@
         <v>76</v>
       </c>
       <c r="M3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -901,7 +910,7 @@
         <v>77</v>
       </c>
       <c r="M4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -922,7 +931,7 @@
         <v>77</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -955,7 +964,7 @@
         <v>78</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -982,7 +991,7 @@
         <v>78</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1015,7 +1024,7 @@
         <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1048,7 +1057,7 @@
         <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1069,7 +1078,7 @@
         <v>80</v>
       </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1088,7 +1097,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1121,7 +1130,7 @@
         <v>82</v>
       </c>
       <c r="M12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1148,7 +1157,7 @@
         <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1181,7 +1190,7 @@
         <v>83</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1208,7 +1217,7 @@
         <v>83</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1249,7 +1258,7 @@
         <v>84</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1270,7 +1279,7 @@
         <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1291,7 +1300,7 @@
         <v>84</v>
       </c>
       <c r="M18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1312,7 +1321,7 @@
         <v>84</v>
       </c>
       <c r="M19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1333,7 +1342,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1366,7 +1375,7 @@
         <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1387,7 +1396,7 @@
         <v>85</v>
       </c>
       <c r="M22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1408,7 +1417,7 @@
         <v>85</v>
       </c>
       <c r="M23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1429,7 +1438,7 @@
         <v>85</v>
       </c>
       <c r="M24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1450,7 +1459,7 @@
         <v>85</v>
       </c>
       <c r="M25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1483,7 +1492,7 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1504,7 +1513,7 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1525,7 +1534,7 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1558,7 +1567,7 @@
         <v>87</v>
       </c>
       <c r="M29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1587,7 +1596,7 @@
         <v>87</v>
       </c>
       <c r="M30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1618,7 +1627,7 @@
         <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1632,9 +1641,7 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
         <v>89</v>
       </c>
@@ -1654,7 +1661,7 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>89</v>
@@ -1668,24 +1675,12 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
         <v>71</v>
       </c>
@@ -1693,7 +1688,7 @@
         <v>90</v>
       </c>
       <c r="M34" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1707,11 +1702,9 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M35" t="s">
         <v>115</v>
@@ -1726,14 +1719,10 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>90</v>
@@ -1753,14 +1742,12 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1769,31 +1756,31 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M38" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1808,13 +1795,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M39" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1826,16 +1813,20 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="I40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1845,26 +1836,18 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>91</v>
       </c>
       <c r="M41" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1872,10 +1855,14 @@
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="G42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>48</v>
@@ -1890,10 +1877,10 @@
         <v>73</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1911,10 +1898,10 @@
         <v>71</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1932,10 +1919,10 @@
         <v>72</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1943,17 +1930,13 @@
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>65</v>
@@ -1962,13 +1945,13 @@
         <v>70</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M45" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1978,18 +1961,26 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M46" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2004,13 +1995,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M47" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2020,26 +2011,18 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M48" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2047,10 +2030,14 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="G49" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>49</v>
@@ -2065,10 +2052,10 @@
         <v>73</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M49" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2086,10 +2073,10 @@
         <v>71</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2107,10 +2094,10 @@
         <v>72</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M51" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2119,14 +2106,12 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="F52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>65</v>
@@ -2135,13 +2120,13 @@
         <v>70</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M52" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2151,18 +2136,26 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K53" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M53" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2177,13 +2170,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M54" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2194,23 +2187,17 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M55" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2219,19 +2206,29 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K56" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M56" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2246,13 +2243,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M57" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2263,23 +2260,17 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M58" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2290,17 +2281,23 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="H59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M59" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2315,13 +2312,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M60" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2331,26 +2328,18 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M61" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2362,7 +2351,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>65</v>
@@ -2371,13 +2360,13 @@
         <v>70</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M62" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2388,23 +2377,17 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M63" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2414,26 +2397,18 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M64" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2443,18 +2418,26 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K65" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M65" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2465,17 +2448,23 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
+      <c r="H66" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K66" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M66" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2487,7 +2476,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>65</v>
@@ -2496,13 +2485,13 @@
         <v>70</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M67" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2512,18 +2501,26 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K68" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M68" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2538,13 +2535,13 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M69" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2555,23 +2552,17 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M70" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2582,17 +2573,23 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="H71" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K71" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M71" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2607,13 +2604,13 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M72" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2622,29 +2619,19 @@
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M73" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2655,17 +2642,23 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="H74" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K74" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M74" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2683,10 +2676,10 @@
         <v>71</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M75" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2704,10 +2697,10 @@
         <v>72</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M76" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2717,10 +2710,10 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>48</v>
@@ -2732,13 +2725,13 @@
         <v>70</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M77" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2753,13 +2746,13 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M78" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2774,13 +2767,13 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M79" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2790,26 +2783,18 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M80" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2818,9 +2803,11 @@
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
+      <c r="F81" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G81" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>48</v>
@@ -2835,10 +2822,10 @@
         <v>73</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M81" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2856,10 +2843,10 @@
         <v>71</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M82" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2877,10 +2864,10 @@
         <v>72</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M83" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2889,11 +2876,9 @@
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>48</v>
@@ -2905,13 +2890,13 @@
         <v>70</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M84" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -2921,18 +2906,26 @@
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="G85" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K85" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M85" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -2947,13 +2940,13 @@
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M86" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -2963,26 +2956,18 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M87" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -2991,9 +2976,11 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G88" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>48</v>
@@ -3008,10 +2995,10 @@
         <v>73</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M88" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3029,10 +3016,10 @@
         <v>71</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M89" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3050,10 +3037,10 @@
         <v>72</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M90" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3061,32 +3048,28 @@
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
-      <c r="E91" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M91" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3096,18 +3079,26 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
+      <c r="G92" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K92" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M92" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3121,12 +3112,14 @@
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
+      <c r="K93" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="L93" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M93" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3141,13 +3134,13 @@
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M94" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3155,20 +3148,32 @@
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
+      <c r="E95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K95" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3183,13 +3188,13 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M96" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3197,32 +3202,18 @@
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
-      <c r="E97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
       <c r="L97" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M97" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3237,13 +3228,13 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M98" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3258,10 +3249,10 @@
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M99" t="s">
         <v>127</v>
@@ -3272,29 +3263,17 @@
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
-      <c r="E100" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M100" t="s">
         <v>128</v>
@@ -3305,14 +3284,26 @@
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
+      <c r="E101" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K101" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>95</v>
@@ -3321,16 +3312,112 @@
         <v>129</v>
       </c>
     </row>
+    <row r="102" spans="1:13">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M102" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M103" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M104" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M105" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="152">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A101"/>
+    <mergeCell ref="A16:A105"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B101"/>
+    <mergeCell ref="B16:B105"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C101"/>
+    <mergeCell ref="C16:C105"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D101"/>
+    <mergeCell ref="D16:D105"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
@@ -3339,13 +3426,13 @@
     <mergeCell ref="E16:E20"/>
     <mergeCell ref="E21:E25"/>
     <mergeCell ref="E26:E28"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="E38:E44"/>
-    <mergeCell ref="E45:E90"/>
-    <mergeCell ref="E91:E96"/>
-    <mergeCell ref="E97:E99"/>
-    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="E29:E37"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="E42:E48"/>
+    <mergeCell ref="E49:E94"/>
+    <mergeCell ref="E95:E100"/>
+    <mergeCell ref="E101:E103"/>
+    <mergeCell ref="E104:E105"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
@@ -3355,17 +3442,17 @@
     <mergeCell ref="F21:F25"/>
     <mergeCell ref="F26:F28"/>
     <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F38:F44"/>
-    <mergeCell ref="F45:F51"/>
-    <mergeCell ref="F52:F72"/>
-    <mergeCell ref="F73:F76"/>
-    <mergeCell ref="F77:F83"/>
-    <mergeCell ref="F84:F90"/>
-    <mergeCell ref="F91:F96"/>
-    <mergeCell ref="F97:F99"/>
-    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F42:F48"/>
+    <mergeCell ref="F49:F55"/>
+    <mergeCell ref="F56:F76"/>
+    <mergeCell ref="F77:F80"/>
+    <mergeCell ref="F81:F87"/>
+    <mergeCell ref="F88:F94"/>
+    <mergeCell ref="F95:F100"/>
+    <mergeCell ref="F101:F103"/>
+    <mergeCell ref="F104:F105"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
@@ -3374,104 +3461,107 @@
     <mergeCell ref="G16:G20"/>
     <mergeCell ref="G21:G25"/>
     <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="G38:G41"/>
     <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G46:G48"/>
     <mergeCell ref="G49:G51"/>
-    <mergeCell ref="G52:G60"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="G64:G72"/>
-    <mergeCell ref="G73:G76"/>
-    <mergeCell ref="G77:G79"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="G56:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="G68:G76"/>
+    <mergeCell ref="G77:G80"/>
     <mergeCell ref="G81:G83"/>
-    <mergeCell ref="G84:G86"/>
+    <mergeCell ref="G85:G87"/>
     <mergeCell ref="G88:G90"/>
-    <mergeCell ref="G91:G96"/>
-    <mergeCell ref="G97:G99"/>
-    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="G95:G100"/>
+    <mergeCell ref="G101:G103"/>
+    <mergeCell ref="G104:G105"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
     <mergeCell ref="H21:H25"/>
     <mergeCell ref="H26:H28"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="H38:H40"/>
+    <mergeCell ref="H31:H37"/>
+    <mergeCell ref="H38:H41"/>
     <mergeCell ref="H42:H44"/>
-    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="H46:H48"/>
     <mergeCell ref="H49:H51"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="H55:H57"/>
-    <mergeCell ref="H58:H60"/>
-    <mergeCell ref="H64:H66"/>
-    <mergeCell ref="H67:H69"/>
-    <mergeCell ref="H70:H72"/>
-    <mergeCell ref="H73:H76"/>
-    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="H77:H80"/>
     <mergeCell ref="H81:H83"/>
-    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="H85:H87"/>
     <mergeCell ref="H88:H90"/>
-    <mergeCell ref="H91:H96"/>
-    <mergeCell ref="H97:H99"/>
-    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="H92:H94"/>
+    <mergeCell ref="H95:H100"/>
+    <mergeCell ref="H101:H103"/>
+    <mergeCell ref="H104:H105"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="I16:I20"/>
     <mergeCell ref="I21:I25"/>
     <mergeCell ref="I26:I28"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="I38:I40"/>
+    <mergeCell ref="I31:I37"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
     <mergeCell ref="I42:I44"/>
-    <mergeCell ref="I45:I47"/>
+    <mergeCell ref="I46:I48"/>
     <mergeCell ref="I49:I51"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="I55:I57"/>
-    <mergeCell ref="I58:I60"/>
-    <mergeCell ref="I64:I66"/>
-    <mergeCell ref="I67:I69"/>
-    <mergeCell ref="I70:I72"/>
-    <mergeCell ref="I73:I76"/>
-    <mergeCell ref="I77:I79"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="I56:I58"/>
+    <mergeCell ref="I59:I61"/>
+    <mergeCell ref="I62:I64"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="I77:I80"/>
     <mergeCell ref="I81:I83"/>
-    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="I85:I87"/>
     <mergeCell ref="I88:I90"/>
-    <mergeCell ref="I91:I96"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="I100:I101"/>
+    <mergeCell ref="I92:I94"/>
+    <mergeCell ref="I95:I100"/>
+    <mergeCell ref="I101:I103"/>
+    <mergeCell ref="I104:I105"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="J16:J20"/>
     <mergeCell ref="J21:J25"/>
     <mergeCell ref="J26:J28"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="J38:J40"/>
+    <mergeCell ref="J31:J37"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J40:J41"/>
     <mergeCell ref="J42:J44"/>
-    <mergeCell ref="J45:J47"/>
+    <mergeCell ref="J46:J48"/>
     <mergeCell ref="J49:J51"/>
-    <mergeCell ref="J52:J54"/>
-    <mergeCell ref="J55:J57"/>
-    <mergeCell ref="J58:J60"/>
-    <mergeCell ref="J64:J66"/>
-    <mergeCell ref="J67:J69"/>
-    <mergeCell ref="J70:J72"/>
-    <mergeCell ref="J73:J76"/>
-    <mergeCell ref="J77:J79"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="J56:J58"/>
+    <mergeCell ref="J59:J61"/>
+    <mergeCell ref="J62:J64"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="J77:J80"/>
     <mergeCell ref="J81:J83"/>
-    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="J85:J87"/>
     <mergeCell ref="J88:J90"/>
-    <mergeCell ref="J91:J96"/>
-    <mergeCell ref="J97:J99"/>
-    <mergeCell ref="J100:J101"/>
+    <mergeCell ref="J92:J94"/>
+    <mergeCell ref="J95:J100"/>
+    <mergeCell ref="J101:J103"/>
+    <mergeCell ref="J104:J105"/>
     <mergeCell ref="K10:K11"/>
-    <mergeCell ref="K92:K93"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="K96:K97"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="132">
   <si>
     <t>variable_id</t>
   </si>
@@ -298,9 +298,6 @@
     <t>v20250415</t>
   </si>
   <si>
-    <t>temp</t>
-  </si>
-  <si>
     <t>v20241216</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
     <t>['pr']</t>
   </si>
   <si>
+    <t>['pr', 'rlut']</t>
+  </si>
+  <si>
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'zg500']</t>
   </si>
   <si>
@@ -386,9 +386,6 @@
   </si>
   <si>
     <t>['pr', 'hurs', 'prw', 'psl', 'rlut', 'sfcWind', 'tas']</t>
-  </si>
-  <si>
-    <t>['va400']</t>
   </si>
   <si>
     <t>['hus1000', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta850', 'ua1000', 'ua200', 'ua250', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va1000', 'va200', 'va250', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zg500']</t>
@@ -770,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -864,7 +861,7 @@
         <v>76</v>
       </c>
       <c r="M2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -885,7 +882,7 @@
         <v>76</v>
       </c>
       <c r="M3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -910,7 +907,7 @@
         <v>77</v>
       </c>
       <c r="M4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -931,7 +928,7 @@
         <v>77</v>
       </c>
       <c r="M5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -964,7 +961,7 @@
         <v>78</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -991,7 +988,7 @@
         <v>78</v>
       </c>
       <c r="M7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1024,7 +1021,7 @@
         <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1057,7 +1054,7 @@
         <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1078,7 +1075,7 @@
         <v>80</v>
       </c>
       <c r="M10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1097,7 +1094,7 @@
         <v>81</v>
       </c>
       <c r="M11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1130,7 +1127,7 @@
         <v>82</v>
       </c>
       <c r="M12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1157,7 +1154,7 @@
         <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1190,7 +1187,7 @@
         <v>83</v>
       </c>
       <c r="M14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1217,7 +1214,7 @@
         <v>83</v>
       </c>
       <c r="M15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1258,7 +1255,7 @@
         <v>84</v>
       </c>
       <c r="M16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1279,7 +1276,7 @@
         <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1300,7 +1297,7 @@
         <v>84</v>
       </c>
       <c r="M18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1321,7 +1318,7 @@
         <v>84</v>
       </c>
       <c r="M19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1342,7 +1339,7 @@
         <v>84</v>
       </c>
       <c r="M20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1375,7 +1372,7 @@
         <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1396,7 +1393,7 @@
         <v>85</v>
       </c>
       <c r="M22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1417,7 +1414,7 @@
         <v>85</v>
       </c>
       <c r="M23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1438,7 +1435,7 @@
         <v>85</v>
       </c>
       <c r="M24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1459,7 +1456,7 @@
         <v>85</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1492,7 +1489,7 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1513,7 +1510,7 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1534,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1567,7 +1564,7 @@
         <v>87</v>
       </c>
       <c r="M29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1577,26 +1574,18 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>87</v>
       </c>
       <c r="M30" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1605,14 +1594,12 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>62</v>
@@ -1621,13 +1608,13 @@
         <v>70</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1641,12 +1628,14 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="L32" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M32" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1655,19 +1644,29 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K33" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1681,14 +1680,12 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1702,12 +1699,14 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="L35" s="1" t="s">
         <v>89</v>
       </c>
       <c r="M35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1722,13 +1721,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>90</v>
       </c>
       <c r="M36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1747,7 +1746,7 @@
         <v>89</v>
       </c>
       <c r="M37" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1755,32 +1754,20 @@
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M38" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1794,14 +1781,12 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1809,12 +1794,20 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I40" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>70</v>
@@ -1826,7 +1819,7 @@
         <v>91</v>
       </c>
       <c r="M40" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1855,32 +1848,24 @@
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1895,13 +1880,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M43" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1909,20 +1894,32 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1932,18 +1929,10 @@
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
         <v>71</v>
       </c>
@@ -1951,7 +1940,7 @@
         <v>92</v>
       </c>
       <c r="M45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1961,26 +1950,18 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -1990,10 +1971,18 @@
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
+      <c r="G47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K47" s="1" t="s">
         <v>71</v>
       </c>
@@ -2001,7 +1990,7 @@
         <v>92</v>
       </c>
       <c r="M47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2011,18 +2000,26 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="G48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K48" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2030,32 +2027,20 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M49" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2070,13 +2055,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M50" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2084,20 +2069,32 @@
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K51" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2107,18 +2104,10 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
         <v>71</v>
       </c>
@@ -2126,7 +2115,7 @@
         <v>92</v>
       </c>
       <c r="M52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2136,26 +2125,18 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2165,10 +2146,18 @@
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K54" s="1" t="s">
         <v>71</v>
       </c>
@@ -2176,7 +2165,7 @@
         <v>92</v>
       </c>
       <c r="M54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2186,18 +2175,26 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K55" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2206,29 +2203,19 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M56" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2243,13 +2230,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M57" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2258,19 +2245,29 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K58" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M58" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2281,23 +2278,17 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M59" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2312,13 +2303,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M60" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2329,17 +2320,23 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
+      <c r="H61" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K61" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M61" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2350,23 +2347,17 @@
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M62" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2381,13 +2372,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M63" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2398,17 +2389,23 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="H64" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K64" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2418,18 +2415,10 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
         <v>71</v>
       </c>
@@ -2437,7 +2426,7 @@
         <v>92</v>
       </c>
       <c r="M65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2448,23 +2437,17 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
-      <c r="H66" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M66" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2474,9 +2457,11 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H67" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>65</v>
@@ -2491,7 +2476,7 @@
         <v>92</v>
       </c>
       <c r="M67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2501,11 +2486,9 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>65</v>
@@ -2514,13 +2497,13 @@
         <v>70</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M68" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2531,9 +2514,15 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="H69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K69" s="1" t="s">
         <v>71</v>
       </c>
@@ -2541,7 +2530,7 @@
         <v>92</v>
       </c>
       <c r="M69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2551,18 +2540,26 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="G70" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M70" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2573,23 +2570,17 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M71" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2604,13 +2595,13 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M72" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2621,17 +2612,23 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="H73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K73" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M73" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2642,23 +2639,17 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M74" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2673,13 +2664,13 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M75" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2690,17 +2681,23 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="H76" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K76" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2709,29 +2706,19 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M77" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2746,13 +2733,13 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2761,19 +2748,29 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="F79" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K79" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M79" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2788,13 +2785,13 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M80" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2803,29 +2800,19 @@
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M81" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2840,13 +2827,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M82" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2855,19 +2842,29 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K83" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M83" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2877,18 +2874,10 @@
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,7 +2885,7 @@
         <v>92</v>
       </c>
       <c r="M84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -2906,26 +2895,18 @@
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M85" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -2935,10 +2916,18 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
+      <c r="G86" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K86" s="1" t="s">
         <v>71</v>
       </c>
@@ -2946,7 +2935,7 @@
         <v>92</v>
       </c>
       <c r="M86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -2956,18 +2945,26 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
+      <c r="G87" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K87" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M87" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -2976,29 +2973,19 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M88" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3013,13 +3000,13 @@
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M89" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3028,19 +3015,29 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
+      <c r="F90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K90" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3050,18 +3047,10 @@
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
         <v>71</v>
       </c>
@@ -3069,7 +3058,7 @@
         <v>92</v>
       </c>
       <c r="M91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3079,26 +3068,18 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M92" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3108,10 +3089,18 @@
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
+      <c r="G93" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K93" s="1" t="s">
         <v>71</v>
       </c>
@@ -3119,7 +3108,7 @@
         <v>92</v>
       </c>
       <c r="M93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3129,18 +3118,26 @@
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
+      <c r="G94" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K94" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M94" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3148,32 +3145,20 @@
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
-      <c r="E95" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M95" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3188,13 +3173,13 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M96" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3202,18 +3187,32 @@
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
+      <c r="E97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="L97" s="1" t="s">
         <v>93</v>
       </c>
       <c r="M97" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3228,13 +3227,13 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>93</v>
       </c>
       <c r="M98" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3249,13 +3248,13 @@
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>93</v>
       </c>
       <c r="M99" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3270,13 +3269,13 @@
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>93</v>
       </c>
       <c r="M100" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3284,32 +3283,20 @@
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
-      <c r="E101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M101" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3317,20 +3304,32 @@
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
+      <c r="E102" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K102" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3345,13 +3344,13 @@
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M103" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3359,32 +3358,20 @@
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
-      <c r="E104" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M104" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3392,32 +3379,65 @@
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
+      <c r="E105" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="K105" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M105" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L105" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="M105" t="s">
-        <v>132</v>
+      <c r="L106" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M106" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="152">
+  <mergeCells count="159">
     <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A105"/>
+    <mergeCell ref="A16:A106"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B105"/>
+    <mergeCell ref="B16:B106"/>
     <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C105"/>
+    <mergeCell ref="C16:C106"/>
     <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D105"/>
+    <mergeCell ref="D16:D106"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E9:E11"/>
@@ -3426,13 +3446,13 @@
     <mergeCell ref="E16:E20"/>
     <mergeCell ref="E21:E25"/>
     <mergeCell ref="E26:E28"/>
-    <mergeCell ref="E29:E37"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="E42:E48"/>
-    <mergeCell ref="E49:E94"/>
-    <mergeCell ref="E95:E100"/>
-    <mergeCell ref="E101:E103"/>
-    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="E29:E39"/>
+    <mergeCell ref="E40:E43"/>
+    <mergeCell ref="E44:E50"/>
+    <mergeCell ref="E51:E96"/>
+    <mergeCell ref="E97:E101"/>
+    <mergeCell ref="E102:E104"/>
+    <mergeCell ref="E105:E106"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F9:F11"/>
@@ -3441,18 +3461,18 @@
     <mergeCell ref="F16:F20"/>
     <mergeCell ref="F21:F25"/>
     <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="F42:F48"/>
-    <mergeCell ref="F49:F55"/>
-    <mergeCell ref="F56:F76"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F81:F87"/>
-    <mergeCell ref="F88:F94"/>
-    <mergeCell ref="F95:F100"/>
-    <mergeCell ref="F101:F103"/>
-    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="F33:F39"/>
+    <mergeCell ref="F40:F43"/>
+    <mergeCell ref="F44:F50"/>
+    <mergeCell ref="F51:F57"/>
+    <mergeCell ref="F58:F78"/>
+    <mergeCell ref="F79:F82"/>
+    <mergeCell ref="F83:F89"/>
+    <mergeCell ref="F90:F96"/>
+    <mergeCell ref="F97:F101"/>
+    <mergeCell ref="F102:F104"/>
+    <mergeCell ref="F105:F106"/>
     <mergeCell ref="G2:G5"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="G9:G11"/>
@@ -3461,107 +3481,114 @@
     <mergeCell ref="G16:G20"/>
     <mergeCell ref="G21:G25"/>
     <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="G38:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="G56:G64"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="G68:G76"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="G85:G87"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="G95:G100"/>
-    <mergeCell ref="G101:G103"/>
-    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G33:G39"/>
+    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="G55:G57"/>
+    <mergeCell ref="G58:G66"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="G70:G78"/>
+    <mergeCell ref="G79:G82"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="G87:G89"/>
+    <mergeCell ref="G90:G92"/>
+    <mergeCell ref="G94:G96"/>
+    <mergeCell ref="G97:G101"/>
+    <mergeCell ref="G102:G104"/>
+    <mergeCell ref="G105:G106"/>
     <mergeCell ref="H2:H5"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="H16:H20"/>
     <mergeCell ref="H21:H25"/>
     <mergeCell ref="H26:H28"/>
-    <mergeCell ref="H31:H37"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="H46:H48"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="H53:H55"/>
-    <mergeCell ref="H56:H58"/>
-    <mergeCell ref="H59:H61"/>
-    <mergeCell ref="H62:H64"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="H77:H80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="H88:H90"/>
-    <mergeCell ref="H92:H94"/>
-    <mergeCell ref="H95:H100"/>
-    <mergeCell ref="H101:H103"/>
-    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H39"/>
+    <mergeCell ref="H40:H43"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="H58:H60"/>
+    <mergeCell ref="H61:H63"/>
+    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="H70:H72"/>
+    <mergeCell ref="H73:H75"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="H79:H82"/>
+    <mergeCell ref="H83:H85"/>
+    <mergeCell ref="H87:H89"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="H94:H96"/>
+    <mergeCell ref="H97:H101"/>
+    <mergeCell ref="H102:H104"/>
+    <mergeCell ref="H105:H106"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="I16:I20"/>
     <mergeCell ref="I21:I25"/>
     <mergeCell ref="I26:I28"/>
-    <mergeCell ref="I31:I37"/>
-    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I39"/>
     <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I44"/>
-    <mergeCell ref="I46:I48"/>
-    <mergeCell ref="I49:I51"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="I56:I58"/>
-    <mergeCell ref="I59:I61"/>
-    <mergeCell ref="I62:I64"/>
-    <mergeCell ref="I68:I70"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="I77:I80"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="I85:I87"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="I92:I94"/>
-    <mergeCell ref="I95:I100"/>
-    <mergeCell ref="I101:I103"/>
-    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="I48:I50"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="I58:I60"/>
+    <mergeCell ref="I61:I63"/>
+    <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I70:I72"/>
+    <mergeCell ref="I73:I75"/>
+    <mergeCell ref="I76:I78"/>
+    <mergeCell ref="I79:I82"/>
+    <mergeCell ref="I83:I85"/>
+    <mergeCell ref="I87:I89"/>
+    <mergeCell ref="I90:I92"/>
+    <mergeCell ref="I94:I96"/>
+    <mergeCell ref="I97:I101"/>
+    <mergeCell ref="I102:I104"/>
+    <mergeCell ref="I105:I106"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="J16:J20"/>
     <mergeCell ref="J21:J25"/>
     <mergeCell ref="J26:J28"/>
-    <mergeCell ref="J31:J37"/>
-    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J39"/>
     <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J42:J44"/>
-    <mergeCell ref="J46:J48"/>
-    <mergeCell ref="J49:J51"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="J56:J58"/>
-    <mergeCell ref="J59:J61"/>
-    <mergeCell ref="J62:J64"/>
-    <mergeCell ref="J68:J70"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="J77:J80"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="J85:J87"/>
-    <mergeCell ref="J88:J90"/>
-    <mergeCell ref="J92:J94"/>
-    <mergeCell ref="J95:J100"/>
-    <mergeCell ref="J101:J103"/>
-    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="J44:J46"/>
+    <mergeCell ref="J48:J50"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="J55:J57"/>
+    <mergeCell ref="J58:J60"/>
+    <mergeCell ref="J61:J63"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J70:J72"/>
+    <mergeCell ref="J73:J75"/>
+    <mergeCell ref="J76:J78"/>
+    <mergeCell ref="J79:J82"/>
+    <mergeCell ref="J83:J85"/>
+    <mergeCell ref="J87:J89"/>
+    <mergeCell ref="J90:J92"/>
+    <mergeCell ref="J94:J96"/>
+    <mergeCell ref="J97:J101"/>
+    <mergeCell ref="J102:J104"/>
+    <mergeCell ref="J105:J106"/>
     <mergeCell ref="K10:K11"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="K33:K34"/>
     <mergeCell ref="K36:K37"/>
-    <mergeCell ref="K96:K97"/>
+    <mergeCell ref="K38:K39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="151">
   <si>
     <t>variable_id</t>
   </si>
@@ -79,9 +79,18 @@
     <t>EUR-12</t>
   </si>
   <si>
+    <t>CLMcom</t>
+  </si>
+  <si>
+    <t>CLMcom-ETH</t>
+  </si>
+  <si>
     <t>CNRM</t>
   </si>
   <si>
+    <t>DHMZ</t>
+  </si>
+  <si>
     <t>GERICS</t>
   </si>
   <si>
@@ -91,9 +100,15 @@
     <t>KNMI</t>
   </si>
   <si>
+    <t>MOHC</t>
+  </si>
+  <si>
     <t>MPI-CSC</t>
   </si>
   <si>
+    <t>RMIB-UGent</t>
+  </si>
+  <si>
     <t>SMHI</t>
   </si>
   <si>
@@ -118,9 +133,6 @@
     <t>ICTP</t>
   </si>
   <si>
-    <t>RMIB-UGent</t>
-  </si>
-  <si>
     <t>ERAINT</t>
   </si>
   <si>
@@ -154,12 +166,12 @@
     <t>ssp126</t>
   </si>
   <si>
+    <t>r0i0p0</t>
+  </si>
+  <si>
     <t>r1i1p1</t>
   </si>
   <si>
-    <t>r0i0p0</t>
-  </si>
-  <si>
     <t>r1i1p1f1</t>
   </si>
   <si>
@@ -172,12 +184,21 @@
     <t>r3i1p1f1</t>
   </si>
   <si>
+    <t>CCLM4-8-17</t>
+  </si>
+  <si>
+    <t>COSMO-crCLIM-v1-1</t>
+  </si>
+  <si>
     <t>ALADIN53</t>
   </si>
   <si>
     <t>ALADIN63</t>
   </si>
   <si>
+    <t>RegCM4-2</t>
+  </si>
+  <si>
     <t>REMO2015</t>
   </si>
   <si>
@@ -187,9 +208,15 @@
     <t>RACMO22E</t>
   </si>
   <si>
+    <t>HadREM3-GA7-05</t>
+  </si>
+  <si>
     <t>REMO2009</t>
   </si>
   <si>
+    <t>ALARO-0</t>
+  </si>
+  <si>
     <t>RCA4</t>
   </si>
   <si>
@@ -244,12 +271,24 @@
     <t>6hr</t>
   </si>
   <si>
+    <t>v20140515</t>
+  </si>
+  <si>
+    <t>v20191210</t>
+  </si>
+  <si>
     <t>v20150127</t>
   </si>
   <si>
     <t>v20191118</t>
   </si>
   <si>
+    <t>v20160112</t>
+  </si>
+  <si>
+    <t>v20150527</t>
+  </si>
+  <si>
     <t>v20180813</t>
   </si>
   <si>
@@ -262,9 +301,21 @@
     <t>v20140319</t>
   </si>
   <si>
+    <t>v20200706</t>
+  </si>
+  <si>
+    <t>v20200330</t>
+  </si>
+  <si>
     <t>v20160525</t>
   </si>
   <si>
+    <t>v20170523</t>
+  </si>
+  <si>
+    <t>v20170207</t>
+  </si>
+  <si>
     <t>v20131026</t>
   </si>
   <si>
@@ -310,10 +361,16 @@
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin']</t>
   </si>
   <si>
+    <t>['pr', 'tas', 'tasmax', 'tasmin']</t>
+  </si>
+  <si>
     <t>['pr', 'psl']</t>
   </si>
   <si>
     <t>['tas', 'tasmax', 'tasmin']</t>
+  </si>
+  <si>
+    <t>['pr', 'tas']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
@@ -767,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -840,28 +897,28 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -872,17 +929,23 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -890,24 +953,32 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -918,17 +989,23 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -937,31 +1014,31 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -972,23 +1049,17 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -996,32 +1067,24 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1029,32 +1092,20 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="M9" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1062,20 +1113,32 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1089,12 +1152,14 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="L11" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1106,28 +1171,28 @@
         <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="M12" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1139,22 +1204,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="M13" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1166,28 +1231,28 @@
         <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1195,67 +1260,53 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1269,14 +1320,12 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M17" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1284,20 +1333,32 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K18" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1312,13 +1373,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="M19" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1326,20 +1387,32 @@
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K20" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="M20" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1347,32 +1420,26 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="M21" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1380,20 +1447,32 @@
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K22" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="M22" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1408,13 +1487,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="M23" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1422,20 +1501,32 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K24" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1446,50 +1537,64 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="H25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="K25" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E26" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M26" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1504,13 +1609,13 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1525,13 +1630,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1539,32 +1644,20 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="M29" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1579,13 +1672,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="M30" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1593,28 +1686,32 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G31" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="M31" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1629,13 +1726,13 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="M32" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1644,29 +1741,19 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="M33" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1680,12 +1767,14 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="L34" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="M34" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1700,13 +1789,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="M35" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1714,20 +1803,32 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K36" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="M36" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1741,12 +1842,14 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="L37" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="M37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1761,13 +1864,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="M38" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1775,18 +1878,32 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="L39" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="M39" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1794,32 +1911,20 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="M40" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1829,18 +1934,26 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K41" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="M41" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1852,20 +1965,16 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="M42" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1874,19 +1983,29 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K43" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -1894,32 +2013,18 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
       <c r="L44" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M44" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -1934,13 +2039,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M45" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -1955,13 +2060,13 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="M46" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -1971,26 +2076,16 @@
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
       <c r="L47" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M47" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2000,26 +2095,18 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="M48" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2033,14 +2120,12 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M49" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2048,20 +2133,32 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K50" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="M50" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2069,32 +2166,20 @@
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="M51" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2106,16 +2191,20 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
+      <c r="I52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K52" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2130,13 +2219,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="M53" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2144,28 +2233,32 @@
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="E54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G54" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M54" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2175,26 +2268,18 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M55" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2209,13 +2294,13 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M56" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2225,18 +2310,26 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K57" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M57" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2245,29 +2338,27 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M58" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2282,13 +2373,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M59" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2303,13 +2394,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M60" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2317,26 +2408,32 @@
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
+      <c r="E61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H61" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M61" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2351,13 +2448,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M62" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2372,13 +2469,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M63" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2388,24 +2485,26 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="H64" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2415,18 +2514,26 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K65" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M65" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2441,13 +2548,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M66" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2457,26 +2564,18 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M67" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2485,25 +2584,29 @@
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
+      <c r="F68" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H68" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M68" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2514,23 +2617,17 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M69" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2540,26 +2637,18 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M70" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2570,17 +2659,23 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="H71" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K71" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M71" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2595,13 +2690,13 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M72" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2612,23 +2707,17 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M73" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2639,17 +2728,23 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="H74" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K74" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M74" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2664,13 +2759,13 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M75" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2681,23 +2776,17 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-      <c r="H76" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2707,18 +2796,26 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="G77" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K77" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M77" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2729,17 +2826,23 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="H78" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K78" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M78" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2748,29 +2851,25 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
       <c r="H79" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M79" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2780,18 +2879,26 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="G80" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K80" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M80" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2806,13 +2913,13 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M81" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2827,13 +2934,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M82" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2842,29 +2949,25 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
       <c r="H83" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M83" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2879,13 +2982,13 @@
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M84" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -2900,13 +3003,13 @@
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M85" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -2916,26 +3019,24 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="G86" s="1"/>
       <c r="H86" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M86" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -2945,26 +3046,18 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M87" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -2979,13 +3072,13 @@
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M88" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -2994,19 +3087,29 @@
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K89" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M89" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3015,29 +3118,19 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M90" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3052,13 +3145,13 @@
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M91" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3073,13 +3166,13 @@
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M92" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3088,27 +3181,29 @@
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G93" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M93" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3118,26 +3213,18 @@
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M94" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3152,13 +3239,13 @@
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M95" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3168,18 +3255,26 @@
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
+      <c r="G96" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K96" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="M96" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3187,32 +3282,28 @@
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
-      <c r="E97" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
       <c r="G97" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="M97" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3227,13 +3318,13 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="M98" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3248,13 +3339,13 @@
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="M99" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3263,19 +3354,29 @@
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
+      <c r="F100" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K100" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="M100" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3290,13 +3391,13 @@
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="M101" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3304,32 +3405,20 @@
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
-      <c r="E102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
       <c r="K102" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="M102" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3339,18 +3428,26 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+      <c r="G103" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K103" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="M103" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3360,18 +3457,26 @@
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
+      <c r="G104" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K104" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="M104" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3379,32 +3484,20 @@
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
-      <c r="E105" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="M105" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3419,176 +3512,446 @@
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="M106" t="s">
-        <v>131</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M107" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M108" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M109" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M110" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M111" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M112" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M114" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M115" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M116" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="A16:A106"/>
-    <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B16:B106"/>
-    <mergeCell ref="C2:C15"/>
-    <mergeCell ref="C16:C106"/>
-    <mergeCell ref="D2:D15"/>
-    <mergeCell ref="D16:D106"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E9:E11"/>
+  <mergeCells count="183">
+    <mergeCell ref="A2:A25"/>
+    <mergeCell ref="A26:A116"/>
+    <mergeCell ref="B2:B25"/>
+    <mergeCell ref="B26:B116"/>
+    <mergeCell ref="C2:C25"/>
+    <mergeCell ref="C26:C116"/>
+    <mergeCell ref="D2:D25"/>
+    <mergeCell ref="D26:D116"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E16:E20"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="E29:E39"/>
-    <mergeCell ref="E40:E43"/>
-    <mergeCell ref="E44:E50"/>
-    <mergeCell ref="E51:E96"/>
-    <mergeCell ref="E97:E101"/>
-    <mergeCell ref="E102:E104"/>
-    <mergeCell ref="E105:E106"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E39:E49"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="E54:E60"/>
+    <mergeCell ref="E61:E106"/>
+    <mergeCell ref="E107:E111"/>
+    <mergeCell ref="E112:E114"/>
+    <mergeCell ref="E115:E116"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F10:F11"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F32"/>
-    <mergeCell ref="F33:F39"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F50"/>
-    <mergeCell ref="F51:F57"/>
-    <mergeCell ref="F58:F78"/>
-    <mergeCell ref="F79:F82"/>
-    <mergeCell ref="F83:F89"/>
-    <mergeCell ref="F90:F96"/>
-    <mergeCell ref="F97:F101"/>
-    <mergeCell ref="F102:F104"/>
-    <mergeCell ref="F105:F106"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F26:F30"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="F43:F49"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F54:F60"/>
+    <mergeCell ref="F61:F67"/>
+    <mergeCell ref="F68:F88"/>
+    <mergeCell ref="F89:F92"/>
+    <mergeCell ref="F93:F99"/>
+    <mergeCell ref="F100:F106"/>
+    <mergeCell ref="F107:F111"/>
+    <mergeCell ref="F112:F114"/>
+    <mergeCell ref="F115:F116"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G9"/>
+    <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G33:G39"/>
-    <mergeCell ref="G40:G43"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="G58:G66"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="G70:G78"/>
-    <mergeCell ref="G79:G82"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="G87:G89"/>
-    <mergeCell ref="G90:G92"/>
-    <mergeCell ref="G94:G96"/>
-    <mergeCell ref="G97:G101"/>
-    <mergeCell ref="G102:G104"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="H21:H25"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H39"/>
-    <mergeCell ref="H40:H43"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="H48:H50"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="H55:H57"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G43:G49"/>
+    <mergeCell ref="G50:G53"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="G68:G76"/>
+    <mergeCell ref="G77:G79"/>
+    <mergeCell ref="G80:G88"/>
+    <mergeCell ref="G89:G92"/>
+    <mergeCell ref="G93:G95"/>
+    <mergeCell ref="G97:G99"/>
+    <mergeCell ref="G100:G102"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="G107:G111"/>
+    <mergeCell ref="G112:G114"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="H31:H35"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H43:H49"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="H54:H56"/>
     <mergeCell ref="H58:H60"/>
     <mergeCell ref="H61:H63"/>
-    <mergeCell ref="H64:H66"/>
-    <mergeCell ref="H70:H72"/>
-    <mergeCell ref="H73:H75"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H79:H82"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="H80:H82"/>
     <mergeCell ref="H83:H85"/>
-    <mergeCell ref="H87:H89"/>
-    <mergeCell ref="H90:H92"/>
-    <mergeCell ref="H94:H96"/>
-    <mergeCell ref="H97:H101"/>
-    <mergeCell ref="H102:H104"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="I16:I20"/>
-    <mergeCell ref="I21:I25"/>
-    <mergeCell ref="I26:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="I48:I50"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="I55:I57"/>
+    <mergeCell ref="H86:H88"/>
+    <mergeCell ref="H89:H92"/>
+    <mergeCell ref="H93:H95"/>
+    <mergeCell ref="H97:H99"/>
+    <mergeCell ref="H100:H102"/>
+    <mergeCell ref="H104:H106"/>
+    <mergeCell ref="H107:H111"/>
+    <mergeCell ref="H112:H114"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="I26:I30"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I49"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="I54:I56"/>
     <mergeCell ref="I58:I60"/>
     <mergeCell ref="I61:I63"/>
-    <mergeCell ref="I64:I66"/>
-    <mergeCell ref="I70:I72"/>
-    <mergeCell ref="I73:I75"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="I79:I82"/>
+    <mergeCell ref="I65:I67"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="I80:I82"/>
     <mergeCell ref="I83:I85"/>
-    <mergeCell ref="I87:I89"/>
-    <mergeCell ref="I90:I92"/>
-    <mergeCell ref="I94:I96"/>
-    <mergeCell ref="I97:I101"/>
-    <mergeCell ref="I102:I104"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="J16:J20"/>
-    <mergeCell ref="J21:J25"/>
-    <mergeCell ref="J26:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J39"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="J44:J46"/>
-    <mergeCell ref="J48:J50"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="J55:J57"/>
+    <mergeCell ref="I86:I88"/>
+    <mergeCell ref="I89:I92"/>
+    <mergeCell ref="I93:I95"/>
+    <mergeCell ref="I97:I99"/>
+    <mergeCell ref="I100:I102"/>
+    <mergeCell ref="I104:I106"/>
+    <mergeCell ref="I107:I111"/>
+    <mergeCell ref="I112:I114"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="J26:J30"/>
+    <mergeCell ref="J31:J35"/>
+    <mergeCell ref="J36:J38"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J43:J49"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="J54:J56"/>
     <mergeCell ref="J58:J60"/>
     <mergeCell ref="J61:J63"/>
-    <mergeCell ref="J64:J66"/>
-    <mergeCell ref="J70:J72"/>
-    <mergeCell ref="J73:J75"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="J79:J82"/>
+    <mergeCell ref="J65:J67"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="J80:J82"/>
     <mergeCell ref="J83:J85"/>
-    <mergeCell ref="J87:J89"/>
-    <mergeCell ref="J90:J92"/>
-    <mergeCell ref="J94:J96"/>
-    <mergeCell ref="J97:J101"/>
-    <mergeCell ref="J102:J104"/>
-    <mergeCell ref="J105:J106"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="J86:J88"/>
+    <mergeCell ref="J89:J92"/>
+    <mergeCell ref="J93:J95"/>
+    <mergeCell ref="J97:J99"/>
+    <mergeCell ref="J100:J102"/>
+    <mergeCell ref="J104:J106"/>
+    <mergeCell ref="J107:J111"/>
+    <mergeCell ref="J112:J114"/>
+    <mergeCell ref="J115:J116"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="K48:K49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -457,7 +457,7 @@
     <t>['pr', 'tas', 'clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
   </si>
   <si>
-    <t>['pr', 'tas', 'zg500']</t>
+    <t>['pr', 'tas', 'zg500', 'clt', 'evspsbl', 'huss', 'psl', 'rlds', 'rsds', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'sfcWind']</t>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="149">
   <si>
     <t>variable_id</t>
   </si>
@@ -331,13 +331,7 @@
     <t>v20250328</t>
   </si>
   <si>
-    <t>v20250304</t>
-  </si>
-  <si>
-    <t>v20250428</t>
-  </si>
-  <si>
-    <t>v20250116</t>
+    <t>v20250505</t>
   </si>
   <si>
     <t>v20241120</t>
@@ -409,34 +403,34 @@
     <t>['tasmax', 'tasmin', 'tas', 'huss', 'pr', 'rlds', 'rsds', 'evspsbl', 'psl', 'clt', 'zg500']</t>
   </si>
   <si>
+    <t>['pr', 'rlut', 'tas', 'hurs', 'prw', 'psl']</t>
+  </si>
+  <si>
+    <t>['hus1000', 'hus925', 'hus850', 'hus700', 'hus600', 'hus500', 'hus400', 'hus300', 'hus250', 'hus200', 'ta850']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'zg500']</t>
+  </si>
+  <si>
+    <t>['orog', 'areacella', 'rootd', 'sftlf', 'mrsofc', 'sftgif', 'sftlaf']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin', 'mrro', 'mrros', 'mrso', 'prsn', 'rldscs', 'rlutcs', 'rsdscs', 'rsutcs', 'snc', 'snd', 'snw', 'zg500']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlaf', 'sftlf']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
+    <t>['sfcWind']</t>
+  </si>
+  <si>
     <t>['pr']</t>
-  </si>
-  <si>
-    <t>['pr', 'rlut']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'zg500']</t>
-  </si>
-  <si>
-    <t>['orog', 'areacella', 'rootd', 'sftlf']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin', 'mrro', 'mrros', 'mrso', 'prsn', 'rldscs', 'rlutcs', 'rsdscs', 'rsutcs', 'snc', 'snd', 'snw', 'zg500']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
-  </si>
-  <si>
-    <t>['orog', 'sftlaf', 'sftlf']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
-  </si>
-  <si>
-    <t>['sfcWind']</t>
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'rlds', 'rsds', 'uas', 'vas', 'sfcWind']</t>
@@ -824,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -918,7 +912,7 @@
         <v>85</v>
       </c>
       <c r="M2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -945,7 +939,7 @@
         <v>85</v>
       </c>
       <c r="M3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -978,7 +972,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1005,7 +999,7 @@
         <v>86</v>
       </c>
       <c r="M5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1038,7 +1032,7 @@
         <v>87</v>
       </c>
       <c r="M6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1059,7 +1053,7 @@
         <v>87</v>
       </c>
       <c r="M7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1084,7 +1078,7 @@
         <v>88</v>
       </c>
       <c r="M8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1105,7 +1099,7 @@
         <v>88</v>
       </c>
       <c r="M9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1138,7 +1132,7 @@
         <v>89</v>
       </c>
       <c r="M10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1159,7 +1153,7 @@
         <v>90</v>
       </c>
       <c r="M11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1192,7 +1186,7 @@
         <v>91</v>
       </c>
       <c r="M12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1219,7 +1213,7 @@
         <v>91</v>
       </c>
       <c r="M13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1252,7 +1246,7 @@
         <v>92</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1285,7 +1279,7 @@
         <v>93</v>
       </c>
       <c r="M15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1306,7 +1300,7 @@
         <v>93</v>
       </c>
       <c r="M16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1325,7 +1319,7 @@
         <v>94</v>
       </c>
       <c r="M17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1358,7 +1352,7 @@
         <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1379,7 +1373,7 @@
         <v>96</v>
       </c>
       <c r="M19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1412,7 +1406,7 @@
         <v>97</v>
       </c>
       <c r="M20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1439,7 +1433,7 @@
         <v>97</v>
       </c>
       <c r="M21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1472,7 +1466,7 @@
         <v>98</v>
       </c>
       <c r="M22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1493,7 +1487,7 @@
         <v>99</v>
       </c>
       <c r="M23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1526,7 +1520,7 @@
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1553,7 +1547,7 @@
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1594,7 +1588,7 @@
         <v>101</v>
       </c>
       <c r="M26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1615,7 +1609,7 @@
         <v>101</v>
       </c>
       <c r="M27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1636,7 +1630,7 @@
         <v>101</v>
       </c>
       <c r="M28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1657,7 +1651,7 @@
         <v>101</v>
       </c>
       <c r="M29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1678,7 +1672,7 @@
         <v>101</v>
       </c>
       <c r="M30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1711,7 +1705,7 @@
         <v>102</v>
       </c>
       <c r="M31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1732,7 +1726,7 @@
         <v>102</v>
       </c>
       <c r="M32" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1753,7 +1747,7 @@
         <v>102</v>
       </c>
       <c r="M33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1774,7 +1768,7 @@
         <v>102</v>
       </c>
       <c r="M34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1795,7 +1789,7 @@
         <v>102</v>
       </c>
       <c r="M35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1828,7 +1822,7 @@
         <v>103</v>
       </c>
       <c r="M36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1849,7 +1843,7 @@
         <v>103</v>
       </c>
       <c r="M37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1870,7 +1864,7 @@
         <v>103</v>
       </c>
       <c r="M38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1903,7 +1897,7 @@
         <v>104</v>
       </c>
       <c r="M39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1924,7 +1918,7 @@
         <v>104</v>
       </c>
       <c r="M40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1953,7 +1947,7 @@
         <v>104</v>
       </c>
       <c r="M41" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1974,7 +1968,7 @@
         <v>104</v>
       </c>
       <c r="M42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2005,7 +1999,7 @@
         <v>105</v>
       </c>
       <c r="M43" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2019,12 +2013,14 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="L44" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2042,10 +2038,10 @@
         <v>82</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M45" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2063,10 +2059,10 @@
         <v>80</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M46" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2080,12 +2076,14 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="L47" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2093,20 +2091,32 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K48" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M48" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2120,12 +2130,14 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+      <c r="K49" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="L49" s="1" t="s">
         <v>106</v>
       </c>
       <c r="M49" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2133,20 +2145,12 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>79</v>
@@ -2155,10 +2159,10 @@
         <v>80</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M50" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2176,10 +2180,10 @@
         <v>81</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M51" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2187,24 +2191,32 @@
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="I52" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>79</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2219,13 +2231,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M53" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2233,32 +2245,20 @@
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2268,18 +2268,26 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K55" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2289,18 +2297,26 @@
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
+      <c r="G56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K56" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M56" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2310,26 +2326,18 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2339,26 +2347,18 @@
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M58" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2366,20 +2366,32 @@
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="E59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M59" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2394,13 +2406,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M60" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2408,32 +2420,20 @@
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M61" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2443,18 +2443,26 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K62" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2464,18 +2472,26 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M63" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2485,26 +2501,18 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M64" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2514,26 +2522,18 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2542,19 +2542,29 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K66" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M66" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2569,13 +2579,13 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M67" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2584,29 +2594,19 @@
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M68" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2617,17 +2617,23 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="H69" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K69" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M69" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2642,13 +2648,13 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M70" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2659,23 +2665,17 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M71" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2686,17 +2686,23 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="H72" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K72" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M72" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2711,13 +2717,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M73" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2728,23 +2734,17 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M74" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2754,18 +2754,26 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K75" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M75" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2776,17 +2784,23 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="H76" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K76" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M76" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2796,11 +2810,9 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>74</v>
@@ -2812,10 +2824,10 @@
         <v>80</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M77" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2825,9 +2837,11 @@
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
+      <c r="G78" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H78" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>74</v>
@@ -2836,13 +2850,13 @@
         <v>79</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M78" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2853,23 +2867,17 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
-      <c r="H79" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M79" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2879,26 +2887,18 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M80" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2909,17 +2909,23 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="H81" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K81" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M81" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2934,13 +2940,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M82" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2951,23 +2957,17 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
-      <c r="H83" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M83" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2978,17 +2978,23 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="H84" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K84" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M84" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3003,13 +3009,13 @@
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M85" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3020,23 +3026,17 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
-      <c r="H86" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3045,19 +3045,29 @@
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K87" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M87" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3072,13 +3082,13 @@
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M88" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3087,29 +3097,19 @@
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M89" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3124,10 +3124,10 @@
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M90" t="s">
         <v>139</v>
@@ -3139,19 +3139,29 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K91" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M91" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3166,13 +3176,13 @@
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M92" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3181,29 +3191,19 @@
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M93" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3213,18 +3213,26 @@
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
+      <c r="G94" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K94" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M94" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3234,18 +3242,26 @@
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K95" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M95" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3255,26 +3271,18 @@
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M96" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3284,26 +3292,18 @@
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="G97" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M97" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3312,19 +3312,29 @@
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
+      <c r="F98" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K98" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M98" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3339,13 +3349,13 @@
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M99" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3354,29 +3364,19 @@
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3386,18 +3386,26 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
+      <c r="G101" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K101" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M101" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3407,18 +3415,26 @@
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
+      <c r="G102" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K102" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M102" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3428,26 +3444,18 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M103" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3457,26 +3465,18 @@
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
-      <c r="G104" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M104" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3484,20 +3484,32 @@
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
+      <c r="E105" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K105" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M105" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3512,13 +3524,13 @@
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M106" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3526,29 +3538,17 @@
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
-      <c r="E107" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M107" t="s">
         <v>142</v>
@@ -3566,10 +3566,10 @@
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M108" t="s">
         <v>143</v>
@@ -3587,10 +3587,10 @@
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M109" t="s">
         <v>144</v>
@@ -3601,17 +3601,29 @@
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
+      <c r="E110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K110" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M110" t="s">
         <v>145</v>
@@ -3629,13 +3641,13 @@
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M111" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3643,32 +3655,20 @@
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
-      <c r="E112" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M112" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3676,20 +3676,32 @@
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
+      <c r="E113" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K113" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M113" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3707,76 +3719,22 @@
         <v>81</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M114" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
-      <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M115" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
-      <c r="K116" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M116" t="s">
-        <v>150</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="183">
+  <mergeCells count="180">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A116"/>
+    <mergeCell ref="A26:A114"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B116"/>
+    <mergeCell ref="B26:B114"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C116"/>
+    <mergeCell ref="C26:C114"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D116"/>
+    <mergeCell ref="D26:D114"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -3790,13 +3748,13 @@
     <mergeCell ref="E26:E30"/>
     <mergeCell ref="E31:E35"/>
     <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E39:E49"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="E54:E60"/>
-    <mergeCell ref="E61:E106"/>
-    <mergeCell ref="E107:E111"/>
-    <mergeCell ref="E112:E114"/>
-    <mergeCell ref="E115:E116"/>
+    <mergeCell ref="E39:E47"/>
+    <mergeCell ref="E48:E51"/>
+    <mergeCell ref="E52:E58"/>
+    <mergeCell ref="E59:E104"/>
+    <mergeCell ref="E105:E109"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="E113:E114"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -3811,17 +3769,17 @@
     <mergeCell ref="F31:F35"/>
     <mergeCell ref="F36:F38"/>
     <mergeCell ref="F39:F42"/>
-    <mergeCell ref="F43:F49"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F54:F60"/>
-    <mergeCell ref="F61:F67"/>
-    <mergeCell ref="F68:F88"/>
-    <mergeCell ref="F89:F92"/>
-    <mergeCell ref="F93:F99"/>
-    <mergeCell ref="F100:F106"/>
-    <mergeCell ref="F107:F111"/>
-    <mergeCell ref="F112:F114"/>
-    <mergeCell ref="F115:F116"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="F48:F51"/>
+    <mergeCell ref="F52:F58"/>
+    <mergeCell ref="F59:F65"/>
+    <mergeCell ref="F66:F86"/>
+    <mergeCell ref="F87:F90"/>
+    <mergeCell ref="F91:F97"/>
+    <mergeCell ref="F98:F104"/>
+    <mergeCell ref="F105:F109"/>
+    <mergeCell ref="F110:F112"/>
+    <mergeCell ref="F113:F114"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -3837,23 +3795,23 @@
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="G39:G40"/>
     <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G43:G49"/>
-    <mergeCell ref="G50:G53"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="G58:G60"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="G68:G76"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="G80:G88"/>
-    <mergeCell ref="G89:G92"/>
-    <mergeCell ref="G93:G95"/>
-    <mergeCell ref="G97:G99"/>
-    <mergeCell ref="G100:G102"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="G107:G111"/>
-    <mergeCell ref="G112:G114"/>
-    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="G48:G51"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="G59:G61"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="G66:G74"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="G78:G86"/>
+    <mergeCell ref="G87:G90"/>
+    <mergeCell ref="G91:G93"/>
+    <mergeCell ref="G95:G97"/>
+    <mergeCell ref="G98:G100"/>
+    <mergeCell ref="G102:G104"/>
+    <mergeCell ref="G105:G109"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="G113:G114"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -3864,26 +3822,26 @@
     <mergeCell ref="H36:H38"/>
     <mergeCell ref="H39:H40"/>
     <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H43:H49"/>
-    <mergeCell ref="H50:H53"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="H58:H60"/>
-    <mergeCell ref="H61:H63"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="H83:H85"/>
-    <mergeCell ref="H86:H88"/>
-    <mergeCell ref="H89:H92"/>
-    <mergeCell ref="H93:H95"/>
-    <mergeCell ref="H97:H99"/>
-    <mergeCell ref="H100:H102"/>
-    <mergeCell ref="H104:H106"/>
-    <mergeCell ref="H107:H111"/>
-    <mergeCell ref="H112:H114"/>
-    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="H48:H51"/>
+    <mergeCell ref="H52:H54"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="H66:H68"/>
+    <mergeCell ref="H69:H71"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="H87:H90"/>
+    <mergeCell ref="H91:H93"/>
+    <mergeCell ref="H95:H97"/>
+    <mergeCell ref="H98:H100"/>
+    <mergeCell ref="H102:H104"/>
+    <mergeCell ref="H105:H109"/>
+    <mergeCell ref="H110:H112"/>
+    <mergeCell ref="H113:H114"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -3895,27 +3853,27 @@
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="I39:I40"/>
     <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I49"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="I48:I49"/>
     <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="I58:I60"/>
-    <mergeCell ref="I61:I63"/>
-    <mergeCell ref="I65:I67"/>
-    <mergeCell ref="I68:I70"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="I83:I85"/>
-    <mergeCell ref="I86:I88"/>
-    <mergeCell ref="I89:I92"/>
-    <mergeCell ref="I93:I95"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="I100:I102"/>
-    <mergeCell ref="I104:I106"/>
-    <mergeCell ref="I107:I111"/>
-    <mergeCell ref="I112:I114"/>
-    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="I52:I54"/>
+    <mergeCell ref="I56:I58"/>
+    <mergeCell ref="I59:I61"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="I66:I68"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="I72:I74"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="I87:I90"/>
+    <mergeCell ref="I91:I93"/>
+    <mergeCell ref="I95:I97"/>
+    <mergeCell ref="I98:I100"/>
+    <mergeCell ref="I102:I104"/>
+    <mergeCell ref="I105:I109"/>
+    <mergeCell ref="I110:I112"/>
+    <mergeCell ref="I113:I114"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -3927,31 +3885,28 @@
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J39:J40"/>
     <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J43:J49"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="J48:J49"/>
     <mergeCell ref="J50:J51"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="J58:J60"/>
-    <mergeCell ref="J61:J63"/>
-    <mergeCell ref="J65:J67"/>
-    <mergeCell ref="J68:J70"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="J83:J85"/>
-    <mergeCell ref="J86:J88"/>
-    <mergeCell ref="J89:J92"/>
-    <mergeCell ref="J93:J95"/>
-    <mergeCell ref="J97:J99"/>
-    <mergeCell ref="J100:J102"/>
-    <mergeCell ref="J104:J106"/>
-    <mergeCell ref="J107:J111"/>
-    <mergeCell ref="J112:J114"/>
-    <mergeCell ref="J115:J116"/>
+    <mergeCell ref="J52:J54"/>
+    <mergeCell ref="J56:J58"/>
+    <mergeCell ref="J59:J61"/>
+    <mergeCell ref="J63:J65"/>
+    <mergeCell ref="J66:J68"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="J87:J90"/>
+    <mergeCell ref="J91:J93"/>
+    <mergeCell ref="J95:J97"/>
+    <mergeCell ref="J98:J100"/>
+    <mergeCell ref="J102:J104"/>
+    <mergeCell ref="J105:J109"/>
+    <mergeCell ref="J110:J112"/>
+    <mergeCell ref="J113:J114"/>
     <mergeCell ref="K16:K17"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="K46:K47"/>
-    <mergeCell ref="K48:K49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="150">
   <si>
     <t>variable_id</t>
   </si>
@@ -449,6 +449,9 @@
   </si>
   <si>
     <t>['pr', 'tas', 'clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['pr', 'tas', 'zg500', 'clt', 'evspsbl', 'huss', 'psl', 'rlds', 'rsds', 'tasmax', 'tasmin', 'uas', 'vas']</t>
@@ -818,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3605,10 +3608,10 @@
         <v>27</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>52</v>
@@ -3636,18 +3639,26 @@
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
+      <c r="G111" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K111" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>109</v>
       </c>
       <c r="M111" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3657,18 +3668,26 @@
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
+      <c r="G112" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="K112" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>109</v>
       </c>
       <c r="M112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3676,9 +3695,7 @@
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="E113" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="E113" s="1"/>
       <c r="F113" s="1" t="s">
         <v>40</v>
       </c>
@@ -3689,19 +3706,19 @@
         <v>52</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>79</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M113" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3716,25 +3733,100 @@
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M114" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L114" s="1" t="s">
+      <c r="L115" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M115" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L116" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="M114" t="s">
+      <c r="M116" t="s">
         <v>148</v>
       </c>
     </row>
+    <row r="117" spans="1:13">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M117" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="180">
+  <mergeCells count="181">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A114"/>
+    <mergeCell ref="A26:A117"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B114"/>
+    <mergeCell ref="B26:B117"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C114"/>
+    <mergeCell ref="C26:C117"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D114"/>
+    <mergeCell ref="D26:D117"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -3753,8 +3845,8 @@
     <mergeCell ref="E52:E58"/>
     <mergeCell ref="E59:E104"/>
     <mergeCell ref="E105:E109"/>
-    <mergeCell ref="E110:E112"/>
-    <mergeCell ref="E113:E114"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E116:E117"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -3779,7 +3871,8 @@
     <mergeCell ref="F98:F104"/>
     <mergeCell ref="F105:F109"/>
     <mergeCell ref="F110:F112"/>
-    <mergeCell ref="F113:F114"/>
+    <mergeCell ref="F113:F115"/>
+    <mergeCell ref="F116:F117"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -3810,8 +3903,8 @@
     <mergeCell ref="G98:G100"/>
     <mergeCell ref="G102:G104"/>
     <mergeCell ref="G105:G109"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="G116:G117"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -3840,8 +3933,8 @@
     <mergeCell ref="H98:H100"/>
     <mergeCell ref="H102:H104"/>
     <mergeCell ref="H105:H109"/>
-    <mergeCell ref="H110:H112"/>
-    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="H113:H115"/>
+    <mergeCell ref="H116:H117"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -3872,8 +3965,8 @@
     <mergeCell ref="I98:I100"/>
     <mergeCell ref="I102:I104"/>
     <mergeCell ref="I105:I109"/>
-    <mergeCell ref="I110:I112"/>
-    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="I113:I115"/>
+    <mergeCell ref="I116:I117"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -3904,8 +3997,8 @@
     <mergeCell ref="J98:J100"/>
     <mergeCell ref="J102:J104"/>
     <mergeCell ref="J105:J109"/>
-    <mergeCell ref="J110:J112"/>
-    <mergeCell ref="J113:J114"/>
+    <mergeCell ref="J113:J115"/>
+    <mergeCell ref="J116:J117"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="154">
   <si>
     <t>variable_id</t>
   </si>
@@ -154,6 +154,9 @@
     <t>MPI-ESM1-2-HR</t>
   </si>
   <si>
+    <t>EC-Earth3</t>
+  </si>
+  <si>
     <t>evaluation</t>
   </si>
   <si>
@@ -164,6 +167,15 @@
   </si>
   <si>
     <t>ssp126</t>
+  </si>
+  <si>
+    <t>ssp245</t>
+  </si>
+  <si>
+    <t>ssp585</t>
+  </si>
+  <si>
+    <t>ssp119</t>
   </si>
   <si>
     <t>r0i0p0</t>
@@ -821,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -897,25 +909,25 @@
         <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -927,22 +939,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -957,25 +969,25 @@
         <v>39</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -987,22 +999,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1017,25 +1029,25 @@
         <v>39</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1050,13 +1062,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1069,19 +1081,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1096,13 +1108,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1117,25 +1129,25 @@
         <v>39</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1150,13 +1162,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1171,25 +1183,25 @@
         <v>39</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="M12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1201,22 +1213,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="M13" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1231,25 +1243,25 @@
         <v>39</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1264,25 +1276,25 @@
         <v>39</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="M15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1297,13 +1309,13 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="M16" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1319,10 +1331,10 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1337,25 +1349,25 @@
         <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1370,13 +1382,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1391,25 +1403,25 @@
         <v>39</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1421,22 +1433,22 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M21" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1451,25 +1463,25 @@
         <v>39</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M22" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1484,13 +1496,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1505,25 +1517,25 @@
         <v>39</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1535,22 +1547,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1573,25 +1585,25 @@
         <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M26" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1606,13 +1618,13 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1627,13 +1639,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1648,13 +1660,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1669,13 +1681,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1690,25 +1702,25 @@
         <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1723,13 +1735,13 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1744,13 +1756,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1765,13 +1777,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M34" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1786,13 +1798,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M35" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1807,25 +1819,25 @@
         <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="M36" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1840,13 +1852,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="M37" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1861,13 +1873,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="M38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1882,25 +1894,25 @@
         <v>41</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1915,13 +1927,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1932,25 +1944,25 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1965,13 +1977,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M42" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1984,25 +1996,25 @@
         <v>40</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M43" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2017,13 +2029,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M44" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2038,13 +2050,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M45" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2059,13 +2071,13 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2080,13 +2092,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M47" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2101,25 +2113,25 @@
         <v>40</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2134,13 +2146,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M49" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2153,19 +2165,19 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M50" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2180,13 +2192,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M51" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2201,25 +2213,25 @@
         <v>42</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2234,13 +2246,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M53" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2255,13 +2267,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M54" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2272,25 +2284,25 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M55" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2301,25 +2313,25 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M56" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2334,13 +2346,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M57" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2355,13 +2367,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M58" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2376,25 +2388,25 @@
         <v>41</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M59" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2409,13 +2421,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M60" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2430,13 +2442,13 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M61" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2447,25 +2459,25 @@
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M62" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2476,25 +2488,25 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M63" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2509,13 +2521,13 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M64" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2530,13 +2542,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M65" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2549,25 +2561,25 @@
         <v>43</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M66" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2582,13 +2594,13 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2603,13 +2615,13 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M68" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2621,22 +2633,22 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M69" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2651,13 +2663,13 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M70" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2672,13 +2684,13 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M71" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2690,22 +2702,22 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M72" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2720,13 +2732,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M73" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2741,13 +2753,13 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M74" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2758,25 +2770,25 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M75" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2788,22 +2800,22 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M76" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2815,22 +2827,22 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M77" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2841,25 +2853,25 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M78" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2874,13 +2886,13 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M79" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2895,13 +2907,13 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M80" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2913,22 +2925,22 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M81" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2943,13 +2955,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M82" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2964,13 +2976,13 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M83" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2982,22 +2994,22 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M84" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3012,13 +3024,13 @@
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M85" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3033,13 +3045,13 @@
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M86" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3052,25 +3064,25 @@
         <v>40</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M87" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3085,13 +3097,13 @@
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M88" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3106,13 +3118,13 @@
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M89" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3127,13 +3139,13 @@
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M90" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3146,25 +3158,25 @@
         <v>44</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M91" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3179,13 +3191,13 @@
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M92" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3200,13 +3212,13 @@
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M93" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3217,25 +3229,25 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M94" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3246,25 +3258,25 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M95" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3279,13 +3291,13 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M96" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3300,13 +3312,13 @@
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M97" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3319,25 +3331,25 @@
         <v>45</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M98" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3352,13 +3364,13 @@
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M99" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3373,13 +3385,13 @@
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M100" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3390,25 +3402,25 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M101" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3419,25 +3431,25 @@
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M102" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3452,13 +3464,13 @@
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M103" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3473,13 +3485,13 @@
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M104" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3494,25 +3506,25 @@
         <v>40</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M105" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3527,13 +3539,13 @@
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M106" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3548,13 +3560,13 @@
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M107" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3569,13 +3581,13 @@
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M108" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3590,13 +3602,13 @@
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M109" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3608,28 +3620,28 @@
         <v>27</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M110" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3640,25 +3652,25 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M111" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3669,25 +3681,25 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M112" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3697,28 +3709,28 @@
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M113" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3728,18 +3740,26 @@
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
+      <c r="G114" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="K114" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M114" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3749,18 +3769,26 @@
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
+      <c r="G115" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="K115" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M115" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3768,32 +3796,28 @@
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="E116" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M116" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3803,30 +3827,519 @@
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
+      <c r="G117" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="K117" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M117" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="118" spans="1:13">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M118" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M119" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M120" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M121" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M122" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M123" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M124" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M125" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M126" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M127" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M128" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M129" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M130" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M131" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M132" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M133" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M134" t="s">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="181">
+  <mergeCells count="185">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A117"/>
+    <mergeCell ref="A26:A134"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B117"/>
+    <mergeCell ref="B26:B134"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C117"/>
+    <mergeCell ref="C26:C134"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D117"/>
+    <mergeCell ref="D26:D134"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -3845,8 +4358,8 @@
     <mergeCell ref="E52:E58"/>
     <mergeCell ref="E59:E104"/>
     <mergeCell ref="E105:E109"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E116:E117"/>
+    <mergeCell ref="E110:E132"/>
+    <mergeCell ref="E133:E134"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -3871,8 +4384,12 @@
     <mergeCell ref="F98:F104"/>
     <mergeCell ref="F105:F109"/>
     <mergeCell ref="F110:F112"/>
-    <mergeCell ref="F113:F115"/>
-    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="F113:F117"/>
+    <mergeCell ref="F118:F123"/>
+    <mergeCell ref="F124:F126"/>
+    <mergeCell ref="F127:F129"/>
+    <mergeCell ref="F130:F132"/>
+    <mergeCell ref="F133:F134"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -3903,8 +4420,8 @@
     <mergeCell ref="G98:G100"/>
     <mergeCell ref="G102:G104"/>
     <mergeCell ref="G105:G109"/>
-    <mergeCell ref="G113:G115"/>
-    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G124:G126"/>
+    <mergeCell ref="G133:G134"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -3933,8 +4450,8 @@
     <mergeCell ref="H98:H100"/>
     <mergeCell ref="H102:H104"/>
     <mergeCell ref="H105:H109"/>
-    <mergeCell ref="H113:H115"/>
-    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="H124:H126"/>
+    <mergeCell ref="H133:H134"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -3965,8 +4482,8 @@
     <mergeCell ref="I98:I100"/>
     <mergeCell ref="I102:I104"/>
     <mergeCell ref="I105:I109"/>
-    <mergeCell ref="I113:I115"/>
-    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="I124:I126"/>
+    <mergeCell ref="I133:I134"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -3997,8 +4514,8 @@
     <mergeCell ref="J98:J100"/>
     <mergeCell ref="J102:J104"/>
     <mergeCell ref="J105:J109"/>
-    <mergeCell ref="J113:J115"/>
-    <mergeCell ref="J116:J117"/>
+    <mergeCell ref="J124:J126"/>
+    <mergeCell ref="J133:J134"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="153">
   <si>
     <t>variable_id</t>
   </si>
@@ -461,9 +461,6 @@
   </si>
   <si>
     <t>['pr', 'tas', 'clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['pr', 'tas', 'zg500', 'clt', 'evspsbl', 'huss', 'psl', 'rlds', 'rsds', 'tasmax', 'tasmin', 'uas', 'vas']</t>
@@ -833,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3641,7 +3638,7 @@
         <v>113</v>
       </c>
       <c r="M110" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3651,26 +3648,18 @@
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
-      <c r="G111" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M111" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3681,7 +3670,7 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>57</v>
@@ -3699,7 +3688,7 @@
         <v>113</v>
       </c>
       <c r="M112" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3708,29 +3697,19 @@
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
       <c r="K113" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M113" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3741,10 +3720,10 @@
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>80</v>
@@ -3759,7 +3738,7 @@
         <v>113</v>
       </c>
       <c r="M114" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3769,26 +3748,18 @@
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M115" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3797,9 +3768,11 @@
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
+      <c r="F116" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="G116" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>56</v>
@@ -3817,7 +3790,7 @@
         <v>113</v>
       </c>
       <c r="M116" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3827,26 +3800,18 @@
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
-      <c r="G117" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
       <c r="K117" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M117" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3855,11 +3820,9 @@
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
-      <c r="F118" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F118" s="1"/>
       <c r="G118" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>56</v>
@@ -3877,7 +3840,7 @@
         <v>113</v>
       </c>
       <c r="M118" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3887,26 +3850,18 @@
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L119" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M119" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3917,7 +3872,7 @@
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>56</v>
@@ -3935,7 +3890,7 @@
         <v>113</v>
       </c>
       <c r="M120" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3946,7 +3901,7 @@
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>56</v>
@@ -3964,7 +3919,7 @@
         <v>113</v>
       </c>
       <c r="M121" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3974,26 +3929,18 @@
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
-      <c r="G122" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
       <c r="K122" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L122" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M122" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -4022,7 +3969,7 @@
         <v>113</v>
       </c>
       <c r="M123" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -4032,10 +3979,10 @@
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>56</v>
@@ -4053,7 +4000,7 @@
         <v>113</v>
       </c>
       <c r="M124" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4084,18 +4031,26 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
+      <c r="G126" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="K126" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M126" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4104,11 +4059,9 @@
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>56</v>
@@ -4126,7 +4079,7 @@
         <v>113</v>
       </c>
       <c r="M127" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4136,26 +4089,18 @@
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
-      <c r="G128" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
       <c r="K128" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L128" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M128" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4166,7 +4111,7 @@
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>56</v>
@@ -4184,7 +4129,7 @@
         <v>113</v>
       </c>
       <c r="M129" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4193,11 +4138,9 @@
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="F130" s="1"/>
       <c r="G130" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>56</v>
@@ -4215,7 +4158,7 @@
         <v>113</v>
       </c>
       <c r="M130" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4225,26 +4168,18 @@
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
-      <c r="G131" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
       <c r="K131" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L131" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M131" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4255,7 +4190,7 @@
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>56</v>
@@ -4273,7 +4208,7 @@
         <v>113</v>
       </c>
       <c r="M132" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4281,9 +4216,7 @@
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
-      <c r="E133" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="E133" s="1"/>
       <c r="F133" s="1" t="s">
         <v>40</v>
       </c>
@@ -4294,19 +4227,19 @@
         <v>56</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J133" s="1" t="s">
         <v>83</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M133" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4321,25 +4254,404 @@
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
       <c r="K134" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M134" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+      <c r="K135" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L134" s="1" t="s">
+      <c r="L135" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M135" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M136" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M137" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M138" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M139" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M140" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
+      <c r="K141" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M142" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+      <c r="E143" s="1"/>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="K143" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M143" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M144" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M145" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M146" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M147" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L148" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="M134" t="s">
-        <v>153</v>
+      <c r="M148" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M149" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="185">
+  <mergeCells count="245">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A134"/>
+    <mergeCell ref="A26:A149"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B134"/>
+    <mergeCell ref="B26:B149"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C134"/>
+    <mergeCell ref="C26:C149"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D134"/>
+    <mergeCell ref="D26:D149"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4358,8 +4670,8 @@
     <mergeCell ref="E52:E58"/>
     <mergeCell ref="E59:E104"/>
     <mergeCell ref="E105:E109"/>
-    <mergeCell ref="E110:E132"/>
-    <mergeCell ref="E133:E134"/>
+    <mergeCell ref="E110:E147"/>
+    <mergeCell ref="E148:E149"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -4383,13 +4695,13 @@
     <mergeCell ref="F91:F97"/>
     <mergeCell ref="F98:F104"/>
     <mergeCell ref="F105:F109"/>
-    <mergeCell ref="F110:F112"/>
-    <mergeCell ref="F113:F117"/>
-    <mergeCell ref="F118:F123"/>
-    <mergeCell ref="F124:F126"/>
-    <mergeCell ref="F127:F129"/>
-    <mergeCell ref="F130:F132"/>
-    <mergeCell ref="F133:F134"/>
+    <mergeCell ref="F110:F115"/>
+    <mergeCell ref="F116:F123"/>
+    <mergeCell ref="F124:F132"/>
+    <mergeCell ref="F133:F135"/>
+    <mergeCell ref="F136:F141"/>
+    <mergeCell ref="F142:F147"/>
+    <mergeCell ref="F148:F149"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -4420,8 +4732,23 @@
     <mergeCell ref="G98:G100"/>
     <mergeCell ref="G102:G104"/>
     <mergeCell ref="G105:G109"/>
-    <mergeCell ref="G124:G126"/>
-    <mergeCell ref="G133:G134"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="G127:G128"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="G133:G135"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="G148:G149"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -4450,8 +4777,23 @@
     <mergeCell ref="H98:H100"/>
     <mergeCell ref="H102:H104"/>
     <mergeCell ref="H105:H109"/>
-    <mergeCell ref="H124:H126"/>
-    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="H110:H111"/>
+    <mergeCell ref="H112:H113"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="H118:H119"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="H133:H135"/>
+    <mergeCell ref="H136:H137"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="H144:H145"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="H148:H149"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -4482,8 +4824,23 @@
     <mergeCell ref="I98:I100"/>
     <mergeCell ref="I102:I104"/>
     <mergeCell ref="I105:I109"/>
-    <mergeCell ref="I124:I126"/>
-    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="I110:I111"/>
+    <mergeCell ref="I112:I113"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="I118:I119"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I124:I125"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="I133:I135"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="I140:I141"/>
+    <mergeCell ref="I142:I143"/>
+    <mergeCell ref="I144:I145"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="I148:I149"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -4514,8 +4871,23 @@
     <mergeCell ref="J98:J100"/>
     <mergeCell ref="J102:J104"/>
     <mergeCell ref="J105:J109"/>
-    <mergeCell ref="J124:J126"/>
-    <mergeCell ref="J133:J134"/>
+    <mergeCell ref="J110:J111"/>
+    <mergeCell ref="J112:J113"/>
+    <mergeCell ref="J114:J115"/>
+    <mergeCell ref="J116:J117"/>
+    <mergeCell ref="J118:J119"/>
+    <mergeCell ref="J121:J122"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="J127:J128"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="J133:J135"/>
+    <mergeCell ref="J136:J137"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="J140:J141"/>
+    <mergeCell ref="J142:J143"/>
+    <mergeCell ref="J144:J145"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="J148:J149"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -3121,7 +3121,7 @@
         <v>111</v>
       </c>
       <c r="M89" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:13">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="157">
   <si>
     <t>variable_id</t>
   </si>
@@ -112,6 +112,9 @@
     <t>SMHI</t>
   </si>
   <si>
+    <t>CESAM-UA</t>
+  </si>
+  <si>
     <t>CLMcom-CMCC</t>
   </si>
   <si>
@@ -232,6 +235,9 @@
     <t>RCA4</t>
   </si>
   <si>
+    <t>WRF451Q</t>
+  </si>
+  <si>
     <t>CCLM6-0-1-URB</t>
   </si>
   <si>
@@ -331,6 +337,9 @@
     <t>v20131026</t>
   </si>
   <si>
+    <t>v20250520</t>
+  </si>
+  <si>
     <t>v20250201</t>
   </si>
   <si>
@@ -377,6 +386,9 @@
   </si>
   <si>
     <t>['pr', 'tas']</t>
+  </si>
+  <si>
+    <t>['hurs', 'sfcWind', 'tas', 'pr']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
@@ -830,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -903,28 +915,28 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -936,22 +948,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -963,28 +975,28 @@
         <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -996,22 +1008,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1023,28 +1035,28 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1059,13 +1071,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1078,19 +1090,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1105,13 +1117,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1123,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1159,13 +1171,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1177,28 +1189,28 @@
         <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1210,22 +1222,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1237,28 +1249,28 @@
         <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1270,28 +1282,28 @@
         <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1306,13 +1318,13 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1328,10 +1340,10 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1343,28 +1355,28 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1379,13 +1391,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1397,28 +1409,28 @@
         <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1430,22 +1442,22 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1457,28 +1469,28 @@
         <v>30</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1493,13 +1505,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1511,28 +1523,28 @@
         <v>31</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1544,22 +1556,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1579,28 +1591,28 @@
         <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M26" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1608,20 +1620,32 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1636,13 +1660,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1657,13 +1681,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1678,13 +1702,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1692,32 +1716,20 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1725,20 +1737,32 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K32" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M32" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1753,13 +1777,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M33" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1774,13 +1798,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1795,13 +1819,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M35" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1809,32 +1833,20 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M36" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1842,20 +1854,32 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K37" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M37" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1870,13 +1894,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M38" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1884,32 +1908,20 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M39" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1917,20 +1929,32 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M40" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1940,26 +1964,18 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M41" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1969,18 +1985,26 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K42" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M42" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -1989,29 +2013,19 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M43" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2020,19 +2034,29 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2047,13 +2071,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M45" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2068,13 +2092,13 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2089,13 +2113,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2103,32 +2127,20 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2136,20 +2148,32 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K49" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M49" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2161,20 +2185,16 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
-      <c r="I50" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M50" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2186,16 +2206,20 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
+      <c r="I51" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K51" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M51" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2203,32 +2227,20 @@
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M52" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2236,20 +2248,32 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K53" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M53" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2264,13 +2288,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M54" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2280,26 +2304,18 @@
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M55" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2310,25 +2326,25 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M56" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2338,18 +2354,26 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K57" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M57" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2364,13 +2388,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M58" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2378,32 +2402,20 @@
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M59" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2411,20 +2423,32 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
+      <c r="E60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K60" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M60" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2439,13 +2463,13 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M61" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2455,26 +2479,18 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M62" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2485,25 +2501,25 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M63" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2513,18 +2529,26 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K64" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M64" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2539,13 +2563,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M65" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2554,29 +2578,19 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M66" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2585,19 +2599,29 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K67" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M67" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2612,13 +2636,13 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M68" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2629,23 +2653,17 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M69" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2656,17 +2674,23 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="H70" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M70" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2681,13 +2705,13 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M71" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2698,23 +2722,17 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M72" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2725,17 +2743,23 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="H73" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K73" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M73" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2750,13 +2774,13 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M74" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2766,26 +2790,18 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M75" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2795,24 +2811,26 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
+      <c r="G76" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="H76" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M76" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2827,19 +2845,19 @@
         <v>59</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M77" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2849,26 +2867,24 @@
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="G78" s="1"/>
       <c r="H78" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M78" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2878,18 +2894,26 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="G79" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K79" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M79" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2904,13 +2928,13 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M80" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2921,23 +2945,17 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M81" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2948,17 +2966,23 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+      <c r="H82" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K82" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M82" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2973,13 +2997,13 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M83" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2990,23 +3014,17 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M84" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3017,17 +3035,23 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="H85" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K85" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M85" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3042,13 +3066,13 @@
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M86" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3057,29 +3081,19 @@
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M87" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3088,19 +3102,29 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K88" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M88" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3115,13 +3139,13 @@
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M89" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3136,13 +3160,13 @@
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M90" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3151,29 +3175,19 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M91" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3182,19 +3196,29 @@
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K92" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M92" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3209,13 +3233,13 @@
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M93" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3225,26 +3249,18 @@
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M94" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3255,25 +3271,25 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M95" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3283,18 +3299,26 @@
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
+      <c r="G96" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K96" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M96" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3309,13 +3333,13 @@
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M97" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3324,29 +3348,19 @@
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M98" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3355,19 +3369,29 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K99" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M99" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3382,13 +3406,13 @@
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M100" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3398,26 +3422,18 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M101" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3428,25 +3444,25 @@
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M102" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3456,18 +3472,26 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+      <c r="G103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K103" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M103" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3482,13 +3506,13 @@
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M104" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3496,32 +3520,20 @@
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
-      <c r="E105" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M105" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3529,20 +3541,32 @@
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
+      <c r="E106" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K106" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M106" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3557,13 +3581,13 @@
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M107" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3578,13 +3602,13 @@
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M108" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3599,13 +3623,13 @@
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M109" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3613,32 +3637,20 @@
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
-      <c r="E110" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
       <c r="K110" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M110" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3646,20 +3658,32 @@
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
+      <c r="E111" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K111" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M111" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3669,26 +3693,18 @@
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
-      <c r="G112" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M112" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3698,18 +3714,26 @@
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
+      <c r="G113" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K113" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M113" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3719,26 +3743,18 @@
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
-      <c r="G114" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M114" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3748,18 +3764,26 @@
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
+      <c r="G115" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K115" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M115" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3768,29 +3792,19 @@
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
       <c r="K116" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M116" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3799,19 +3813,29 @@
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
+      <c r="F117" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K117" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M117" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3821,26 +3845,18 @@
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
       <c r="K118" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M118" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3850,18 +3866,26 @@
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
+      <c r="G119" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K119" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M119" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3871,26 +3895,18 @@
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
-      <c r="G120" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
       <c r="K120" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M120" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3901,25 +3917,25 @@
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M121" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3929,18 +3945,26 @@
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
+      <c r="G122" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K122" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M122" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3950,26 +3974,18 @@
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
-      <c r="G123" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
       <c r="K123" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M123" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3978,29 +3994,27 @@
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M124" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4009,19 +4023,29 @@
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
+      <c r="F125" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K125" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M125" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4031,26 +4055,18 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
       <c r="K126" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M126" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4061,25 +4077,25 @@
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M127" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4089,18 +4105,26 @@
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
+      <c r="G128" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K128" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M128" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4110,26 +4134,18 @@
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
-      <c r="G129" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
       <c r="K129" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M129" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4140,25 +4156,25 @@
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M130" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4168,18 +4184,26 @@
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
+      <c r="G131" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K131" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M131" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4189,26 +4213,18 @@
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
-      <c r="G132" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
       <c r="K132" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M132" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4217,29 +4233,27 @@
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
-      <c r="F133" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M133" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4248,19 +4262,29 @@
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
+      <c r="F134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K134" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M134" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4275,13 +4299,13 @@
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
       <c r="K135" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M135" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4290,29 +4314,19 @@
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
       <c r="K136" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M136" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4321,19 +4335,29 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
+      <c r="F137" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K137" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M137" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4343,26 +4367,18 @@
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
       <c r="K138" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M138" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4372,18 +4388,26 @@
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
+      <c r="G139" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K139" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M139" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4393,26 +4417,18 @@
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
       <c r="K140" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M140" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4422,18 +4438,26 @@
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1"/>
+      <c r="G141" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K141" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M141" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4442,29 +4466,19 @@
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
       <c r="K142" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M142" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4473,19 +4487,29 @@
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
-      <c r="F143" s="1"/>
-      <c r="G143" s="1"/>
-      <c r="H143" s="1"/>
-      <c r="I143" s="1"/>
-      <c r="J143" s="1"/>
+      <c r="F143" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K143" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M143" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4495,26 +4519,18 @@
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
-      <c r="G144" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
       <c r="K144" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M144" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4524,18 +4540,26 @@
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
-      <c r="H145" s="1"/>
-      <c r="I145" s="1"/>
-      <c r="J145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K145" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M145" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4545,26 +4569,18 @@
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
-      <c r="G146" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
       <c r="K146" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M146" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4574,18 +4590,26 @@
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
-      <c r="H147" s="1"/>
-      <c r="I147" s="1"/>
-      <c r="J147" s="1"/>
+      <c r="G147" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K147" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M147" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4593,29 +4617,17 @@
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
-      <c r="E148" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H148" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
       <c r="K148" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M148" t="s">
         <v>151</v>
@@ -4626,32 +4638,65 @@
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
-      <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
-      <c r="H149" s="1"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="1"/>
+      <c r="E149" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K149" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M149" t="s">
-        <v>152</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M150" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="245">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A149"/>
+    <mergeCell ref="A26:A150"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B149"/>
+    <mergeCell ref="B26:B150"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C149"/>
+    <mergeCell ref="C26:C150"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D149"/>
+    <mergeCell ref="D26:D150"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4662,16 +4707,16 @@
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E39:E47"/>
-    <mergeCell ref="E48:E51"/>
-    <mergeCell ref="E52:E58"/>
-    <mergeCell ref="E59:E104"/>
-    <mergeCell ref="E105:E109"/>
-    <mergeCell ref="E110:E147"/>
-    <mergeCell ref="E148:E149"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E40:E48"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="E53:E59"/>
+    <mergeCell ref="E60:E105"/>
+    <mergeCell ref="E106:E110"/>
+    <mergeCell ref="E111:E148"/>
+    <mergeCell ref="E149:E150"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -4682,26 +4727,26 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F26:F30"/>
-    <mergeCell ref="F31:F35"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="F48:F51"/>
-    <mergeCell ref="F52:F58"/>
-    <mergeCell ref="F59:F65"/>
-    <mergeCell ref="F66:F86"/>
-    <mergeCell ref="F87:F90"/>
-    <mergeCell ref="F91:F97"/>
-    <mergeCell ref="F98:F104"/>
-    <mergeCell ref="F105:F109"/>
-    <mergeCell ref="F110:F115"/>
-    <mergeCell ref="F116:F123"/>
-    <mergeCell ref="F124:F132"/>
-    <mergeCell ref="F133:F135"/>
-    <mergeCell ref="F136:F141"/>
-    <mergeCell ref="F142:F147"/>
-    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="F40:F43"/>
+    <mergeCell ref="F44:F48"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="F53:F59"/>
+    <mergeCell ref="F60:F66"/>
+    <mergeCell ref="F67:F87"/>
+    <mergeCell ref="F88:F91"/>
+    <mergeCell ref="F92:F98"/>
+    <mergeCell ref="F99:F105"/>
+    <mergeCell ref="F106:F110"/>
+    <mergeCell ref="F111:F116"/>
+    <mergeCell ref="F117:F124"/>
+    <mergeCell ref="F125:F133"/>
+    <mergeCell ref="F134:F136"/>
+    <mergeCell ref="F137:F142"/>
+    <mergeCell ref="F143:F148"/>
+    <mergeCell ref="F149:F150"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -4712,182 +4757,182 @@
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="G48:G51"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="G59:G61"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="G66:G74"/>
-    <mergeCell ref="G75:G77"/>
-    <mergeCell ref="G78:G86"/>
-    <mergeCell ref="G87:G90"/>
-    <mergeCell ref="G91:G93"/>
-    <mergeCell ref="G95:G97"/>
-    <mergeCell ref="G98:G100"/>
-    <mergeCell ref="G102:G104"/>
-    <mergeCell ref="G105:G109"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="G114:G115"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="G133:G135"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="G32:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="G44:G48"/>
+    <mergeCell ref="G49:G52"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="G67:G75"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G87"/>
+    <mergeCell ref="G88:G91"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="G96:G98"/>
+    <mergeCell ref="G99:G101"/>
+    <mergeCell ref="G103:G105"/>
+    <mergeCell ref="G106:G110"/>
+    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="G119:G120"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="G134:G136"/>
+    <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="G145:G146"/>
+    <mergeCell ref="G147:G148"/>
+    <mergeCell ref="G149:G150"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="H31:H35"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="H48:H51"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="H56:H58"/>
-    <mergeCell ref="H59:H61"/>
-    <mergeCell ref="H63:H65"/>
-    <mergeCell ref="H66:H68"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="H84:H86"/>
-    <mergeCell ref="H87:H90"/>
-    <mergeCell ref="H91:H93"/>
-    <mergeCell ref="H95:H97"/>
-    <mergeCell ref="H98:H100"/>
-    <mergeCell ref="H102:H104"/>
-    <mergeCell ref="H105:H109"/>
-    <mergeCell ref="H110:H111"/>
-    <mergeCell ref="H112:H113"/>
-    <mergeCell ref="H114:H115"/>
-    <mergeCell ref="H116:H117"/>
-    <mergeCell ref="H118:H119"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="H133:H135"/>
-    <mergeCell ref="H136:H137"/>
-    <mergeCell ref="H138:H139"/>
-    <mergeCell ref="H140:H141"/>
-    <mergeCell ref="H142:H143"/>
-    <mergeCell ref="H144:H145"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="H148:H149"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="H32:H36"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H44:H48"/>
+    <mergeCell ref="H49:H52"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="H67:H69"/>
+    <mergeCell ref="H70:H72"/>
+    <mergeCell ref="H73:H75"/>
+    <mergeCell ref="H79:H81"/>
+    <mergeCell ref="H82:H84"/>
+    <mergeCell ref="H85:H87"/>
+    <mergeCell ref="H88:H91"/>
+    <mergeCell ref="H92:H94"/>
+    <mergeCell ref="H96:H98"/>
+    <mergeCell ref="H99:H101"/>
+    <mergeCell ref="H103:H105"/>
+    <mergeCell ref="H106:H110"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="H122:H123"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="H134:H136"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H149:H150"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I26:I30"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="I56:I58"/>
-    <mergeCell ref="I59:I61"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="I66:I68"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="I72:I74"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="I84:I86"/>
-    <mergeCell ref="I87:I90"/>
-    <mergeCell ref="I91:I93"/>
-    <mergeCell ref="I95:I97"/>
-    <mergeCell ref="I98:I100"/>
-    <mergeCell ref="I102:I104"/>
-    <mergeCell ref="I105:I109"/>
-    <mergeCell ref="I110:I111"/>
-    <mergeCell ref="I112:I113"/>
-    <mergeCell ref="I114:I115"/>
-    <mergeCell ref="I116:I117"/>
-    <mergeCell ref="I118:I119"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I124:I125"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="I133:I135"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="I140:I141"/>
-    <mergeCell ref="I142:I143"/>
-    <mergeCell ref="I144:I145"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="I148:I149"/>
+    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="I32:I36"/>
+    <mergeCell ref="I37:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I44:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="I57:I59"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I67:I69"/>
+    <mergeCell ref="I70:I72"/>
+    <mergeCell ref="I73:I75"/>
+    <mergeCell ref="I79:I81"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="I85:I87"/>
+    <mergeCell ref="I88:I91"/>
+    <mergeCell ref="I92:I94"/>
+    <mergeCell ref="I96:I98"/>
+    <mergeCell ref="I99:I101"/>
+    <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I106:I110"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="I122:I123"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="I134:I136"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="I141:I142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I149:I150"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J26:J30"/>
-    <mergeCell ref="J31:J35"/>
-    <mergeCell ref="J36:J38"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="J48:J49"/>
-    <mergeCell ref="J50:J51"/>
-    <mergeCell ref="J52:J54"/>
-    <mergeCell ref="J56:J58"/>
-    <mergeCell ref="J59:J61"/>
-    <mergeCell ref="J63:J65"/>
-    <mergeCell ref="J66:J68"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="J72:J74"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="J84:J86"/>
-    <mergeCell ref="J87:J90"/>
-    <mergeCell ref="J91:J93"/>
-    <mergeCell ref="J95:J97"/>
-    <mergeCell ref="J98:J100"/>
-    <mergeCell ref="J102:J104"/>
-    <mergeCell ref="J105:J109"/>
-    <mergeCell ref="J110:J111"/>
-    <mergeCell ref="J112:J113"/>
-    <mergeCell ref="J114:J115"/>
-    <mergeCell ref="J116:J117"/>
-    <mergeCell ref="J118:J119"/>
-    <mergeCell ref="J121:J122"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="J127:J128"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="J133:J135"/>
-    <mergeCell ref="J136:J137"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="J140:J141"/>
-    <mergeCell ref="J142:J143"/>
-    <mergeCell ref="J144:J145"/>
-    <mergeCell ref="J146:J147"/>
-    <mergeCell ref="J148:J149"/>
+    <mergeCell ref="J27:J31"/>
+    <mergeCell ref="J32:J36"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="J44:J48"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J67:J69"/>
+    <mergeCell ref="J70:J72"/>
+    <mergeCell ref="J73:J75"/>
+    <mergeCell ref="J79:J81"/>
+    <mergeCell ref="J82:J84"/>
+    <mergeCell ref="J85:J87"/>
+    <mergeCell ref="J88:J91"/>
+    <mergeCell ref="J92:J94"/>
+    <mergeCell ref="J96:J98"/>
+    <mergeCell ref="J99:J101"/>
+    <mergeCell ref="J103:J105"/>
+    <mergeCell ref="J106:J110"/>
+    <mergeCell ref="J111:J112"/>
+    <mergeCell ref="J113:J114"/>
+    <mergeCell ref="J115:J116"/>
+    <mergeCell ref="J117:J118"/>
+    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="J122:J123"/>
+    <mergeCell ref="J125:J126"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="J131:J132"/>
+    <mergeCell ref="J134:J136"/>
+    <mergeCell ref="J137:J138"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="J141:J142"/>
+    <mergeCell ref="J143:J144"/>
+    <mergeCell ref="J145:J146"/>
+    <mergeCell ref="J147:J148"/>
+    <mergeCell ref="J149:J150"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="159">
   <si>
     <t>variable_id</t>
   </si>
@@ -421,6 +421,9 @@
     <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
+    <t>['hurs']</t>
+  </si>
+  <si>
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
   </si>
   <si>
@@ -440,6 +443,9 @@
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin', 'mrro', 'mrros', 'mrso', 'prsn', 'rldscs', 'rlutcs', 'rsdscs', 'rsutcs', 'snc', 'snd', 'snw', 'zg500']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
@@ -842,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1873,7 +1879,7 @@
         <v>85</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>110</v>
@@ -1894,13 +1900,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>110</v>
       </c>
       <c r="M38" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1915,13 +1921,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>110</v>
       </c>
       <c r="M39" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1929,29 +1935,17 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M40" t="s">
         <v>136</v>
@@ -1962,20 +1956,32 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K41" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>111</v>
       </c>
       <c r="M41" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -1985,26 +1991,18 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>111</v>
       </c>
       <c r="M42" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2014,18 +2012,26 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="G43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K43" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>111</v>
       </c>
       <c r="M43" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2034,29 +2040,19 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M44" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2065,13 +2061,23 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K45" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>112</v>
@@ -2092,7 +2098,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>112</v>
@@ -2113,7 +2119,7 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>112</v>
@@ -2134,7 +2140,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>112</v>
@@ -2148,32 +2154,20 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M49" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2181,20 +2175,32 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K50" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2206,12 +2212,8 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
         <v>86</v>
       </c>
@@ -2219,7 +2221,7 @@
         <v>113</v>
       </c>
       <c r="M51" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2240,7 +2242,7 @@
         <v>113</v>
       </c>
       <c r="M52" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2248,20 +2250,12 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>85</v>
@@ -2270,10 +2264,10 @@
         <v>88</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2291,10 +2285,10 @@
         <v>86</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M54" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2312,10 +2306,10 @@
         <v>87</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2323,10 +2317,14 @@
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+      <c r="E56" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G56" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>57</v>
@@ -2338,13 +2336,13 @@
         <v>85</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M56" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2354,26 +2352,18 @@
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M57" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2388,13 +2378,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M58" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2404,18 +2394,26 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="G59" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M59" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2423,17 +2421,13 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>80</v>
@@ -2448,7 +2442,7 @@
         <v>114</v>
       </c>
       <c r="M60" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2490,7 +2484,7 @@
         <v>114</v>
       </c>
       <c r="M62" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2498,10 +2492,14 @@
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
+      <c r="E63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G63" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>58</v>
@@ -2513,13 +2511,13 @@
         <v>85</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M63" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2529,26 +2527,18 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M64" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2563,13 +2553,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M65" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2579,18 +2569,26 @@
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
+      <c r="G66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K66" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M66" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2599,14 +2597,12 @@
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>80</v>
@@ -2621,7 +2617,7 @@
         <v>114</v>
       </c>
       <c r="M67" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2663,7 +2659,7 @@
         <v>114</v>
       </c>
       <c r="M69" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2672,10 +2668,14 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="H70" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>80</v>
@@ -2690,7 +2690,7 @@
         <v>114</v>
       </c>
       <c r="M70" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2732,7 +2732,7 @@
         <v>114</v>
       </c>
       <c r="M72" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2744,7 +2744,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>80</v>
@@ -2759,7 +2759,7 @@
         <v>114</v>
       </c>
       <c r="M73" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2801,7 +2801,7 @@
         <v>114</v>
       </c>
       <c r="M75" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2811,11 +2811,9 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>80</v>
@@ -2824,13 +2822,13 @@
         <v>85</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M76" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2841,15 +2839,9 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-      <c r="H77" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
         <v>86</v>
       </c>
@@ -2868,23 +2860,17 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-      <c r="H78" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M78" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2895,7 +2881,7 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>57</v>
@@ -2907,13 +2893,13 @@
         <v>85</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M79" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2924,9 +2910,15 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="H80" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K80" s="1" t="s">
         <v>86</v>
       </c>
@@ -2945,17 +2937,23 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="H81" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K81" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M81" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2965,9 +2963,11 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
+      <c r="G82" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="H82" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>80</v>
@@ -2982,7 +2982,7 @@
         <v>114</v>
       </c>
       <c r="M82" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -3024,7 +3024,7 @@
         <v>114</v>
       </c>
       <c r="M84" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3036,7 +3036,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>80</v>
@@ -3051,7 +3051,7 @@
         <v>114</v>
       </c>
       <c r="M85" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3093,7 +3093,7 @@
         <v>114</v>
       </c>
       <c r="M87" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3102,14 +3102,10 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>80</v>
@@ -3118,7 +3114,7 @@
         <v>85</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>114</v>
@@ -3139,13 +3135,13 @@
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M89" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3160,13 +3156,13 @@
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M90" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3175,19 +3171,29 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K91" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3196,21 +3202,11 @@
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
         <v>88</v>
       </c>
@@ -3218,7 +3214,7 @@
         <v>114</v>
       </c>
       <c r="M92" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3239,7 +3235,7 @@
         <v>114</v>
       </c>
       <c r="M93" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3260,7 +3256,7 @@
         <v>114</v>
       </c>
       <c r="M94" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3269,9 +3265,11 @@
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
+      <c r="F95" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="G95" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>57</v>
@@ -3283,13 +3281,13 @@
         <v>85</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M95" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3299,26 +3297,18 @@
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M96" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3333,13 +3323,13 @@
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M97" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3349,18 +3339,26 @@
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
+      <c r="G98" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K98" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M98" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3369,11 +3367,9 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="F99" s="1"/>
       <c r="G99" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>57</v>
@@ -3391,7 +3387,7 @@
         <v>114</v>
       </c>
       <c r="M99" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3433,7 +3429,7 @@
         <v>114</v>
       </c>
       <c r="M101" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3442,9 +3438,11 @@
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="G102" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>57</v>
@@ -3456,13 +3454,13 @@
         <v>85</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L102" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M102" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3472,26 +3470,18 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M103" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3506,13 +3496,13 @@
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M104" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3522,18 +3512,26 @@
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
+      <c r="G105" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K105" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M105" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3541,32 +3539,28 @@
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
-      <c r="E106" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>85</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M106" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3581,13 +3575,13 @@
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M107" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3602,13 +3596,13 @@
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M108" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3616,20 +3610,32 @@
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
+      <c r="E109" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K109" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3644,13 +3650,13 @@
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M110" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3658,32 +3664,20 @@
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="E111" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M111" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3701,10 +3695,10 @@
         <v>86</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M112" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3714,26 +3708,18 @@
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
-      <c r="G113" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
       <c r="K113" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M113" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3741,20 +3727,32 @@
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
+      <c r="E114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K114" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M114" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3764,26 +3762,18 @@
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M115" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3793,18 +3783,26 @@
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
+      <c r="G116" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K116" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M116" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3813,29 +3811,19 @@
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
       <c r="K117" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M117" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3845,18 +3833,26 @@
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
+      <c r="G118" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K118" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M118" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3866,26 +3862,18 @@
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L119" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M119" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3894,19 +3882,29 @@
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
+      <c r="F120" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K120" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M120" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3916,26 +3914,18 @@
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
-      <c r="G121" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
       <c r="K121" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M121" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3946,7 +3936,7 @@
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>57</v>
@@ -3964,7 +3954,7 @@
         <v>116</v>
       </c>
       <c r="M122" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3985,7 +3975,7 @@
         <v>116</v>
       </c>
       <c r="M123" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3996,7 +3986,7 @@
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>57</v>
@@ -4014,7 +4004,7 @@
         <v>116</v>
       </c>
       <c r="M124" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4023,11 +4013,9 @@
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="F125" s="1"/>
       <c r="G125" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>57</v>
@@ -4045,7 +4033,7 @@
         <v>116</v>
       </c>
       <c r="M125" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4066,7 +4054,7 @@
         <v>116</v>
       </c>
       <c r="M126" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4077,7 +4065,7 @@
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>57</v>
@@ -4095,7 +4083,7 @@
         <v>116</v>
       </c>
       <c r="M127" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4104,9 +4092,11 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
+      <c r="F128" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G128" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>57</v>
@@ -4124,7 +4114,7 @@
         <v>116</v>
       </c>
       <c r="M128" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4145,7 +4135,7 @@
         <v>116</v>
       </c>
       <c r="M129" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4156,7 +4146,7 @@
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>57</v>
@@ -4174,7 +4164,7 @@
         <v>116</v>
       </c>
       <c r="M130" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4185,7 +4175,7 @@
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>57</v>
@@ -4203,7 +4193,7 @@
         <v>116</v>
       </c>
       <c r="M131" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4224,7 +4214,7 @@
         <v>116</v>
       </c>
       <c r="M132" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4235,7 +4225,7 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>57</v>
@@ -4253,7 +4243,7 @@
         <v>116</v>
       </c>
       <c r="M133" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4262,11 +4252,9 @@
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F134" s="1"/>
       <c r="G134" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>57</v>
@@ -4284,7 +4272,7 @@
         <v>116</v>
       </c>
       <c r="M134" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4305,7 +4293,7 @@
         <v>116</v>
       </c>
       <c r="M135" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4315,18 +4303,26 @@
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
+      <c r="G136" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K136" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M136" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4336,10 +4332,10 @@
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>57</v>
@@ -4357,7 +4353,7 @@
         <v>116</v>
       </c>
       <c r="M137" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4378,7 +4374,7 @@
         <v>116</v>
       </c>
       <c r="M138" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4388,26 +4384,18 @@
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
       <c r="K139" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M139" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4416,19 +4404,29 @@
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
+      <c r="F140" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K140" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M140" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4438,26 +4436,18 @@
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
-      <c r="G141" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
       <c r="K141" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M141" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4467,18 +4457,26 @@
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
-      <c r="G142" s="1"/>
-      <c r="H142" s="1"/>
-      <c r="I142" s="1"/>
-      <c r="J142" s="1"/>
+      <c r="G142" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K142" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M142" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4487,29 +4485,19 @@
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
-      <c r="F143" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H143" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J143" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
       <c r="K143" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L143" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M143" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4519,18 +4507,26 @@
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
-      <c r="G144" s="1"/>
-      <c r="H144" s="1"/>
-      <c r="I144" s="1"/>
-      <c r="J144" s="1"/>
+      <c r="G144" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K144" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M144" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4540,26 +4536,18 @@
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
-      <c r="G145" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
       <c r="K145" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M145" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4568,19 +4556,29 @@
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="1"/>
-      <c r="G146" s="1"/>
-      <c r="H146" s="1"/>
-      <c r="I146" s="1"/>
-      <c r="J146" s="1"/>
+      <c r="F146" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K146" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L146" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M146" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4590,26 +4588,18 @@
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
-      <c r="G147" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J147" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
       <c r="K147" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L147" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M147" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4619,18 +4609,26 @@
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
-      <c r="H148" s="1"/>
-      <c r="I148" s="1"/>
-      <c r="J148" s="1"/>
+      <c r="G148" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K148" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L148" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M148" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4638,32 +4636,20 @@
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
-      <c r="E149" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
       <c r="K149" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M149" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4673,30 +4659,113 @@
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
+      <c r="G150" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K150" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M150" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
+      <c r="K151" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M151" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M152" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L150" s="1" t="s">
+      <c r="L153" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M150" t="s">
-        <v>156</v>
+      <c r="M153" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="245">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A150"/>
+    <mergeCell ref="A26:A153"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B150"/>
+    <mergeCell ref="B26:B153"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C150"/>
+    <mergeCell ref="C26:C153"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D150"/>
+    <mergeCell ref="D26:D153"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4709,14 +4778,14 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E27:E31"/>
     <mergeCell ref="E32:E36"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E40:E48"/>
-    <mergeCell ref="E49:E52"/>
-    <mergeCell ref="E53:E59"/>
-    <mergeCell ref="E60:E105"/>
-    <mergeCell ref="E106:E110"/>
-    <mergeCell ref="E111:E148"/>
-    <mergeCell ref="E149:E150"/>
+    <mergeCell ref="E37:E40"/>
+    <mergeCell ref="E41:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E62"/>
+    <mergeCell ref="E63:E108"/>
+    <mergeCell ref="E109:E113"/>
+    <mergeCell ref="E114:E151"/>
+    <mergeCell ref="E152:E153"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -4729,24 +4798,24 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F27:F31"/>
     <mergeCell ref="F32:F36"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F48"/>
-    <mergeCell ref="F49:F52"/>
-    <mergeCell ref="F53:F59"/>
-    <mergeCell ref="F60:F66"/>
-    <mergeCell ref="F67:F87"/>
-    <mergeCell ref="F88:F91"/>
-    <mergeCell ref="F92:F98"/>
-    <mergeCell ref="F99:F105"/>
-    <mergeCell ref="F106:F110"/>
-    <mergeCell ref="F111:F116"/>
-    <mergeCell ref="F117:F124"/>
-    <mergeCell ref="F125:F133"/>
-    <mergeCell ref="F134:F136"/>
-    <mergeCell ref="F137:F142"/>
-    <mergeCell ref="F143:F148"/>
-    <mergeCell ref="F149:F150"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="F41:F44"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="F50:F55"/>
+    <mergeCell ref="F56:F62"/>
+    <mergeCell ref="F63:F69"/>
+    <mergeCell ref="F70:F90"/>
+    <mergeCell ref="F91:F94"/>
+    <mergeCell ref="F95:F101"/>
+    <mergeCell ref="F102:F108"/>
+    <mergeCell ref="F109:F113"/>
+    <mergeCell ref="F114:F119"/>
+    <mergeCell ref="F120:F127"/>
+    <mergeCell ref="F128:F136"/>
+    <mergeCell ref="F137:F139"/>
+    <mergeCell ref="F140:F145"/>
+    <mergeCell ref="F146:F151"/>
+    <mergeCell ref="F152:F153"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -4759,41 +4828,41 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G27:G31"/>
     <mergeCell ref="G32:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="G44:G48"/>
-    <mergeCell ref="G49:G52"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="G50:G55"/>
+    <mergeCell ref="G56:G58"/>
     <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="G67:G75"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G79:G87"/>
-    <mergeCell ref="G88:G91"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="G96:G98"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="G70:G78"/>
+    <mergeCell ref="G79:G81"/>
+    <mergeCell ref="G82:G90"/>
+    <mergeCell ref="G91:G94"/>
+    <mergeCell ref="G95:G97"/>
     <mergeCell ref="G99:G101"/>
-    <mergeCell ref="G103:G105"/>
-    <mergeCell ref="G106:G110"/>
-    <mergeCell ref="G111:G112"/>
-    <mergeCell ref="G113:G114"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="G119:G120"/>
+    <mergeCell ref="G102:G104"/>
+    <mergeCell ref="G106:G108"/>
+    <mergeCell ref="G109:G113"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="G120:G121"/>
     <mergeCell ref="G122:G123"/>
     <mergeCell ref="G125:G126"/>
     <mergeCell ref="G128:G129"/>
     <mergeCell ref="G131:G132"/>
-    <mergeCell ref="G134:G136"/>
-    <mergeCell ref="G137:G138"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="G141:G142"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="G145:G146"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="G137:G139"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G152:G153"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -4801,44 +4870,44 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H27:H31"/>
     <mergeCell ref="H32:H36"/>
-    <mergeCell ref="H37:H39"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H44:H48"/>
-    <mergeCell ref="H49:H52"/>
-    <mergeCell ref="H53:H55"/>
-    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="H37:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H58"/>
     <mergeCell ref="H60:H62"/>
-    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="H63:H65"/>
     <mergeCell ref="H67:H69"/>
     <mergeCell ref="H70:H72"/>
     <mergeCell ref="H73:H75"/>
-    <mergeCell ref="H79:H81"/>
+    <mergeCell ref="H76:H78"/>
     <mergeCell ref="H82:H84"/>
     <mergeCell ref="H85:H87"/>
-    <mergeCell ref="H88:H91"/>
-    <mergeCell ref="H92:H94"/>
-    <mergeCell ref="H96:H98"/>
+    <mergeCell ref="H88:H90"/>
+    <mergeCell ref="H91:H94"/>
+    <mergeCell ref="H95:H97"/>
     <mergeCell ref="H99:H101"/>
-    <mergeCell ref="H103:H105"/>
-    <mergeCell ref="H106:H110"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="H102:H104"/>
+    <mergeCell ref="H106:H108"/>
+    <mergeCell ref="H109:H113"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="H118:H119"/>
+    <mergeCell ref="H120:H121"/>
     <mergeCell ref="H122:H123"/>
     <mergeCell ref="H125:H126"/>
     <mergeCell ref="H128:H129"/>
     <mergeCell ref="H131:H132"/>
-    <mergeCell ref="H134:H136"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H134:H135"/>
+    <mergeCell ref="H137:H139"/>
+    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="H144:H145"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="H148:H149"/>
+    <mergeCell ref="H150:H151"/>
+    <mergeCell ref="H152:H153"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -4847,45 +4916,45 @@
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I27:I31"/>
     <mergeCell ref="I32:I36"/>
-    <mergeCell ref="I37:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="I44:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="I50:I52"/>
     <mergeCell ref="I53:I55"/>
-    <mergeCell ref="I57:I59"/>
+    <mergeCell ref="I56:I58"/>
     <mergeCell ref="I60:I62"/>
-    <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I63:I65"/>
     <mergeCell ref="I67:I69"/>
     <mergeCell ref="I70:I72"/>
     <mergeCell ref="I73:I75"/>
-    <mergeCell ref="I79:I81"/>
+    <mergeCell ref="I76:I78"/>
     <mergeCell ref="I82:I84"/>
     <mergeCell ref="I85:I87"/>
-    <mergeCell ref="I88:I91"/>
-    <mergeCell ref="I92:I94"/>
-    <mergeCell ref="I96:I98"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="I91:I94"/>
+    <mergeCell ref="I95:I97"/>
     <mergeCell ref="I99:I101"/>
-    <mergeCell ref="I103:I105"/>
-    <mergeCell ref="I106:I110"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="I102:I104"/>
+    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="I109:I113"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="I118:I119"/>
+    <mergeCell ref="I120:I121"/>
     <mergeCell ref="I122:I123"/>
     <mergeCell ref="I125:I126"/>
     <mergeCell ref="I128:I129"/>
     <mergeCell ref="I131:I132"/>
-    <mergeCell ref="I134:I136"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="I141:I142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I134:I135"/>
+    <mergeCell ref="I137:I139"/>
+    <mergeCell ref="I140:I141"/>
+    <mergeCell ref="I142:I143"/>
+    <mergeCell ref="I144:I145"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="I148:I149"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="I152:I153"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -4894,45 +4963,45 @@
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="J27:J31"/>
     <mergeCell ref="J32:J36"/>
-    <mergeCell ref="J37:J39"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="J44:J48"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J37:J40"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="J45:J49"/>
+    <mergeCell ref="J50:J52"/>
     <mergeCell ref="J53:J55"/>
-    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="J56:J58"/>
     <mergeCell ref="J60:J62"/>
-    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J63:J65"/>
     <mergeCell ref="J67:J69"/>
     <mergeCell ref="J70:J72"/>
     <mergeCell ref="J73:J75"/>
-    <mergeCell ref="J79:J81"/>
+    <mergeCell ref="J76:J78"/>
     <mergeCell ref="J82:J84"/>
     <mergeCell ref="J85:J87"/>
-    <mergeCell ref="J88:J91"/>
-    <mergeCell ref="J92:J94"/>
-    <mergeCell ref="J96:J98"/>
+    <mergeCell ref="J88:J90"/>
+    <mergeCell ref="J91:J94"/>
+    <mergeCell ref="J95:J97"/>
     <mergeCell ref="J99:J101"/>
-    <mergeCell ref="J103:J105"/>
-    <mergeCell ref="J106:J110"/>
-    <mergeCell ref="J111:J112"/>
-    <mergeCell ref="J113:J114"/>
-    <mergeCell ref="J115:J116"/>
-    <mergeCell ref="J117:J118"/>
-    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="J102:J104"/>
+    <mergeCell ref="J106:J108"/>
+    <mergeCell ref="J109:J113"/>
+    <mergeCell ref="J114:J115"/>
+    <mergeCell ref="J116:J117"/>
+    <mergeCell ref="J118:J119"/>
+    <mergeCell ref="J120:J121"/>
     <mergeCell ref="J122:J123"/>
     <mergeCell ref="J125:J126"/>
     <mergeCell ref="J128:J129"/>
     <mergeCell ref="J131:J132"/>
-    <mergeCell ref="J134:J136"/>
-    <mergeCell ref="J137:J138"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="J141:J142"/>
-    <mergeCell ref="J143:J144"/>
-    <mergeCell ref="J145:J146"/>
-    <mergeCell ref="J147:J148"/>
-    <mergeCell ref="J149:J150"/>
+    <mergeCell ref="J134:J135"/>
+    <mergeCell ref="J137:J139"/>
+    <mergeCell ref="J140:J141"/>
+    <mergeCell ref="J142:J143"/>
+    <mergeCell ref="J144:J145"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="J148:J149"/>
+    <mergeCell ref="J150:J151"/>
+    <mergeCell ref="J152:J153"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="161">
   <si>
     <t>variable_id</t>
   </si>
@@ -445,10 +445,16 @@
     <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin', 'mrro', 'mrros', 'mrso', 'prsn', 'rldscs', 'rlutcs', 'rsdscs', 'rsutcs', 'snc', 'snd', 'snw', 'zg500']</t>
   </si>
   <si>
+    <t>['pr', 'sfcWind']</t>
+  </si>
+  <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['pr', 'sfcWind', 'tas']</t>
   </si>
   <si>
     <t>['orog', 'sftlaf', 'sftlf']</t>
@@ -848,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -2194,7 +2200,7 @@
         <v>85</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>113</v>
@@ -2215,13 +2221,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M51" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2236,13 +2242,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M52" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2254,20 +2260,16 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M53" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2279,16 +2281,20 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="I54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K54" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2303,7 +2309,7 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>113</v>
@@ -2317,32 +2323,20 @@
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2357,13 +2351,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M57" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2371,20 +2365,32 @@
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="E58" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K58" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M58" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2394,18 +2400,10 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
         <v>86</v>
       </c>
@@ -2423,26 +2421,18 @@
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M60" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2452,10 +2442,18 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
+      <c r="G61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K61" s="1" t="s">
         <v>86</v>
       </c>
@@ -2473,18 +2471,26 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K62" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M62" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2492,32 +2498,20 @@
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M63" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2532,13 +2526,13 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M64" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2546,20 +2540,32 @@
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K65" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2569,18 +2575,10 @@
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
         <v>86</v>
       </c>
@@ -2598,26 +2596,18 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M67" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2627,10 +2617,18 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K68" s="1" t="s">
         <v>86</v>
       </c>
@@ -2648,18 +2646,26 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K69" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2668,29 +2674,19 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M70" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2705,13 +2701,13 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M71" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2720,19 +2716,29 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K72" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2743,23 +2749,17 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M73" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2774,13 +2774,13 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M74" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2791,17 +2791,23 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
+      <c r="H75" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K75" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2812,23 +2818,17 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-      <c r="H76" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M76" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2843,13 +2843,13 @@
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M77" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2860,17 +2860,23 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="H78" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K78" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2880,18 +2886,10 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
         <v>86</v>
       </c>
@@ -2910,23 +2908,17 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M80" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2936,9 +2928,11 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
+      <c r="G81" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="H81" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>80</v>
@@ -2963,11 +2957,9 @@
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>80</v>
@@ -2976,13 +2968,13 @@
         <v>85</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M82" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2993,9 +2985,15 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
+      <c r="H83" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K83" s="1" t="s">
         <v>86</v>
       </c>
@@ -3013,18 +3011,26 @@
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="G84" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K84" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M84" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3035,23 +3041,17 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M85" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3066,13 +3066,13 @@
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M86" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3083,17 +3083,23 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
+      <c r="H87" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K87" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3104,23 +3110,17 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
-      <c r="H88" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M88" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3135,13 +3135,13 @@
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M89" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3152,17 +3152,23 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
+      <c r="H90" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K90" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3171,29 +3177,19 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M91" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3208,13 +3204,13 @@
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M92" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3223,19 +3219,29 @@
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K93" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M93" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3250,13 +3256,13 @@
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M94" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3265,29 +3271,19 @@
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M95" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3302,13 +3298,13 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M96" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3317,19 +3313,29 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K97" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M97" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3339,18 +3345,10 @@
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3368,26 +3366,18 @@
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M99" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3397,10 +3387,18 @@
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
+      <c r="G100" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K100" s="1" t="s">
         <v>86</v>
       </c>
@@ -3418,18 +3416,26 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
+      <c r="G101" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K101" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3438,29 +3444,19 @@
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
       <c r="K102" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L102" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M102" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3475,13 +3471,13 @@
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M103" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3490,19 +3486,29 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
+      <c r="F104" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K104" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M104" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3512,18 +3518,10 @@
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
         <v>86</v>
       </c>
@@ -3541,26 +3539,18 @@
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="G106" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M106" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3570,10 +3560,18 @@
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
+      <c r="G107" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K107" s="1" t="s">
         <v>86</v>
       </c>
@@ -3591,18 +3589,26 @@
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
+      <c r="G108" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K108" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>114</v>
       </c>
       <c r="M108" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3610,32 +3616,20 @@
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
-      <c r="E109" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M109" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3650,13 +3644,13 @@
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M110" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3664,14 +3658,26 @@
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
+      <c r="E111" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K111" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>115</v>
@@ -3692,7 +3698,7 @@
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>115</v>
@@ -3713,7 +3719,7 @@
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>115</v>
@@ -3727,32 +3733,20 @@
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
-      <c r="E114" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M114" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3767,13 +3761,13 @@
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M115" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3781,10 +3775,14 @@
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
+      <c r="E116" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G116" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>58</v>
@@ -3802,7 +3800,7 @@
         <v>116</v>
       </c>
       <c r="M116" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3823,7 +3821,7 @@
         <v>116</v>
       </c>
       <c r="M117" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3834,7 +3832,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>58</v>
@@ -3852,7 +3850,7 @@
         <v>116</v>
       </c>
       <c r="M118" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3873,7 +3871,7 @@
         <v>116</v>
       </c>
       <c r="M119" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3882,14 +3880,12 @@
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>82</v>
@@ -3904,7 +3900,7 @@
         <v>116</v>
       </c>
       <c r="M120" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3925,7 +3921,7 @@
         <v>116</v>
       </c>
       <c r="M121" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3934,9 +3930,11 @@
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
+      <c r="F122" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G122" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>57</v>
@@ -3954,7 +3952,7 @@
         <v>116</v>
       </c>
       <c r="M122" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3975,7 +3973,7 @@
         <v>116</v>
       </c>
       <c r="M123" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3986,7 +3984,7 @@
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>57</v>
@@ -4004,7 +4002,7 @@
         <v>116</v>
       </c>
       <c r="M124" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4014,26 +4012,18 @@
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
-      <c r="G125" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
       <c r="K125" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M125" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4043,18 +4033,26 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
+      <c r="G126" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K126" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M126" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4065,7 +4063,7 @@
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>57</v>
@@ -4083,7 +4081,7 @@
         <v>116</v>
       </c>
       <c r="M127" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4092,29 +4090,19 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
       <c r="K128" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L128" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M128" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4124,18 +4112,26 @@
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
-      <c r="G129" s="1"/>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="1"/>
+      <c r="G129" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K129" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L129" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M129" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4144,9 +4140,11 @@
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G130" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>57</v>
@@ -4164,7 +4162,7 @@
         <v>116</v>
       </c>
       <c r="M130" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4174,26 +4172,18 @@
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
-      <c r="G131" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
       <c r="K131" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L131" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M131" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4203,18 +4193,26 @@
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
+      <c r="G132" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K132" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L132" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M132" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4225,7 +4223,7 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>57</v>
@@ -4243,7 +4241,7 @@
         <v>116</v>
       </c>
       <c r="M133" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4253,26 +4251,18 @@
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
       <c r="K134" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L134" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M134" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4282,18 +4272,26 @@
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1"/>
+      <c r="G135" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K135" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L135" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M135" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4304,7 +4302,7 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>57</v>
@@ -4322,7 +4320,7 @@
         <v>116</v>
       </c>
       <c r="M136" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4331,23 +4329,13 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
       <c r="K137" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>116</v>
@@ -4363,18 +4351,26 @@
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="1"/>
+      <c r="G138" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K138" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M138" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4383,19 +4379,29 @@
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
+      <c r="F139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K139" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M139" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4404,29 +4410,19 @@
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
-      <c r="F140" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
       <c r="K140" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M140" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4441,13 +4437,13 @@
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M141" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4456,9 +4452,11 @@
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="1"/>
+      <c r="F142" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="G142" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>57</v>
@@ -4476,7 +4474,7 @@
         <v>116</v>
       </c>
       <c r="M142" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4497,7 +4495,7 @@
         <v>116</v>
       </c>
       <c r="M143" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4508,7 +4506,7 @@
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>57</v>
@@ -4526,7 +4524,7 @@
         <v>116</v>
       </c>
       <c r="M144" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4547,7 +4545,7 @@
         <v>116</v>
       </c>
       <c r="M145" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4556,11 +4554,9 @@
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>57</v>
@@ -4578,7 +4574,7 @@
         <v>116</v>
       </c>
       <c r="M146" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4599,7 +4595,7 @@
         <v>116</v>
       </c>
       <c r="M147" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4608,9 +4604,11 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="1"/>
+      <c r="F148" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G148" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>57</v>
@@ -4628,7 +4626,7 @@
         <v>116</v>
       </c>
       <c r="M148" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4649,7 +4647,7 @@
         <v>116</v>
       </c>
       <c r="M149" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4660,7 +4658,7 @@
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>57</v>
@@ -4678,7 +4676,7 @@
         <v>116</v>
       </c>
       <c r="M150" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4699,7 +4697,7 @@
         <v>116</v>
       </c>
       <c r="M151" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4707,32 +4705,28 @@
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
-      <c r="E152" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>85</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M152" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4747,25 +4741,79 @@
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
       <c r="K153" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M153" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M154" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L153" s="1" t="s">
+      <c r="L155" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M153" t="s">
-        <v>158</v>
+      <c r="M155" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="245">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A153"/>
+    <mergeCell ref="A26:A155"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B153"/>
+    <mergeCell ref="B26:B155"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C153"/>
+    <mergeCell ref="C26:C155"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D153"/>
+    <mergeCell ref="D26:D155"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4780,12 +4828,12 @@
     <mergeCell ref="E32:E36"/>
     <mergeCell ref="E37:E40"/>
     <mergeCell ref="E41:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E62"/>
-    <mergeCell ref="E63:E108"/>
-    <mergeCell ref="E109:E113"/>
-    <mergeCell ref="E114:E151"/>
-    <mergeCell ref="E152:E153"/>
+    <mergeCell ref="E50:E57"/>
+    <mergeCell ref="E58:E64"/>
+    <mergeCell ref="E65:E110"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E116:E153"/>
+    <mergeCell ref="E154:E155"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -4801,21 +4849,21 @@
     <mergeCell ref="F37:F40"/>
     <mergeCell ref="F41:F44"/>
     <mergeCell ref="F45:F49"/>
-    <mergeCell ref="F50:F55"/>
-    <mergeCell ref="F56:F62"/>
-    <mergeCell ref="F63:F69"/>
-    <mergeCell ref="F70:F90"/>
-    <mergeCell ref="F91:F94"/>
-    <mergeCell ref="F95:F101"/>
-    <mergeCell ref="F102:F108"/>
-    <mergeCell ref="F109:F113"/>
-    <mergeCell ref="F114:F119"/>
-    <mergeCell ref="F120:F127"/>
-    <mergeCell ref="F128:F136"/>
-    <mergeCell ref="F137:F139"/>
-    <mergeCell ref="F140:F145"/>
-    <mergeCell ref="F146:F151"/>
-    <mergeCell ref="F152:F153"/>
+    <mergeCell ref="F50:F57"/>
+    <mergeCell ref="F58:F64"/>
+    <mergeCell ref="F65:F71"/>
+    <mergeCell ref="F72:F92"/>
+    <mergeCell ref="F93:F96"/>
+    <mergeCell ref="F97:F103"/>
+    <mergeCell ref="F104:F110"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="F116:F121"/>
+    <mergeCell ref="F122:F129"/>
+    <mergeCell ref="F130:F138"/>
+    <mergeCell ref="F139:F141"/>
+    <mergeCell ref="F142:F147"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="F154:F155"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -4832,37 +4880,37 @@
     <mergeCell ref="G41:G42"/>
     <mergeCell ref="G43:G44"/>
     <mergeCell ref="G45:G49"/>
-    <mergeCell ref="G50:G55"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="G70:G78"/>
-    <mergeCell ref="G79:G81"/>
-    <mergeCell ref="G82:G90"/>
-    <mergeCell ref="G91:G94"/>
-    <mergeCell ref="G95:G97"/>
-    <mergeCell ref="G99:G101"/>
-    <mergeCell ref="G102:G104"/>
-    <mergeCell ref="G106:G108"/>
-    <mergeCell ref="G109:G113"/>
-    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="G50:G57"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="G72:G80"/>
+    <mergeCell ref="G81:G83"/>
+    <mergeCell ref="G84:G92"/>
+    <mergeCell ref="G93:G96"/>
+    <mergeCell ref="G97:G99"/>
+    <mergeCell ref="G101:G103"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="G111:G115"/>
     <mergeCell ref="G116:G117"/>
     <mergeCell ref="G118:G119"/>
     <mergeCell ref="G120:G121"/>
     <mergeCell ref="G122:G123"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="G137:G139"/>
-    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="G127:G128"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="G133:G134"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="G139:G141"/>
     <mergeCell ref="G142:G143"/>
     <mergeCell ref="G144:G145"/>
     <mergeCell ref="G146:G147"/>
     <mergeCell ref="G148:G149"/>
     <mergeCell ref="G150:G151"/>
     <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G154:G155"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -4874,40 +4922,40 @@
     <mergeCell ref="H41:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="H45:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H58"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="H63:H65"/>
-    <mergeCell ref="H67:H69"/>
-    <mergeCell ref="H70:H72"/>
-    <mergeCell ref="H73:H75"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H82:H84"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="H88:H90"/>
-    <mergeCell ref="H91:H94"/>
-    <mergeCell ref="H95:H97"/>
-    <mergeCell ref="H99:H101"/>
-    <mergeCell ref="H102:H104"/>
-    <mergeCell ref="H106:H108"/>
-    <mergeCell ref="H109:H113"/>
-    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="H50:H57"/>
+    <mergeCell ref="H58:H60"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="H69:H71"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="H75:H77"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="H87:H89"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="H93:H96"/>
+    <mergeCell ref="H97:H99"/>
+    <mergeCell ref="H101:H103"/>
+    <mergeCell ref="H104:H106"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="H111:H115"/>
     <mergeCell ref="H116:H117"/>
     <mergeCell ref="H118:H119"/>
     <mergeCell ref="H120:H121"/>
     <mergeCell ref="H122:H123"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="H137:H139"/>
-    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="H136:H137"/>
+    <mergeCell ref="H139:H141"/>
     <mergeCell ref="H142:H143"/>
     <mergeCell ref="H144:H145"/>
     <mergeCell ref="H146:H147"/>
     <mergeCell ref="H148:H149"/>
     <mergeCell ref="H150:H151"/>
     <mergeCell ref="H152:H153"/>
+    <mergeCell ref="H154:H155"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -4920,41 +4968,41 @@
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="I43:I44"/>
     <mergeCell ref="I45:I49"/>
-    <mergeCell ref="I50:I52"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="I56:I58"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="I63:I65"/>
-    <mergeCell ref="I67:I69"/>
-    <mergeCell ref="I70:I72"/>
-    <mergeCell ref="I73:I75"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="I85:I87"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="I91:I94"/>
-    <mergeCell ref="I95:I97"/>
-    <mergeCell ref="I99:I101"/>
-    <mergeCell ref="I102:I104"/>
-    <mergeCell ref="I106:I108"/>
-    <mergeCell ref="I109:I113"/>
-    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="I50:I53"/>
+    <mergeCell ref="I54:I57"/>
+    <mergeCell ref="I58:I60"/>
+    <mergeCell ref="I62:I64"/>
+    <mergeCell ref="I65:I67"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="I72:I74"/>
+    <mergeCell ref="I75:I77"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="I87:I89"/>
+    <mergeCell ref="I90:I92"/>
+    <mergeCell ref="I93:I96"/>
+    <mergeCell ref="I97:I99"/>
+    <mergeCell ref="I101:I103"/>
+    <mergeCell ref="I104:I106"/>
+    <mergeCell ref="I108:I110"/>
+    <mergeCell ref="I111:I115"/>
     <mergeCell ref="I116:I117"/>
     <mergeCell ref="I118:I119"/>
     <mergeCell ref="I120:I121"/>
     <mergeCell ref="I122:I123"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="I134:I135"/>
-    <mergeCell ref="I137:I139"/>
-    <mergeCell ref="I140:I141"/>
+    <mergeCell ref="I124:I125"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="I139:I141"/>
     <mergeCell ref="I142:I143"/>
     <mergeCell ref="I144:I145"/>
     <mergeCell ref="I146:I147"/>
     <mergeCell ref="I148:I149"/>
     <mergeCell ref="I150:I151"/>
     <mergeCell ref="I152:I153"/>
+    <mergeCell ref="I154:I155"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -4967,41 +5015,41 @@
     <mergeCell ref="J41:J42"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="J45:J49"/>
-    <mergeCell ref="J50:J52"/>
-    <mergeCell ref="J53:J55"/>
-    <mergeCell ref="J56:J58"/>
-    <mergeCell ref="J60:J62"/>
-    <mergeCell ref="J63:J65"/>
-    <mergeCell ref="J67:J69"/>
-    <mergeCell ref="J70:J72"/>
-    <mergeCell ref="J73:J75"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="J82:J84"/>
-    <mergeCell ref="J85:J87"/>
-    <mergeCell ref="J88:J90"/>
-    <mergeCell ref="J91:J94"/>
-    <mergeCell ref="J95:J97"/>
-    <mergeCell ref="J99:J101"/>
-    <mergeCell ref="J102:J104"/>
-    <mergeCell ref="J106:J108"/>
-    <mergeCell ref="J109:J113"/>
-    <mergeCell ref="J114:J115"/>
+    <mergeCell ref="J50:J53"/>
+    <mergeCell ref="J54:J57"/>
+    <mergeCell ref="J58:J60"/>
+    <mergeCell ref="J62:J64"/>
+    <mergeCell ref="J65:J67"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="J75:J77"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="J87:J89"/>
+    <mergeCell ref="J90:J92"/>
+    <mergeCell ref="J93:J96"/>
+    <mergeCell ref="J97:J99"/>
+    <mergeCell ref="J101:J103"/>
+    <mergeCell ref="J104:J106"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J111:J115"/>
     <mergeCell ref="J116:J117"/>
     <mergeCell ref="J118:J119"/>
     <mergeCell ref="J120:J121"/>
     <mergeCell ref="J122:J123"/>
-    <mergeCell ref="J125:J126"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="J131:J132"/>
-    <mergeCell ref="J134:J135"/>
-    <mergeCell ref="J137:J139"/>
-    <mergeCell ref="J140:J141"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="J127:J128"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="J133:J134"/>
+    <mergeCell ref="J136:J137"/>
+    <mergeCell ref="J139:J141"/>
     <mergeCell ref="J142:J143"/>
     <mergeCell ref="J144:J145"/>
     <mergeCell ref="J146:J147"/>
     <mergeCell ref="J148:J149"/>
     <mergeCell ref="J150:J151"/>
     <mergeCell ref="J152:J153"/>
+    <mergeCell ref="J154:J155"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="164">
   <si>
     <t>variable_id</t>
   </si>
@@ -256,6 +256,12 @@
     <t>REMO2020-2-2-MR2</t>
   </si>
   <si>
+    <t>REMO2020-2-2-iMOVE</t>
+  </si>
+  <si>
+    <t>REMO2020-2-2-iMOVE-LUC</t>
+  </si>
+  <si>
     <t>HCLIM43-ALADIN</t>
   </si>
   <si>
@@ -358,6 +364,9 @@
     <t>v20241120</t>
   </si>
   <si>
+    <t>v20250515</t>
+  </si>
+  <si>
     <t>v20241205</t>
   </si>
   <si>
@@ -445,7 +454,7 @@
     <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'od550aer', 'pr', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'tas', 'tasmax', 'tasmin', 'mrro', 'mrros', 'mrso', 'prsn', 'rldscs', 'rlutcs', 'rsdscs', 'rsutcs', 'snc', 'snd', 'snw', 'zg500']</t>
   </si>
   <si>
-    <t>['pr', 'sfcWind']</t>
+    <t>['pr', 'sfcWind', 'tas']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
@@ -454,10 +463,10 @@
     <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
-    <t>['pr', 'sfcWind', 'tas']</t>
-  </si>
-  <si>
     <t>['orog', 'sftlaf', 'sftlf']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
@@ -854,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -864,7 +873,8 @@
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="10" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="12" width="11.7109375" customWidth="1"/>
     <col min="13" max="13" width="303.7109375" customWidth="1"/>
   </cols>
@@ -939,16 +949,16 @@
         <v>61</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -966,16 +976,16 @@
         <v>61</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -999,16 +1009,16 @@
         <v>62</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1026,16 +1036,16 @@
         <v>62</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1059,16 +1069,16 @@
         <v>63</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1083,13 +1093,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1105,16 +1115,16 @@
         <v>64</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1129,13 +1139,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1159,16 +1169,16 @@
         <v>65</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1183,13 +1193,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1213,16 +1223,16 @@
         <v>66</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1240,16 +1250,16 @@
         <v>66</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1273,16 +1283,16 @@
         <v>67</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1306,16 +1316,16 @@
         <v>68</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1330,13 +1340,13 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1352,10 +1362,10 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1379,16 +1389,16 @@
         <v>69</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1403,13 +1413,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1433,16 +1443,16 @@
         <v>70</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1460,16 +1470,16 @@
         <v>70</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1493,16 +1503,16 @@
         <v>71</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M22" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1517,13 +1527,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1547,16 +1557,16 @@
         <v>72</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1574,16 +1584,16 @@
         <v>72</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1615,16 +1625,16 @@
         <v>73</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1648,16 +1658,16 @@
         <v>74</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1672,13 +1682,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M28" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1693,13 +1703,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1714,13 +1724,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M30" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1735,13 +1745,13 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M31" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1765,16 +1775,16 @@
         <v>75</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M32" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1789,13 +1799,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1810,13 +1820,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M34" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1831,13 +1841,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M35" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1852,13 +1862,13 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1882,16 +1892,16 @@
         <v>76</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1906,13 +1916,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1927,13 +1937,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M39" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1948,13 +1958,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1978,16 +1988,16 @@
         <v>77</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M41" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2002,13 +2012,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M42" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2028,16 +2038,16 @@
         <v>77</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M43" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2052,13 +2062,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M44" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2080,16 +2090,16 @@
         <v>77</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M45" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2104,13 +2114,13 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M46" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2125,13 +2135,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M47" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2146,13 +2156,13 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M48" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2167,13 +2177,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M49" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2197,16 +2207,16 @@
         <v>78</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2221,13 +2231,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M51" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2242,13 +2252,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M52" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2263,13 +2273,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M53" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2285,13 +2295,13 @@
         <v>79</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M54" t="s">
         <v>146</v>
@@ -2309,13 +2319,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M55" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2330,13 +2340,13 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M56" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2351,13 +2361,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M57" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2365,32 +2375,24 @@
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2402,16 +2404,20 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="I59" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M59" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2419,20 +2425,32 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
+      <c r="E60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K60" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M60" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2442,26 +2460,18 @@
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M61" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2471,26 +2481,18 @@
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M62" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2500,18 +2502,26 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K63" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M63" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2521,18 +2531,26 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K64" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2540,32 +2558,20 @@
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M65" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2580,13 +2586,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M66" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2594,20 +2600,32 @@
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="E67" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K67" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2617,26 +2635,18 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M68" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2646,26 +2656,18 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M69" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2675,18 +2677,26 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="G70" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M70" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2696,18 +2706,26 @@
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="G71" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K71" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M71" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2716,29 +2734,19 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M72" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2753,13 +2761,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M73" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2768,19 +2776,29 @@
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K74" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M74" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2791,23 +2809,17 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M75" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2822,13 +2834,13 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M76" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2839,17 +2851,23 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="H77" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K77" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M77" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2860,23 +2878,17 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-      <c r="H78" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M78" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2891,13 +2903,13 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M79" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2908,17 +2920,23 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="H80" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K80" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M80" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2928,26 +2946,18 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M81" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2958,23 +2968,17 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M82" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2984,24 +2988,26 @@
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
+      <c r="G83" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="H83" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M83" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -3011,26 +3017,24 @@
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K84" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M84" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3041,17 +3045,23 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="H85" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K85" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M85" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3061,18 +3071,26 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
+      <c r="G86" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K86" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M86" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3083,23 +3101,17 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
-      <c r="H87" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M87" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3114,13 +3126,13 @@
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M88" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3131,17 +3143,23 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
+      <c r="H89" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K89" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M89" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3152,23 +3170,17 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
-      <c r="H90" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M90" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3183,13 +3195,13 @@
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M91" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3200,17 +3212,23 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
+      <c r="H92" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K92" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M92" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3219,29 +3237,19 @@
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M93" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3256,13 +3264,13 @@
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M94" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3271,19 +3279,29 @@
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
+      <c r="F95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K95" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M95" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3298,10 +3316,10 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M96" t="s">
         <v>151</v>
@@ -3313,29 +3331,19 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M97" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3350,13 +3358,13 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M98" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3365,19 +3373,29 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K99" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3387,26 +3405,18 @@
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M100" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3416,26 +3426,18 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M101" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3445,18 +3447,26 @@
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
+      <c r="G102" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K102" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M102" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3466,18 +3476,26 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+      <c r="G103" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K103" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M103" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3486,29 +3504,19 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M104" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3523,13 +3531,13 @@
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M105" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3538,19 +3546,29 @@
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
+      <c r="F106" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K106" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M106" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3560,26 +3578,18 @@
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M107" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3589,26 +3599,18 @@
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M108" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3618,18 +3620,26 @@
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
+      <c r="G109" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K109" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M109" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3639,18 +3649,26 @@
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
+      <c r="G110" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K110" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M110" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3658,32 +3676,20 @@
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="E111" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M111" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3698,13 +3704,13 @@
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M112" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3712,20 +3718,32 @@
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
+      <c r="E113" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K113" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M113" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3740,13 +3758,13 @@
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M114" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3761,13 +3779,13 @@
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M115" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3775,32 +3793,20 @@
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="E116" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
       <c r="K116" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M116" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3815,13 +3821,13 @@
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M117" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3829,28 +3835,32 @@
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
+      <c r="E118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G118" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M118" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3865,13 +3875,13 @@
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M119" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3882,25 +3892,25 @@
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M120" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3915,13 +3925,13 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M121" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3930,29 +3940,27 @@
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M122" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3967,13 +3975,13 @@
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M123" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3982,27 +3990,29 @@
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
+      <c r="F124" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G124" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M124" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4017,13 +4027,13 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M125" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4034,25 +4044,25 @@
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M126" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4062,26 +4072,18 @@
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
-      <c r="G127" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
       <c r="K127" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M127" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4091,18 +4093,26 @@
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
+      <c r="G128" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K128" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M128" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4113,25 +4123,25 @@
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M129" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4140,29 +4150,19 @@
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
       <c r="K130" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M130" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4172,18 +4172,26 @@
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
+      <c r="G131" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K131" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M131" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4192,27 +4200,29 @@
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
+      <c r="F132" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G132" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M132" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4222,26 +4232,18 @@
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
-      <c r="G133" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
       <c r="K133" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M133" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4251,18 +4253,26 @@
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
+      <c r="G134" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K134" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M134" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4273,25 +4283,25 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M135" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4301,26 +4311,18 @@
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
       <c r="K136" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M136" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4330,18 +4332,26 @@
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
+      <c r="G137" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K137" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M137" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4352,25 +4362,25 @@
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M138" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4379,29 +4389,19 @@
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
       <c r="K139" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M139" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4411,18 +4411,26 @@
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
+      <c r="G140" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K140" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M140" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4431,19 +4439,29 @@
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1"/>
+      <c r="F141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K141" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M141" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4452,29 +4470,19 @@
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
       <c r="K142" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M142" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4489,13 +4497,13 @@
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
       <c r="K143" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M143" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4504,27 +4512,29 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="1"/>
+      <c r="F144" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="G144" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M144" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4539,13 +4549,13 @@
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
       <c r="K145" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M145" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4556,25 +4566,25 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M146" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4589,13 +4599,13 @@
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
       <c r="K147" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M147" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4604,29 +4614,27 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F148" s="1"/>
       <c r="G148" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M148" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4641,13 +4649,13 @@
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
       <c r="K149" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M149" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4656,27 +4664,29 @@
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
-      <c r="F150" s="1"/>
+      <c r="F150" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G150" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M150" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4691,13 +4701,13 @@
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M151" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4708,25 +4718,25 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M152" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4741,13 +4751,13 @@
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
       <c r="K153" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M153" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4755,32 +4765,28 @@
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
-      <c r="E154" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
       <c r="G154" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M154" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4795,25 +4801,79 @@
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
       <c r="K155" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M155" t="s">
-        <v>160</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M156" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
+      <c r="K157" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M157" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="245">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A155"/>
+    <mergeCell ref="A26:A157"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B155"/>
+    <mergeCell ref="B26:B157"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C155"/>
+    <mergeCell ref="C26:C157"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D155"/>
+    <mergeCell ref="D26:D157"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4828,12 +4888,12 @@
     <mergeCell ref="E32:E36"/>
     <mergeCell ref="E37:E40"/>
     <mergeCell ref="E41:E49"/>
-    <mergeCell ref="E50:E57"/>
-    <mergeCell ref="E58:E64"/>
-    <mergeCell ref="E65:E110"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E116:E153"/>
-    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="E50:E59"/>
+    <mergeCell ref="E60:E66"/>
+    <mergeCell ref="E67:E112"/>
+    <mergeCell ref="E113:E117"/>
+    <mergeCell ref="E118:E155"/>
+    <mergeCell ref="E156:E157"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -4849,21 +4909,21 @@
     <mergeCell ref="F37:F40"/>
     <mergeCell ref="F41:F44"/>
     <mergeCell ref="F45:F49"/>
-    <mergeCell ref="F50:F57"/>
-    <mergeCell ref="F58:F64"/>
-    <mergeCell ref="F65:F71"/>
-    <mergeCell ref="F72:F92"/>
-    <mergeCell ref="F93:F96"/>
-    <mergeCell ref="F97:F103"/>
-    <mergeCell ref="F104:F110"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="F116:F121"/>
-    <mergeCell ref="F122:F129"/>
-    <mergeCell ref="F130:F138"/>
-    <mergeCell ref="F139:F141"/>
-    <mergeCell ref="F142:F147"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="F154:F155"/>
+    <mergeCell ref="F50:F59"/>
+    <mergeCell ref="F60:F66"/>
+    <mergeCell ref="F67:F73"/>
+    <mergeCell ref="F74:F94"/>
+    <mergeCell ref="F95:F98"/>
+    <mergeCell ref="F99:F105"/>
+    <mergeCell ref="F106:F112"/>
+    <mergeCell ref="F113:F117"/>
+    <mergeCell ref="F118:F123"/>
+    <mergeCell ref="F124:F131"/>
+    <mergeCell ref="F132:F140"/>
+    <mergeCell ref="F141:F143"/>
+    <mergeCell ref="F144:F149"/>
+    <mergeCell ref="F150:F155"/>
+    <mergeCell ref="F156:F157"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -4880,37 +4940,37 @@
     <mergeCell ref="G41:G42"/>
     <mergeCell ref="G43:G44"/>
     <mergeCell ref="G45:G49"/>
-    <mergeCell ref="G50:G57"/>
-    <mergeCell ref="G58:G60"/>
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="G72:G80"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="G84:G92"/>
-    <mergeCell ref="G93:G96"/>
-    <mergeCell ref="G97:G99"/>
-    <mergeCell ref="G101:G103"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="G50:G59"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="G67:G69"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="G74:G82"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="G86:G94"/>
+    <mergeCell ref="G95:G98"/>
+    <mergeCell ref="G99:G101"/>
+    <mergeCell ref="G103:G105"/>
+    <mergeCell ref="G106:G108"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="G113:G117"/>
     <mergeCell ref="G118:G119"/>
     <mergeCell ref="G120:G121"/>
     <mergeCell ref="G122:G123"/>
     <mergeCell ref="G124:G125"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="G133:G134"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="G139:G141"/>
-    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="G129:G130"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G135:G136"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G141:G143"/>
     <mergeCell ref="G144:G145"/>
     <mergeCell ref="G146:G147"/>
     <mergeCell ref="G148:G149"/>
     <mergeCell ref="G150:G151"/>
     <mergeCell ref="G152:G153"/>
     <mergeCell ref="G154:G155"/>
+    <mergeCell ref="G156:G157"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -4922,40 +4982,40 @@
     <mergeCell ref="H41:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="H45:H49"/>
-    <mergeCell ref="H50:H57"/>
-    <mergeCell ref="H58:H60"/>
-    <mergeCell ref="H62:H64"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="H75:H77"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="H84:H86"/>
-    <mergeCell ref="H87:H89"/>
-    <mergeCell ref="H90:H92"/>
-    <mergeCell ref="H93:H96"/>
-    <mergeCell ref="H97:H99"/>
-    <mergeCell ref="H101:H103"/>
-    <mergeCell ref="H104:H106"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="H111:H115"/>
-    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="H50:H59"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="H67:H69"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="H86:H88"/>
+    <mergeCell ref="H89:H91"/>
+    <mergeCell ref="H92:H94"/>
+    <mergeCell ref="H95:H98"/>
+    <mergeCell ref="H99:H101"/>
+    <mergeCell ref="H103:H105"/>
+    <mergeCell ref="H106:H108"/>
+    <mergeCell ref="H110:H112"/>
+    <mergeCell ref="H113:H117"/>
     <mergeCell ref="H118:H119"/>
     <mergeCell ref="H120:H121"/>
     <mergeCell ref="H122:H123"/>
     <mergeCell ref="H124:H125"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="H136:H137"/>
-    <mergeCell ref="H139:H141"/>
-    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="H126:H127"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="H132:H133"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="H141:H143"/>
     <mergeCell ref="H144:H145"/>
     <mergeCell ref="H146:H147"/>
     <mergeCell ref="H148:H149"/>
     <mergeCell ref="H150:H151"/>
     <mergeCell ref="H152:H153"/>
     <mergeCell ref="H154:H155"/>
+    <mergeCell ref="H156:H157"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -4970,39 +5030,39 @@
     <mergeCell ref="I45:I49"/>
     <mergeCell ref="I50:I53"/>
     <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I58:I60"/>
-    <mergeCell ref="I62:I64"/>
-    <mergeCell ref="I65:I67"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="I72:I74"/>
-    <mergeCell ref="I75:I77"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="I84:I86"/>
-    <mergeCell ref="I87:I89"/>
-    <mergeCell ref="I90:I92"/>
-    <mergeCell ref="I93:I96"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="I101:I103"/>
-    <mergeCell ref="I104:I106"/>
-    <mergeCell ref="I108:I110"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I67:I69"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="I77:I79"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="I86:I88"/>
+    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="I92:I94"/>
+    <mergeCell ref="I95:I98"/>
+    <mergeCell ref="I99:I101"/>
+    <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="I110:I112"/>
+    <mergeCell ref="I113:I117"/>
     <mergeCell ref="I118:I119"/>
     <mergeCell ref="I120:I121"/>
     <mergeCell ref="I122:I123"/>
     <mergeCell ref="I124:I125"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="I139:I141"/>
-    <mergeCell ref="I142:I143"/>
+    <mergeCell ref="I126:I127"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="I132:I133"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="I141:I143"/>
     <mergeCell ref="I144:I145"/>
     <mergeCell ref="I146:I147"/>
     <mergeCell ref="I148:I149"/>
     <mergeCell ref="I150:I151"/>
     <mergeCell ref="I152:I153"/>
     <mergeCell ref="I154:I155"/>
+    <mergeCell ref="I156:I157"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -5017,39 +5077,39 @@
     <mergeCell ref="J45:J49"/>
     <mergeCell ref="J50:J53"/>
     <mergeCell ref="J54:J57"/>
-    <mergeCell ref="J58:J60"/>
-    <mergeCell ref="J62:J64"/>
-    <mergeCell ref="J65:J67"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="J72:J74"/>
-    <mergeCell ref="J75:J77"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="J84:J86"/>
-    <mergeCell ref="J87:J89"/>
-    <mergeCell ref="J90:J92"/>
-    <mergeCell ref="J93:J96"/>
-    <mergeCell ref="J97:J99"/>
-    <mergeCell ref="J101:J103"/>
-    <mergeCell ref="J104:J106"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J111:J115"/>
-    <mergeCell ref="J116:J117"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J67:J69"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="J77:J79"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="J86:J88"/>
+    <mergeCell ref="J89:J91"/>
+    <mergeCell ref="J92:J94"/>
+    <mergeCell ref="J95:J98"/>
+    <mergeCell ref="J99:J101"/>
+    <mergeCell ref="J103:J105"/>
+    <mergeCell ref="J106:J108"/>
+    <mergeCell ref="J110:J112"/>
+    <mergeCell ref="J113:J117"/>
     <mergeCell ref="J118:J119"/>
     <mergeCell ref="J120:J121"/>
     <mergeCell ref="J122:J123"/>
     <mergeCell ref="J124:J125"/>
-    <mergeCell ref="J127:J128"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="J133:J134"/>
-    <mergeCell ref="J136:J137"/>
-    <mergeCell ref="J139:J141"/>
-    <mergeCell ref="J142:J143"/>
+    <mergeCell ref="J126:J127"/>
+    <mergeCell ref="J129:J130"/>
+    <mergeCell ref="J132:J133"/>
+    <mergeCell ref="J135:J136"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="J141:J143"/>
     <mergeCell ref="J144:J145"/>
     <mergeCell ref="J146:J147"/>
     <mergeCell ref="J148:J149"/>
     <mergeCell ref="J150:J151"/>
     <mergeCell ref="J152:J153"/>
     <mergeCell ref="J154:J155"/>
+    <mergeCell ref="J156:J157"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="163">
   <si>
     <t>variable_id</t>
   </si>
@@ -430,9 +430,6 @@
     <t>['zg500', 'clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'od550aer', 'pr', 'prsn', 'psl', 'rlds', 'rldscs', 'rlut', 'rlutcs', 'rsds', 'rsdscs', 'rsut', 'rsutcs', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
-    <t>['hurs']</t>
-  </si>
-  <si>
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'uas', 'vas']</t>
   </si>
   <si>
@@ -466,7 +463,7 @@
     <t>['orog', 'sftlaf', 'sftlf']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
@@ -863,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1895,7 +1892,7 @@
         <v>87</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>112</v>
@@ -1916,13 +1913,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>112</v>
       </c>
       <c r="M38" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1937,13 +1934,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="M39" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1951,17 +1948,29 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M40" t="s">
         <v>139</v>
@@ -1972,32 +1981,20 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M41" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2007,18 +2004,26 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K42" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M42" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2028,26 +2033,18 @@
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M43" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2056,19 +2053,29 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M44" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2077,23 +2084,13 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>114</v>
@@ -2114,7 +2111,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>114</v>
@@ -2135,7 +2132,7 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>114</v>
@@ -2156,7 +2153,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>114</v>
@@ -2170,17 +2167,29 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K49" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s">
         <v>145</v>
@@ -2191,26 +2200,14 @@
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>115</v>
@@ -2231,13 +2228,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M51" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2252,13 +2249,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M52" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2270,16 +2267,20 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
+      <c r="I53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K53" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M53" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2291,14 +2292,10 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>115</v>
@@ -2319,13 +2316,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2340,13 +2337,13 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>115</v>
       </c>
       <c r="M56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2358,16 +2355,20 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
+      <c r="I57" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K57" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M57" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2379,20 +2380,16 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2404,20 +2401,16 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M59" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2425,32 +2418,20 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2462,16 +2443,20 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
+      <c r="I61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K61" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M61" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2486,13 +2471,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M62" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2502,23 +2487,15 @@
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M63" t="s">
         <v>121</v>
@@ -2531,26 +2508,18 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M64" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2558,20 +2527,32 @@
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K65" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M65" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2586,13 +2567,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M66" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2600,26 +2581,14 @@
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>117</v>
@@ -2635,10 +2604,18 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K68" s="1" t="s">
         <v>88</v>
       </c>
@@ -2656,18 +2633,26 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K69" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M69" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2677,18 +2662,10 @@
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
         <v>88</v>
       </c>
@@ -2706,20 +2683,12 @@
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>117</v>
@@ -2733,20 +2702,32 @@
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="E72" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K72" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M72" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2761,13 +2742,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M73" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2776,23 +2757,13 @@
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>117</v>
@@ -2808,10 +2779,18 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K75" s="1" t="s">
         <v>88</v>
       </c>
@@ -2829,18 +2808,26 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="G76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K76" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2851,23 +2838,17 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-      <c r="H77" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M77" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2882,13 +2863,13 @@
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M78" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2897,19 +2878,29 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="F79" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K79" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M79" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2920,23 +2911,17 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M80" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2951,13 +2936,13 @@
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M81" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2968,17 +2953,23 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+      <c r="H82" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K82" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M82" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2988,18 +2979,10 @@
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
         <v>88</v>
       </c>
@@ -3018,23 +3001,17 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M84" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3055,13 +3032,13 @@
         <v>87</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M85" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3071,26 +3048,18 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M86" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3105,13 +3074,13 @@
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M87" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3121,18 +3090,26 @@
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
+      <c r="G88" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K88" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M88" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3153,13 +3130,13 @@
         <v>87</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M89" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3170,9 +3147,15 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
+      <c r="H90" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K90" s="1" t="s">
         <v>88</v>
       </c>
@@ -3190,18 +3173,26 @@
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+      <c r="G91" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K91" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M91" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3212,23 +3203,17 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
-      <c r="H92" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M92" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3243,13 +3228,13 @@
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M93" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3260,17 +3245,23 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
+      <c r="H94" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K94" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M94" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3279,29 +3270,19 @@
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M95" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3316,7 +3297,7 @@
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>117</v>
@@ -3333,17 +3314,23 @@
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
+      <c r="H97" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K97" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M97" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3358,13 +3345,13 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M98" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3373,23 +3360,13 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>117</v>
@@ -3404,19 +3381,29 @@
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
+      <c r="F100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K100" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M100" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3431,13 +3418,13 @@
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M101" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3447,18 +3434,10 @@
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
-      <c r="G102" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
       <c r="K102" s="1" t="s">
         <v>88</v>
       </c>
@@ -3466,7 +3445,7 @@
         <v>117</v>
       </c>
       <c r="M102" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3476,26 +3455,18 @@
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M103" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3504,19 +3475,29 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
+      <c r="F104" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K104" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M104" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3531,13 +3512,13 @@
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M105" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3546,23 +3527,13 @@
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>117</v>
@@ -3578,10 +3549,18 @@
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
+      <c r="G107" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K107" s="1" t="s">
         <v>88</v>
       </c>
@@ -3599,18 +3578,26 @@
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
+      <c r="G108" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K108" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M108" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3620,18 +3607,10 @@
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
-      <c r="G109" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
         <v>88</v>
       </c>
@@ -3649,20 +3628,12 @@
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
-      <c r="G110" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
       <c r="K110" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>117</v>
@@ -3677,19 +3648,29 @@
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
+      <c r="F111" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K111" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M111" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3704,13 +3685,13 @@
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>117</v>
       </c>
       <c r="M112" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3718,32 +3699,20 @@
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="E113" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
       <c r="K113" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M113" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3753,18 +3722,26 @@
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
+      <c r="G114" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K114" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M114" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3774,18 +3751,26 @@
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
+      <c r="G115" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K115" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M115" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3803,10 +3788,10 @@
         <v>88</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M116" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3824,10 +3809,10 @@
         <v>89</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M117" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3836,31 +3821,31 @@
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>87</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M118" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3875,13 +3860,13 @@
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M119" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3891,26 +3876,18 @@
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
-      <c r="G120" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
       <c r="K120" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M120" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3928,10 +3905,10 @@
         <v>88</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M121" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3941,26 +3918,18 @@
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
-      <c r="G122" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
       <c r="K122" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M122" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3968,20 +3937,32 @@
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
+      <c r="E123" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K123" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L123" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M123" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3990,29 +3971,19 @@
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
       <c r="K124" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L124" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M124" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4022,18 +3993,26 @@
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
+      <c r="G125" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K125" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M125" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4043,26 +4022,18 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
       <c r="K126" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M126" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4072,18 +4043,26 @@
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
+      <c r="G127" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K127" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L127" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M127" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4093,26 +4072,18 @@
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
-      <c r="G128" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
       <c r="K128" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L128" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M128" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4121,9 +4092,11 @@
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
+      <c r="F129" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G129" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>57</v>
@@ -4141,7 +4114,7 @@
         <v>119</v>
       </c>
       <c r="M129" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4162,7 +4135,7 @@
         <v>119</v>
       </c>
       <c r="M130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4173,7 +4146,7 @@
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>57</v>
@@ -4191,7 +4164,7 @@
         <v>119</v>
       </c>
       <c r="M131" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4200,29 +4173,19 @@
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
       <c r="K132" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L132" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M132" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4232,18 +4195,26 @@
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
-      <c r="G133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
+      <c r="G133" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K133" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L133" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M133" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4254,7 +4225,7 @@
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>57</v>
@@ -4272,7 +4243,7 @@
         <v>119</v>
       </c>
       <c r="M134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4282,26 +4253,18 @@
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
-      <c r="G135" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
       <c r="K135" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L135" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M135" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4311,18 +4274,26 @@
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
+      <c r="G136" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K136" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M136" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4331,9 +4302,11 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
+      <c r="F137" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G137" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>57</v>
@@ -4351,7 +4324,7 @@
         <v>119</v>
       </c>
       <c r="M137" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4361,26 +4334,18 @@
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
       <c r="K138" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M138" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4390,18 +4355,26 @@
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
+      <c r="G139" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K139" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M139" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4412,7 +4385,7 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>57</v>
@@ -4430,7 +4403,7 @@
         <v>119</v>
       </c>
       <c r="M140" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4439,29 +4412,19 @@
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
       <c r="K141" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M141" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4471,18 +4434,26 @@
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
-      <c r="G142" s="1"/>
-      <c r="H142" s="1"/>
-      <c r="I142" s="1"/>
-      <c r="J142" s="1"/>
+      <c r="G142" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K142" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M142" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4492,18 +4463,26 @@
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
-      <c r="G143" s="1"/>
-      <c r="H143" s="1"/>
-      <c r="I143" s="1"/>
-      <c r="J143" s="1"/>
+      <c r="G143" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K143" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L143" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M143" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4512,29 +4491,19 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
       <c r="K144" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M144" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4544,18 +4513,26 @@
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
-      <c r="H145" s="1"/>
-      <c r="I145" s="1"/>
-      <c r="J145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K145" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M145" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4564,9 +4541,11 @@
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="1"/>
+      <c r="F146" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G146" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>57</v>
@@ -4584,7 +4563,7 @@
         <v>119</v>
       </c>
       <c r="M146" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4605,7 +4584,7 @@
         <v>119</v>
       </c>
       <c r="M147" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4615,26 +4594,18 @@
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
-      <c r="G148" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H148" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
       <c r="K148" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L148" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M148" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4643,19 +4614,29 @@
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
-      <c r="H149" s="1"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="1"/>
+      <c r="F149" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K149" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L149" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M149" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4664,29 +4645,19 @@
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
-      <c r="F150" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
       <c r="K150" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L150" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M150" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4696,18 +4667,26 @@
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="1"/>
+      <c r="G151" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K151" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L151" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M151" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4717,26 +4696,18 @@
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
-      <c r="G152" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
       <c r="K152" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L152" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M152" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4746,18 +4717,26 @@
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
-      <c r="H153" s="1"/>
-      <c r="I153" s="1"/>
-      <c r="J153" s="1"/>
+      <c r="G153" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K153" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L153" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M153" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4767,26 +4746,18 @@
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
-      <c r="G154" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
       <c r="K154" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M154" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4795,19 +4766,29 @@
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
-      <c r="H155" s="1"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="1"/>
+      <c r="F155" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K155" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L155" s="1" t="s">
         <v>119</v>
       </c>
       <c r="M155" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -4815,32 +4796,20 @@
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
-      <c r="E156" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
       <c r="K156" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M156" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -4850,30 +4819,163 @@
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="1"/>
-      <c r="H157" s="1"/>
-      <c r="I157" s="1"/>
-      <c r="J157" s="1"/>
+      <c r="G157" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="K157" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M157" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="J158" s="1"/>
+      <c r="K158" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M158" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J159" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M159" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L160" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M160" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L161" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M161" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L157" s="1" t="s">
+      <c r="L162" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="M157" t="s">
-        <v>163</v>
+      <c r="M162" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="245">
+  <mergeCells count="249">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A157"/>
+    <mergeCell ref="A26:A162"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B157"/>
+    <mergeCell ref="B26:B162"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C157"/>
+    <mergeCell ref="C26:C162"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D157"/>
+    <mergeCell ref="D26:D162"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4886,14 +4988,14 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E27:E31"/>
     <mergeCell ref="E32:E36"/>
-    <mergeCell ref="E37:E40"/>
-    <mergeCell ref="E41:E49"/>
-    <mergeCell ref="E50:E59"/>
-    <mergeCell ref="E60:E66"/>
-    <mergeCell ref="E67:E112"/>
-    <mergeCell ref="E113:E117"/>
-    <mergeCell ref="E118:E155"/>
-    <mergeCell ref="E156:E157"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E40:E48"/>
+    <mergeCell ref="E49:E64"/>
+    <mergeCell ref="E65:E71"/>
+    <mergeCell ref="E72:E117"/>
+    <mergeCell ref="E118:E122"/>
+    <mergeCell ref="E123:E160"/>
+    <mergeCell ref="E161:E162"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -4906,24 +5008,24 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="F27:F31"/>
     <mergeCell ref="F32:F36"/>
-    <mergeCell ref="F37:F40"/>
-    <mergeCell ref="F41:F44"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="F50:F59"/>
-    <mergeCell ref="F60:F66"/>
-    <mergeCell ref="F67:F73"/>
-    <mergeCell ref="F74:F94"/>
-    <mergeCell ref="F95:F98"/>
-    <mergeCell ref="F99:F105"/>
-    <mergeCell ref="F106:F112"/>
-    <mergeCell ref="F113:F117"/>
-    <mergeCell ref="F118:F123"/>
-    <mergeCell ref="F124:F131"/>
-    <mergeCell ref="F132:F140"/>
-    <mergeCell ref="F141:F143"/>
-    <mergeCell ref="F144:F149"/>
-    <mergeCell ref="F150:F155"/>
-    <mergeCell ref="F156:F157"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="F40:F43"/>
+    <mergeCell ref="F44:F48"/>
+    <mergeCell ref="F49:F64"/>
+    <mergeCell ref="F65:F71"/>
+    <mergeCell ref="F72:F78"/>
+    <mergeCell ref="F79:F99"/>
+    <mergeCell ref="F100:F103"/>
+    <mergeCell ref="F104:F110"/>
+    <mergeCell ref="F111:F117"/>
+    <mergeCell ref="F118:F122"/>
+    <mergeCell ref="F123:F128"/>
+    <mergeCell ref="F129:F136"/>
+    <mergeCell ref="F137:F145"/>
+    <mergeCell ref="F146:F148"/>
+    <mergeCell ref="F149:F154"/>
+    <mergeCell ref="F155:F160"/>
+    <mergeCell ref="F161:F162"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -4936,41 +5038,41 @@
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G27:G31"/>
     <mergeCell ref="G32:G36"/>
-    <mergeCell ref="G37:G40"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="G50:G59"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="G67:G69"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="G74:G82"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="G86:G94"/>
-    <mergeCell ref="G95:G98"/>
-    <mergeCell ref="G99:G101"/>
-    <mergeCell ref="G103:G105"/>
-    <mergeCell ref="G106:G108"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="G113:G117"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="G120:G121"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="G44:G48"/>
+    <mergeCell ref="G49:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G79:G87"/>
+    <mergeCell ref="G88:G90"/>
+    <mergeCell ref="G91:G99"/>
+    <mergeCell ref="G100:G103"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="G111:G113"/>
+    <mergeCell ref="G115:G117"/>
+    <mergeCell ref="G118:G122"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="G125:G126"/>
+    <mergeCell ref="G127:G128"/>
     <mergeCell ref="G129:G130"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G135:G136"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="G141:G143"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G154:G155"/>
-    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="G146:G148"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="G151:G152"/>
+    <mergeCell ref="G153:G154"/>
+    <mergeCell ref="G155:G156"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="G159:G160"/>
+    <mergeCell ref="G161:G162"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -4978,44 +5080,44 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H27:H31"/>
     <mergeCell ref="H32:H36"/>
-    <mergeCell ref="H37:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="H50:H59"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="H64:H66"/>
-    <mergeCell ref="H67:H69"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="H77:H79"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="H86:H88"/>
-    <mergeCell ref="H89:H91"/>
-    <mergeCell ref="H92:H94"/>
-    <mergeCell ref="H95:H98"/>
-    <mergeCell ref="H99:H101"/>
-    <mergeCell ref="H103:H105"/>
-    <mergeCell ref="H106:H108"/>
-    <mergeCell ref="H110:H112"/>
-    <mergeCell ref="H113:H117"/>
-    <mergeCell ref="H118:H119"/>
-    <mergeCell ref="H120:H121"/>
-    <mergeCell ref="H122:H123"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="H126:H127"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H44:H48"/>
+    <mergeCell ref="H49:H64"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="H69:H71"/>
+    <mergeCell ref="H72:H74"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="H79:H81"/>
+    <mergeCell ref="H82:H84"/>
+    <mergeCell ref="H85:H87"/>
+    <mergeCell ref="H91:H93"/>
+    <mergeCell ref="H94:H96"/>
+    <mergeCell ref="H97:H99"/>
+    <mergeCell ref="H100:H103"/>
+    <mergeCell ref="H104:H106"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="H111:H113"/>
+    <mergeCell ref="H115:H117"/>
+    <mergeCell ref="H118:H122"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H127:H128"/>
     <mergeCell ref="H129:H130"/>
-    <mergeCell ref="H132:H133"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="H138:H139"/>
-    <mergeCell ref="H141:H143"/>
-    <mergeCell ref="H144:H145"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="H148:H149"/>
-    <mergeCell ref="H150:H151"/>
-    <mergeCell ref="H152:H153"/>
-    <mergeCell ref="H154:H155"/>
-    <mergeCell ref="H156:H157"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="H134:H135"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H146:H148"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H161:H162"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -5024,45 +5126,47 @@
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="I27:I31"/>
     <mergeCell ref="I32:I36"/>
-    <mergeCell ref="I37:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I49"/>
-    <mergeCell ref="I50:I53"/>
-    <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="I64:I66"/>
-    <mergeCell ref="I67:I69"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="I77:I79"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="I86:I88"/>
-    <mergeCell ref="I89:I91"/>
-    <mergeCell ref="I92:I94"/>
-    <mergeCell ref="I95:I98"/>
-    <mergeCell ref="I99:I101"/>
-    <mergeCell ref="I103:I105"/>
-    <mergeCell ref="I106:I108"/>
-    <mergeCell ref="I110:I112"/>
-    <mergeCell ref="I113:I117"/>
-    <mergeCell ref="I118:I119"/>
-    <mergeCell ref="I120:I121"/>
-    <mergeCell ref="I122:I123"/>
-    <mergeCell ref="I124:I125"/>
-    <mergeCell ref="I126:I127"/>
+    <mergeCell ref="I37:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I44:I48"/>
+    <mergeCell ref="I49:I52"/>
+    <mergeCell ref="I53:I56"/>
+    <mergeCell ref="I57:I60"/>
+    <mergeCell ref="I61:I64"/>
+    <mergeCell ref="I65:I67"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="I72:I74"/>
+    <mergeCell ref="I76:I78"/>
+    <mergeCell ref="I79:I81"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="I85:I87"/>
+    <mergeCell ref="I91:I93"/>
+    <mergeCell ref="I94:I96"/>
+    <mergeCell ref="I97:I99"/>
+    <mergeCell ref="I100:I103"/>
+    <mergeCell ref="I104:I106"/>
+    <mergeCell ref="I108:I110"/>
+    <mergeCell ref="I111:I113"/>
+    <mergeCell ref="I115:I117"/>
+    <mergeCell ref="I118:I122"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="I127:I128"/>
     <mergeCell ref="I129:I130"/>
-    <mergeCell ref="I132:I133"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="I141:I143"/>
-    <mergeCell ref="I144:I145"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="I148:I149"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="I152:I153"/>
-    <mergeCell ref="I154:I155"/>
-    <mergeCell ref="I156:I157"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="I134:I135"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I140:I141"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I146:I148"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -5071,45 +5175,47 @@
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="J27:J31"/>
     <mergeCell ref="J32:J36"/>
-    <mergeCell ref="J37:J40"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="J45:J49"/>
-    <mergeCell ref="J50:J53"/>
-    <mergeCell ref="J54:J57"/>
-    <mergeCell ref="J60:J62"/>
-    <mergeCell ref="J64:J66"/>
-    <mergeCell ref="J67:J69"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="J77:J79"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="J86:J88"/>
-    <mergeCell ref="J89:J91"/>
-    <mergeCell ref="J92:J94"/>
-    <mergeCell ref="J95:J98"/>
-    <mergeCell ref="J99:J101"/>
-    <mergeCell ref="J103:J105"/>
-    <mergeCell ref="J106:J108"/>
-    <mergeCell ref="J110:J112"/>
-    <mergeCell ref="J113:J117"/>
-    <mergeCell ref="J118:J119"/>
-    <mergeCell ref="J120:J121"/>
-    <mergeCell ref="J122:J123"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="J126:J127"/>
+    <mergeCell ref="J37:J39"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="J44:J48"/>
+    <mergeCell ref="J49:J52"/>
+    <mergeCell ref="J53:J56"/>
+    <mergeCell ref="J57:J60"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="J65:J67"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="J76:J78"/>
+    <mergeCell ref="J79:J81"/>
+    <mergeCell ref="J82:J84"/>
+    <mergeCell ref="J85:J87"/>
+    <mergeCell ref="J91:J93"/>
+    <mergeCell ref="J94:J96"/>
+    <mergeCell ref="J97:J99"/>
+    <mergeCell ref="J100:J103"/>
+    <mergeCell ref="J104:J106"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J111:J113"/>
+    <mergeCell ref="J115:J117"/>
+    <mergeCell ref="J118:J122"/>
+    <mergeCell ref="J123:J124"/>
+    <mergeCell ref="J125:J126"/>
+    <mergeCell ref="J127:J128"/>
     <mergeCell ref="J129:J130"/>
-    <mergeCell ref="J132:J133"/>
-    <mergeCell ref="J135:J136"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="J141:J143"/>
-    <mergeCell ref="J144:J145"/>
-    <mergeCell ref="J146:J147"/>
-    <mergeCell ref="J148:J149"/>
-    <mergeCell ref="J150:J151"/>
-    <mergeCell ref="J152:J153"/>
-    <mergeCell ref="J154:J155"/>
-    <mergeCell ref="J156:J157"/>
+    <mergeCell ref="J131:J132"/>
+    <mergeCell ref="J134:J135"/>
+    <mergeCell ref="J137:J138"/>
+    <mergeCell ref="J140:J141"/>
+    <mergeCell ref="J143:J144"/>
+    <mergeCell ref="J146:J148"/>
+    <mergeCell ref="J149:J150"/>
+    <mergeCell ref="J151:J152"/>
+    <mergeCell ref="J153:J154"/>
+    <mergeCell ref="J155:J156"/>
+    <mergeCell ref="J157:J158"/>
+    <mergeCell ref="J159:J160"/>
+    <mergeCell ref="J161:J162"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="164">
   <si>
     <t>variable_id</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'sfcWind']</t>
+  </si>
+  <si>
+    <t>['pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'uas', 'vas']</t>
   </si>
   <si>
     <t>['orog', 'sftlf', 'sfturf', 'sftlaf']</t>
@@ -860,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4936,7 +4939,7 @@
         <v>87</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>120</v>
@@ -4957,25 +4960,46 @@
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>120</v>
       </c>
       <c r="M162" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+      <c r="J163" s="1"/>
+      <c r="K163" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M163" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="249">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A162"/>
+    <mergeCell ref="A26:A163"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B162"/>
+    <mergeCell ref="B26:B163"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C162"/>
+    <mergeCell ref="C26:C163"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D162"/>
+    <mergeCell ref="D26:D163"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4995,7 +5019,7 @@
     <mergeCell ref="E72:E117"/>
     <mergeCell ref="E118:E122"/>
     <mergeCell ref="E123:E160"/>
-    <mergeCell ref="E161:E162"/>
+    <mergeCell ref="E161:E163"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -5025,7 +5049,7 @@
     <mergeCell ref="F146:F148"/>
     <mergeCell ref="F149:F154"/>
     <mergeCell ref="F155:F160"/>
-    <mergeCell ref="F161:F162"/>
+    <mergeCell ref="F161:F163"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -5072,7 +5096,7 @@
     <mergeCell ref="G155:G156"/>
     <mergeCell ref="G157:G158"/>
     <mergeCell ref="G159:G160"/>
-    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="G161:G163"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -5117,7 +5141,7 @@
     <mergeCell ref="H155:H156"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H161:H163"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -5166,7 +5190,7 @@
     <mergeCell ref="I155:I156"/>
     <mergeCell ref="I157:I158"/>
     <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I161:I163"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -5215,7 +5239,7 @@
     <mergeCell ref="J155:J156"/>
     <mergeCell ref="J157:J158"/>
     <mergeCell ref="J159:J160"/>
-    <mergeCell ref="J161:J162"/>
+    <mergeCell ref="J161:J163"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="165">
   <si>
     <t>variable_id</t>
   </si>
@@ -499,13 +499,16 @@
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'sfcWind']</t>
   </si>
   <si>
-    <t>['pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'uas', 'vas']</t>
+    <t>['pr', 'uas', 'vas', 'sfcWind', 'tas', 'hurs']</t>
+  </si>
+  <si>
+    <t>['pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'clt', 'evspsbl', 'huss', 'uas', 'vas', 'hurs', 'sfcWind']</t>
   </si>
   <si>
     <t>['orog', 'sftlf', 'sfturf', 'sftlaf']</t>
   </si>
   <si>
-    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'rsds', 'rlds']</t>
+    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'rsds', 'rlds', 'evspsbl', 'uas', 'vas', 'sfcWind']</t>
   </si>
 </sst>
 </file>
@@ -863,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4939,7 +4942,7 @@
         <v>87</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>120</v>
@@ -4960,7 +4963,7 @@
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>120</v>
@@ -4981,25 +4984,46 @@
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L163" s="1" t="s">
         <v>120</v>
       </c>
       <c r="M163" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
+      <c r="K164" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M164" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="249">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A163"/>
+    <mergeCell ref="A26:A164"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B163"/>
+    <mergeCell ref="B26:B164"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C163"/>
+    <mergeCell ref="C26:C164"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D163"/>
+    <mergeCell ref="D26:D164"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -5019,7 +5043,7 @@
     <mergeCell ref="E72:E117"/>
     <mergeCell ref="E118:E122"/>
     <mergeCell ref="E123:E160"/>
-    <mergeCell ref="E161:E163"/>
+    <mergeCell ref="E161:E164"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -5049,7 +5073,7 @@
     <mergeCell ref="F146:F148"/>
     <mergeCell ref="F149:F154"/>
     <mergeCell ref="F155:F160"/>
-    <mergeCell ref="F161:F163"/>
+    <mergeCell ref="F161:F164"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -5096,7 +5120,7 @@
     <mergeCell ref="G155:G156"/>
     <mergeCell ref="G157:G158"/>
     <mergeCell ref="G159:G160"/>
-    <mergeCell ref="G161:G163"/>
+    <mergeCell ref="G161:G164"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
@@ -5141,7 +5165,7 @@
     <mergeCell ref="H155:H156"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H161:H163"/>
+    <mergeCell ref="H161:H164"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
@@ -5190,7 +5214,7 @@
     <mergeCell ref="I155:I156"/>
     <mergeCell ref="I157:I158"/>
     <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I163"/>
+    <mergeCell ref="I161:I164"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
@@ -5239,7 +5263,7 @@
     <mergeCell ref="J155:J156"/>
     <mergeCell ref="J157:J158"/>
     <mergeCell ref="J159:J160"/>
-    <mergeCell ref="J161:J163"/>
+    <mergeCell ref="J161:J164"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="161">
   <si>
     <t>variable_id</t>
   </si>
@@ -112,9 +112,6 @@
     <t>SMHI</t>
   </si>
   <si>
-    <t>CESAM-UA</t>
-  </si>
-  <si>
     <t>CLMcom-CMCC</t>
   </si>
   <si>
@@ -235,9 +232,6 @@
     <t>RCA4</t>
   </si>
   <si>
-    <t>WRF451Q</t>
-  </si>
-  <si>
     <t>CCLM6-0-1-URB</t>
   </si>
   <si>
@@ -343,9 +337,6 @@
     <t>v20131026</t>
   </si>
   <si>
-    <t>v20250520</t>
-  </si>
-  <si>
     <t>v20250201</t>
   </si>
   <si>
@@ -395,9 +386,6 @@
   </si>
   <si>
     <t>['pr', 'tas']</t>
-  </si>
-  <si>
-    <t>['hurs', 'sfcWind', 'tas', 'pr']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
@@ -866,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -940,28 +928,28 @@
         <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -973,22 +961,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1000,28 +988,28 @@
         <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1033,22 +1021,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1060,28 +1048,28 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1096,13 +1084,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1115,19 +1103,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1142,13 +1130,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1160,28 +1148,28 @@
         <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1196,13 +1184,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1214,28 +1202,28 @@
         <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1247,22 +1235,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1274,28 +1262,28 @@
         <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M14" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1307,28 +1295,28 @@
         <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1343,13 +1331,13 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1365,10 +1353,10 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1380,28 +1368,28 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1416,13 +1404,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1434,28 +1422,28 @@
         <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1467,22 +1455,22 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1494,28 +1482,28 @@
         <v>30</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1530,13 +1518,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1548,28 +1536,28 @@
         <v>31</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1581,22 +1569,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1616,28 +1604,28 @@
         <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M26" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1645,32 +1633,20 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1685,13 +1661,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M28" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1706,13 +1682,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M29" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1727,13 +1703,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M30" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1741,20 +1717,32 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K31" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1762,32 +1750,20 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1802,13 +1778,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M33" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1823,13 +1799,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1844,13 +1820,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1858,20 +1834,32 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K36" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1879,32 +1867,20 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M37" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1919,13 +1895,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M38" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1933,20 +1909,32 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K39" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M39" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1954,32 +1942,20 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M40" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1989,18 +1965,26 @@
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K41" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M41" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2010,26 +1994,18 @@
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M42" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2038,19 +2014,29 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K43" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M43" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2059,29 +2045,19 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M44" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2096,13 +2072,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M45" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2117,13 +2093,13 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M46" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2138,13 +2114,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2152,20 +2128,32 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K48" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2173,32 +2161,20 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M49" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2213,13 +2189,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M50" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2234,13 +2210,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M51" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2252,16 +2228,20 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
+      <c r="I52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K52" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2273,20 +2253,16 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M53" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2301,13 +2277,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2322,13 +2298,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M55" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2340,16 +2316,20 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
+      <c r="I56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K56" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M56" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2361,20 +2341,16 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M57" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2389,13 +2365,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M58" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2410,13 +2386,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M59" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2428,16 +2404,20 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
+      <c r="I60" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K60" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M60" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2449,20 +2429,16 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M61" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2477,13 +2453,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M62" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2498,13 +2474,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M63" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2512,20 +2488,32 @@
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="E64" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K64" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2533,32 +2521,20 @@
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M65" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2573,13 +2549,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M66" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2589,18 +2565,26 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K67" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M67" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2611,25 +2595,25 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M68" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2639,26 +2623,18 @@
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M69" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2673,13 +2649,13 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M70" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2687,20 +2663,32 @@
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="E71" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K71" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M71" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2708,32 +2696,20 @@
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
-      <c r="E72" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M72" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2748,13 +2724,13 @@
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M73" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2764,18 +2740,26 @@
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="G74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K74" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M74" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2786,25 +2770,25 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M75" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2814,26 +2798,18 @@
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M76" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2848,13 +2824,13 @@
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M77" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2863,19 +2839,29 @@
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K78" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M78" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2884,29 +2870,19 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M79" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2921,13 +2897,13 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M80" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2938,17 +2914,23 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="H81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K81" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M81" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2959,23 +2941,17 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M82" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2990,13 +2966,13 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M83" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -3007,17 +2983,23 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="H84" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K84" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M84" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3028,23 +3010,17 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M85" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3059,13 +3035,13 @@
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M86" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3075,18 +3051,26 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
+      <c r="G87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K87" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M87" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3096,26 +3080,24 @@
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="G88" s="1"/>
       <c r="H88" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M88" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3130,19 +3112,19 @@
         <v>59</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M89" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3152,24 +3134,26 @@
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
+      <c r="G90" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="H90" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M90" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3179,26 +3163,18 @@
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M91" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3213,13 +3189,13 @@
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M92" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3230,17 +3206,23 @@
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
+      <c r="H93" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K93" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M93" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3251,23 +3233,17 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
       <c r="K94" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M94" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3282,13 +3258,13 @@
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M95" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3299,17 +3275,23 @@
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
+      <c r="H96" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K96" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M96" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3320,23 +3302,17 @@
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
-      <c r="H97" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M97" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3351,13 +3327,13 @@
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M98" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3366,19 +3342,29 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K99" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M99" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3387,29 +3373,19 @@
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M100" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3424,13 +3400,13 @@
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M101" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3445,13 +3421,13 @@
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M102" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3460,19 +3436,29 @@
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+      <c r="F103" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K103" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M103" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3481,29 +3467,19 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M104" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3518,13 +3494,13 @@
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M105" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3534,18 +3510,26 @@
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
+      <c r="G106" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K106" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M106" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3556,25 +3540,25 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K107" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M107" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3584,26 +3568,18 @@
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M108" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3618,13 +3594,13 @@
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M109" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3633,19 +3609,29 @@
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K110" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M110" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3654,29 +3640,19 @@
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M111" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3691,13 +3667,13 @@
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M112" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3707,18 +3683,26 @@
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
+      <c r="G113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K113" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M113" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3729,25 +3713,25 @@
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K114" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M114" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3757,26 +3741,18 @@
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M115" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3791,13 +3767,13 @@
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M116" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3805,20 +3781,32 @@
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
+      <c r="E117" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K117" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M117" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3826,32 +3814,20 @@
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
-      <c r="E118" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
       <c r="K118" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M118" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3866,13 +3842,13 @@
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M119" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3887,13 +3863,13 @@
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M120" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3908,13 +3884,13 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M121" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3922,20 +3898,32 @@
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
+      <c r="E122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K122" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M122" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3943,32 +3931,20 @@
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
-      <c r="E123" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
       <c r="K123" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M123" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3978,18 +3954,26 @@
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
+      <c r="G124" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K124" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M124" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -3999,26 +3983,18 @@
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
-      <c r="G125" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
       <c r="K125" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M125" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4028,18 +4004,26 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
+      <c r="G126" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K126" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M126" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4049,26 +4033,18 @@
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
-      <c r="G127" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
       <c r="K127" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M127" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4077,19 +4053,29 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
+      <c r="F128" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K128" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M128" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4098,29 +4084,19 @@
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
       <c r="K129" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M129" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4130,18 +4106,26 @@
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
+      <c r="G130" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K130" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M130" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4151,26 +4135,18 @@
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
-      <c r="G131" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
       <c r="K131" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M131" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4180,18 +4156,26 @@
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
+      <c r="G132" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K132" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M132" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4202,25 +4186,25 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M133" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4230,26 +4214,18 @@
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
       <c r="K134" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M134" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4259,18 +4235,26 @@
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1"/>
+      <c r="G135" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K135" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M135" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4279,27 +4263,29 @@
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
+      <c r="F136" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G136" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M136" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4308,29 +4294,19 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
       <c r="K137" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M137" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4340,18 +4316,26 @@
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="1"/>
+      <c r="G138" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K138" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M138" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4362,25 +4346,25 @@
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M139" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4390,26 +4374,18 @@
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
       <c r="K140" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M140" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4419,18 +4395,26 @@
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1"/>
+      <c r="G141" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K141" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M141" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4441,25 +4425,25 @@
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
       <c r="G142" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M142" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4469,26 +4453,18 @@
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
-      <c r="G143" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H143" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J143" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
       <c r="K143" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M143" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4498,18 +4474,26 @@
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
-      <c r="G144" s="1"/>
-      <c r="H144" s="1"/>
-      <c r="I144" s="1"/>
-      <c r="J144" s="1"/>
+      <c r="G144" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K144" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M144" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4518,27 +4502,29 @@
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
-      <c r="F145" s="1"/>
+      <c r="F145" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G145" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M145" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4547,29 +4533,19 @@
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
       <c r="K146" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M146" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4584,13 +4560,13 @@
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
       <c r="K147" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M147" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4599,19 +4575,29 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
-      <c r="H148" s="1"/>
-      <c r="I148" s="1"/>
-      <c r="J148" s="1"/>
+      <c r="F148" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K148" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M148" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4620,29 +4606,19 @@
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
       <c r="K149" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M149" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4652,18 +4628,26 @@
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
+      <c r="G150" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K150" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M150" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4673,26 +4657,18 @@
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
-      <c r="G151" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J151" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+      <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M151" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4702,18 +4678,26 @@
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
-      <c r="H152" s="1"/>
-      <c r="I152" s="1"/>
-      <c r="J152" s="1"/>
+      <c r="G152" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K152" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M152" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4723,26 +4707,18 @@
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
-      <c r="G153" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
       <c r="K153" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M153" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4751,19 +4727,29 @@
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="1"/>
-      <c r="G154" s="1"/>
-      <c r="H154" s="1"/>
-      <c r="I154" s="1"/>
-      <c r="J154" s="1"/>
+      <c r="F154" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K154" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M154" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4772,29 +4758,19 @@
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
       <c r="K155" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M155" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -4804,18 +4780,26 @@
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="1"/>
+      <c r="G156" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K156" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M156" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -4825,26 +4809,18 @@
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I157" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J157" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="J157" s="1"/>
       <c r="K157" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M157" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -4854,18 +4830,26 @@
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
-      <c r="H158" s="1"/>
-      <c r="I158" s="1"/>
-      <c r="J158" s="1"/>
+      <c r="G158" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K158" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M158" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -4875,26 +4859,18 @@
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
-      <c r="G159" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J159" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+      <c r="J159" s="1"/>
       <c r="K159" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M159" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -4902,17 +4878,29 @@
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
-      <c r="H160" s="1"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="1"/>
+      <c r="E160" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="K160" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M160" t="s">
         <v>157</v>
@@ -4923,32 +4911,20 @@
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
-      <c r="E161" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
       <c r="K161" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M161" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -4963,13 +4939,13 @@
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M162" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -4984,46 +4960,25 @@
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M163" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13">
-      <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-      <c r="E164" s="1"/>
-      <c r="F164" s="1"/>
-      <c r="G164" s="1"/>
-      <c r="H164" s="1"/>
-      <c r="I164" s="1"/>
-      <c r="J164" s="1"/>
-      <c r="K164" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="M164" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="249">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A164"/>
+    <mergeCell ref="A26:A163"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B164"/>
+    <mergeCell ref="B26:B163"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C164"/>
+    <mergeCell ref="C26:C163"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D164"/>
+    <mergeCell ref="D26:D163"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -5034,16 +4989,16 @@
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="E32:E36"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E40:E48"/>
-    <mergeCell ref="E49:E64"/>
-    <mergeCell ref="E65:E71"/>
-    <mergeCell ref="E72:E117"/>
-    <mergeCell ref="E118:E122"/>
-    <mergeCell ref="E123:E160"/>
-    <mergeCell ref="E161:E164"/>
+    <mergeCell ref="E26:E30"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E39:E47"/>
+    <mergeCell ref="E48:E63"/>
+    <mergeCell ref="E64:E70"/>
+    <mergeCell ref="E71:E116"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="E122:E159"/>
+    <mergeCell ref="E160:E163"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -5054,26 +5009,26 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="F32:F36"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="F40:F43"/>
-    <mergeCell ref="F44:F48"/>
-    <mergeCell ref="F49:F64"/>
-    <mergeCell ref="F65:F71"/>
-    <mergeCell ref="F72:F78"/>
-    <mergeCell ref="F79:F99"/>
-    <mergeCell ref="F100:F103"/>
-    <mergeCell ref="F104:F110"/>
-    <mergeCell ref="F111:F117"/>
-    <mergeCell ref="F118:F122"/>
-    <mergeCell ref="F123:F128"/>
-    <mergeCell ref="F129:F136"/>
-    <mergeCell ref="F137:F145"/>
-    <mergeCell ref="F146:F148"/>
-    <mergeCell ref="F149:F154"/>
-    <mergeCell ref="F155:F160"/>
-    <mergeCell ref="F161:F164"/>
+    <mergeCell ref="F26:F30"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="F43:F47"/>
+    <mergeCell ref="F48:F63"/>
+    <mergeCell ref="F64:F70"/>
+    <mergeCell ref="F71:F77"/>
+    <mergeCell ref="F78:F98"/>
+    <mergeCell ref="F99:F102"/>
+    <mergeCell ref="F103:F109"/>
+    <mergeCell ref="F110:F116"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="F122:F127"/>
+    <mergeCell ref="F128:F135"/>
+    <mergeCell ref="F136:F144"/>
+    <mergeCell ref="F145:F147"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="F154:F159"/>
+    <mergeCell ref="F160:F163"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -5084,186 +5039,186 @@
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="G32:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="G44:G48"/>
-    <mergeCell ref="G49:G64"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="G72:G74"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G79:G87"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="G91:G99"/>
-    <mergeCell ref="G100:G103"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="G111:G113"/>
-    <mergeCell ref="G115:G117"/>
-    <mergeCell ref="G118:G122"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="G125:G126"/>
-    <mergeCell ref="G127:G128"/>
-    <mergeCell ref="G129:G130"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="G137:G138"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="G146:G148"/>
-    <mergeCell ref="G149:G150"/>
-    <mergeCell ref="G151:G152"/>
-    <mergeCell ref="G153:G154"/>
-    <mergeCell ref="G155:G156"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="G159:G160"/>
-    <mergeCell ref="G161:G164"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="G48:G63"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="G68:G70"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="G75:G77"/>
+    <mergeCell ref="G78:G86"/>
+    <mergeCell ref="G87:G89"/>
+    <mergeCell ref="G90:G98"/>
+    <mergeCell ref="G99:G102"/>
+    <mergeCell ref="G103:G105"/>
+    <mergeCell ref="G107:G109"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="G114:G116"/>
+    <mergeCell ref="G117:G121"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="G133:G134"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="G139:G140"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="G145:G147"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G154:G155"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="G158:G159"/>
+    <mergeCell ref="G160:G163"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H27:H31"/>
-    <mergeCell ref="H32:H36"/>
-    <mergeCell ref="H37:H39"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H44:H48"/>
-    <mergeCell ref="H49:H64"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H79:H81"/>
-    <mergeCell ref="H82:H84"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="H91:H93"/>
-    <mergeCell ref="H94:H96"/>
-    <mergeCell ref="H97:H99"/>
-    <mergeCell ref="H100:H103"/>
-    <mergeCell ref="H104:H106"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="H111:H113"/>
-    <mergeCell ref="H115:H117"/>
-    <mergeCell ref="H118:H122"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H140:H141"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H146:H148"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H161:H164"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="H31:H35"/>
+    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="H48:H63"/>
+    <mergeCell ref="H64:H66"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="H75:H77"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="H90:H92"/>
+    <mergeCell ref="H93:H95"/>
+    <mergeCell ref="H96:H98"/>
+    <mergeCell ref="H99:H102"/>
+    <mergeCell ref="H103:H105"/>
+    <mergeCell ref="H107:H109"/>
+    <mergeCell ref="H110:H112"/>
+    <mergeCell ref="H114:H116"/>
+    <mergeCell ref="H117:H121"/>
+    <mergeCell ref="H122:H123"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="H126:H127"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="H136:H137"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="H145:H147"/>
+    <mergeCell ref="H148:H149"/>
+    <mergeCell ref="H150:H151"/>
+    <mergeCell ref="H152:H153"/>
+    <mergeCell ref="H154:H155"/>
+    <mergeCell ref="H156:H157"/>
+    <mergeCell ref="H158:H159"/>
+    <mergeCell ref="H160:H163"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I27:I31"/>
-    <mergeCell ref="I32:I36"/>
-    <mergeCell ref="I37:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="I44:I48"/>
-    <mergeCell ref="I49:I52"/>
-    <mergeCell ref="I53:I56"/>
-    <mergeCell ref="I57:I60"/>
-    <mergeCell ref="I61:I64"/>
-    <mergeCell ref="I65:I67"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="I72:I74"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="I79:I81"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="I85:I87"/>
-    <mergeCell ref="I91:I93"/>
-    <mergeCell ref="I94:I96"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="I100:I103"/>
-    <mergeCell ref="I104:I106"/>
-    <mergeCell ref="I108:I110"/>
-    <mergeCell ref="I111:I113"/>
-    <mergeCell ref="I115:I117"/>
-    <mergeCell ref="I118:I122"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="I134:I135"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I140:I141"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I146:I148"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I164"/>
+    <mergeCell ref="I26:I30"/>
+    <mergeCell ref="I31:I35"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="I48:I51"/>
+    <mergeCell ref="I52:I55"/>
+    <mergeCell ref="I56:I59"/>
+    <mergeCell ref="I60:I63"/>
+    <mergeCell ref="I64:I66"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="I75:I77"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="I84:I86"/>
+    <mergeCell ref="I90:I92"/>
+    <mergeCell ref="I93:I95"/>
+    <mergeCell ref="I96:I98"/>
+    <mergeCell ref="I99:I102"/>
+    <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I107:I109"/>
+    <mergeCell ref="I110:I112"/>
+    <mergeCell ref="I114:I116"/>
+    <mergeCell ref="I117:I121"/>
+    <mergeCell ref="I122:I123"/>
+    <mergeCell ref="I124:I125"/>
+    <mergeCell ref="I126:I127"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="I142:I143"/>
+    <mergeCell ref="I145:I147"/>
+    <mergeCell ref="I148:I149"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="I152:I153"/>
+    <mergeCell ref="I154:I155"/>
+    <mergeCell ref="I156:I157"/>
+    <mergeCell ref="I158:I159"/>
+    <mergeCell ref="I160:I163"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J27:J31"/>
-    <mergeCell ref="J32:J36"/>
-    <mergeCell ref="J37:J39"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="J42:J43"/>
-    <mergeCell ref="J44:J48"/>
-    <mergeCell ref="J49:J52"/>
-    <mergeCell ref="J53:J56"/>
-    <mergeCell ref="J57:J60"/>
-    <mergeCell ref="J61:J64"/>
-    <mergeCell ref="J65:J67"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="J72:J74"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="J79:J81"/>
-    <mergeCell ref="J82:J84"/>
-    <mergeCell ref="J85:J87"/>
-    <mergeCell ref="J91:J93"/>
-    <mergeCell ref="J94:J96"/>
-    <mergeCell ref="J97:J99"/>
-    <mergeCell ref="J100:J103"/>
-    <mergeCell ref="J104:J106"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J111:J113"/>
-    <mergeCell ref="J115:J117"/>
-    <mergeCell ref="J118:J122"/>
-    <mergeCell ref="J123:J124"/>
-    <mergeCell ref="J125:J126"/>
-    <mergeCell ref="J127:J128"/>
-    <mergeCell ref="J129:J130"/>
-    <mergeCell ref="J131:J132"/>
-    <mergeCell ref="J134:J135"/>
-    <mergeCell ref="J137:J138"/>
-    <mergeCell ref="J140:J141"/>
-    <mergeCell ref="J143:J144"/>
-    <mergeCell ref="J146:J148"/>
-    <mergeCell ref="J149:J150"/>
-    <mergeCell ref="J151:J152"/>
-    <mergeCell ref="J153:J154"/>
-    <mergeCell ref="J155:J156"/>
-    <mergeCell ref="J157:J158"/>
-    <mergeCell ref="J159:J160"/>
-    <mergeCell ref="J161:J164"/>
+    <mergeCell ref="J26:J30"/>
+    <mergeCell ref="J31:J35"/>
+    <mergeCell ref="J36:J38"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="J48:J51"/>
+    <mergeCell ref="J52:J55"/>
+    <mergeCell ref="J56:J59"/>
+    <mergeCell ref="J60:J63"/>
+    <mergeCell ref="J64:J66"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="J75:J77"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="J84:J86"/>
+    <mergeCell ref="J90:J92"/>
+    <mergeCell ref="J93:J95"/>
+    <mergeCell ref="J96:J98"/>
+    <mergeCell ref="J99:J102"/>
+    <mergeCell ref="J103:J105"/>
+    <mergeCell ref="J107:J109"/>
+    <mergeCell ref="J110:J112"/>
+    <mergeCell ref="J114:J116"/>
+    <mergeCell ref="J117:J121"/>
+    <mergeCell ref="J122:J123"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="J126:J127"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="J133:J134"/>
+    <mergeCell ref="J136:J137"/>
+    <mergeCell ref="J139:J140"/>
+    <mergeCell ref="J142:J143"/>
+    <mergeCell ref="J145:J147"/>
+    <mergeCell ref="J148:J149"/>
+    <mergeCell ref="J150:J151"/>
+    <mergeCell ref="J152:J153"/>
+    <mergeCell ref="J154:J155"/>
+    <mergeCell ref="J156:J157"/>
+    <mergeCell ref="J158:J159"/>
+    <mergeCell ref="J160:J163"/>
     <mergeCell ref="K16:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="162">
   <si>
     <t>variable_id</t>
   </si>
@@ -442,13 +442,16 @@
     <t>['pr', 'sfcWind', 'tas']</t>
   </si>
   <si>
-    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+    <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'sfcWind']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlf', 'areacella', 'sftlaf']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
-    <t>['orog', 'sftlaf', 'sftlf']</t>
+    <t>['orog', 'sftlaf', 'sftlf', 'areacella']</t>
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
@@ -2195,7 +2198,7 @@
         <v>112</v>
       </c>
       <c r="M50" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2216,7 +2219,7 @@
         <v>112</v>
       </c>
       <c r="M51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2283,7 +2286,7 @@
         <v>112</v>
       </c>
       <c r="M54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2304,7 +2307,7 @@
         <v>112</v>
       </c>
       <c r="M55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2350,7 +2353,7 @@
         <v>113</v>
       </c>
       <c r="M57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2392,7 +2395,7 @@
         <v>113</v>
       </c>
       <c r="M59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2438,7 +2441,7 @@
         <v>113</v>
       </c>
       <c r="M61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2480,7 +2483,7 @@
         <v>113</v>
       </c>
       <c r="M63" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2513,7 +2516,7 @@
         <v>114</v>
       </c>
       <c r="M64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2555,7 +2558,7 @@
         <v>114</v>
       </c>
       <c r="M66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2613,7 +2616,7 @@
         <v>114</v>
       </c>
       <c r="M68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2655,7 +2658,7 @@
         <v>114</v>
       </c>
       <c r="M70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2688,7 +2691,7 @@
         <v>114</v>
       </c>
       <c r="M71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2730,7 +2733,7 @@
         <v>114</v>
       </c>
       <c r="M73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2788,7 +2791,7 @@
         <v>114</v>
       </c>
       <c r="M75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2830,7 +2833,7 @@
         <v>114</v>
       </c>
       <c r="M77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2861,7 +2864,7 @@
         <v>114</v>
       </c>
       <c r="M78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2903,7 +2906,7 @@
         <v>114</v>
       </c>
       <c r="M80" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2930,7 +2933,7 @@
         <v>114</v>
       </c>
       <c r="M81" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2972,7 +2975,7 @@
         <v>114</v>
       </c>
       <c r="M83" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2999,7 +3002,7 @@
         <v>114</v>
       </c>
       <c r="M84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3041,7 +3044,7 @@
         <v>114</v>
       </c>
       <c r="M86" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3153,7 +3156,7 @@
         <v>114</v>
       </c>
       <c r="M90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3195,7 +3198,7 @@
         <v>114</v>
       </c>
       <c r="M92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3222,7 +3225,7 @@
         <v>114</v>
       </c>
       <c r="M93" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3264,7 +3267,7 @@
         <v>114</v>
       </c>
       <c r="M95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3291,7 +3294,7 @@
         <v>114</v>
       </c>
       <c r="M96" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3333,7 +3336,7 @@
         <v>114</v>
       </c>
       <c r="M98" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3364,7 +3367,7 @@
         <v>114</v>
       </c>
       <c r="M99" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3385,7 +3388,7 @@
         <v>114</v>
       </c>
       <c r="M100" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3427,7 +3430,7 @@
         <v>114</v>
       </c>
       <c r="M102" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3458,7 +3461,7 @@
         <v>114</v>
       </c>
       <c r="M103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3500,7 +3503,7 @@
         <v>114</v>
       </c>
       <c r="M105" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3558,7 +3561,7 @@
         <v>114</v>
       </c>
       <c r="M107" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3600,7 +3603,7 @@
         <v>114</v>
       </c>
       <c r="M109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3631,7 +3634,7 @@
         <v>114</v>
       </c>
       <c r="M110" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3673,7 +3676,7 @@
         <v>114</v>
       </c>
       <c r="M112" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3731,7 +3734,7 @@
         <v>114</v>
       </c>
       <c r="M114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3773,7 +3776,7 @@
         <v>114</v>
       </c>
       <c r="M116" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3806,7 +3809,7 @@
         <v>115</v>
       </c>
       <c r="M117" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3827,7 +3830,7 @@
         <v>115</v>
       </c>
       <c r="M118" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3848,7 +3851,7 @@
         <v>115</v>
       </c>
       <c r="M119" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3869,7 +3872,7 @@
         <v>115</v>
       </c>
       <c r="M120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3890,7 +3893,7 @@
         <v>115</v>
       </c>
       <c r="M121" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3923,7 +3926,7 @@
         <v>116</v>
       </c>
       <c r="M122" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3944,7 +3947,7 @@
         <v>116</v>
       </c>
       <c r="M123" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3973,7 +3976,7 @@
         <v>116</v>
       </c>
       <c r="M124" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -3994,7 +3997,7 @@
         <v>116</v>
       </c>
       <c r="M125" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4023,7 +4026,7 @@
         <v>116</v>
       </c>
       <c r="M126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4044,7 +4047,7 @@
         <v>116</v>
       </c>
       <c r="M127" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4075,7 +4078,7 @@
         <v>116</v>
       </c>
       <c r="M128" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4096,7 +4099,7 @@
         <v>116</v>
       </c>
       <c r="M129" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4125,7 +4128,7 @@
         <v>116</v>
       </c>
       <c r="M130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4146,7 +4149,7 @@
         <v>116</v>
       </c>
       <c r="M131" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4175,7 +4178,7 @@
         <v>116</v>
       </c>
       <c r="M132" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4204,7 +4207,7 @@
         <v>116</v>
       </c>
       <c r="M133" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4225,7 +4228,7 @@
         <v>116</v>
       </c>
       <c r="M134" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4254,7 +4257,7 @@
         <v>116</v>
       </c>
       <c r="M135" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4285,7 +4288,7 @@
         <v>116</v>
       </c>
       <c r="M136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4306,7 +4309,7 @@
         <v>116</v>
       </c>
       <c r="M137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4335,7 +4338,7 @@
         <v>116</v>
       </c>
       <c r="M138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4364,7 +4367,7 @@
         <v>116</v>
       </c>
       <c r="M139" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4385,7 +4388,7 @@
         <v>116</v>
       </c>
       <c r="M140" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4414,7 +4417,7 @@
         <v>116</v>
       </c>
       <c r="M141" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4443,7 +4446,7 @@
         <v>116</v>
       </c>
       <c r="M142" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4464,7 +4467,7 @@
         <v>116</v>
       </c>
       <c r="M143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4493,7 +4496,7 @@
         <v>116</v>
       </c>
       <c r="M144" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4524,7 +4527,7 @@
         <v>116</v>
       </c>
       <c r="M145" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4545,7 +4548,7 @@
         <v>116</v>
       </c>
       <c r="M146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4566,7 +4569,7 @@
         <v>116</v>
       </c>
       <c r="M147" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4597,7 +4600,7 @@
         <v>116</v>
       </c>
       <c r="M148" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4618,7 +4621,7 @@
         <v>116</v>
       </c>
       <c r="M149" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4647,7 +4650,7 @@
         <v>116</v>
       </c>
       <c r="M150" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4668,7 +4671,7 @@
         <v>116</v>
       </c>
       <c r="M151" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4697,7 +4700,7 @@
         <v>116</v>
       </c>
       <c r="M152" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4718,7 +4721,7 @@
         <v>116</v>
       </c>
       <c r="M153" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4749,7 +4752,7 @@
         <v>116</v>
       </c>
       <c r="M154" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4770,7 +4773,7 @@
         <v>116</v>
       </c>
       <c r="M155" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -4799,7 +4802,7 @@
         <v>116</v>
       </c>
       <c r="M156" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -4820,7 +4823,7 @@
         <v>116</v>
       </c>
       <c r="M157" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -4849,7 +4852,7 @@
         <v>116</v>
       </c>
       <c r="M158" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -4870,7 +4873,7 @@
         <v>116</v>
       </c>
       <c r="M159" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -4903,7 +4906,7 @@
         <v>117</v>
       </c>
       <c r="M160" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -4924,7 +4927,7 @@
         <v>117</v>
       </c>
       <c r="M161" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -4945,7 +4948,7 @@
         <v>117</v>
       </c>
       <c r="M162" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -4966,7 +4969,7 @@
         <v>117</v>
       </c>
       <c r="M163" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="191">
   <si>
     <t>variable_id</t>
   </si>
@@ -61,6 +61,9 @@
     <t>CORDEX-CMIP6</t>
   </si>
   <si>
+    <t>sim_data</t>
+  </si>
+  <si>
     <t>CMIP5</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>SMHI</t>
   </si>
   <si>
+    <t>CESAM-UA</t>
+  </si>
+  <si>
     <t>CLMcom-CMCC</t>
   </si>
   <si>
@@ -133,6 +139,9 @@
     <t>ICTP</t>
   </si>
   <si>
+    <t>IDL-FCUL</t>
+  </si>
+  <si>
     <t>ERAINT</t>
   </si>
   <si>
@@ -157,6 +166,9 @@
     <t>EC-Earth3</t>
   </si>
   <si>
+    <t>HCLIMcom-DMI</t>
+  </si>
+  <si>
     <t>evaluation</t>
   </si>
   <si>
@@ -178,6 +190,9 @@
     <t>ssp119</t>
   </si>
   <si>
+    <t>IPSL-CM6A-LR</t>
+  </si>
+  <si>
     <t>r0i0p0</t>
   </si>
   <si>
@@ -232,9 +247,15 @@
     <t>RCA4</t>
   </si>
   <si>
+    <t>WRF451Q</t>
+  </si>
+  <si>
     <t>CCLM6-0-1-URB</t>
   </si>
   <si>
+    <t>COSMO-CLM-6-0-clm3</t>
+  </si>
+  <si>
     <t>ICON-CLM-202407-1-1</t>
   </si>
   <si>
@@ -337,9 +358,15 @@
     <t>v20131026</t>
   </si>
   <si>
+    <t>v20250520</t>
+  </si>
+  <si>
     <t>v20250201</t>
   </si>
   <si>
+    <t>v20230222</t>
+  </si>
+  <si>
     <t>v20240920</t>
   </si>
   <si>
@@ -364,12 +391,51 @@
     <t>v20250415</t>
   </si>
   <si>
+    <t>v20240630</t>
+  </si>
+  <si>
     <t>v20241216</t>
   </si>
   <si>
     <t>v20241009</t>
   </si>
   <si>
+    <t>clt</t>
+  </si>
+  <si>
+    <t>evspsbl</t>
+  </si>
+  <si>
+    <t>huss</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>psl</t>
+  </si>
+  <si>
+    <t>rlds</t>
+  </si>
+  <si>
+    <t>rsds</t>
+  </si>
+  <si>
+    <t>tas</t>
+  </si>
+  <si>
+    <t>tasmax</t>
+  </si>
+  <si>
+    <t>tasmin</t>
+  </si>
+  <si>
+    <t>uas</t>
+  </si>
+  <si>
+    <t>vas</t>
+  </si>
+  <si>
     <t>['orog', 'sftlf']</t>
   </si>
   <si>
@@ -388,6 +454,9 @@
     <t>['pr', 'tas']</t>
   </si>
   <si>
+    <t>['rsdscs', 'rldscs', 'zg250', 'rsds', 'rsut', 'zg1000', 'huss', 'zg925', 'hurs', 'snd', 'evspsbl']</t>
+  </si>
+  <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
   </si>
   <si>
@@ -403,15 +472,21 @@
     <t>['clt', 'hfls', 'pr', 'psl', 'rlut', 'rlutcs', 'rsds', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500', 'snw']</t>
   </si>
   <si>
+    <t>['hurs', 'pr', 'prw', 'psl', 'rlut', 'sfcWind', 'tas', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['hus1000', 'hus200', 'hus250', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta850', 'ua1000', 'ua200', 'ua250', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va1000', 'va200', 'va250', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zg500']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
+    <t>['clt', 'evspsbl', 'hfls', 'mrros', 'mrro', 'mrso', 'pr', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
+  </si>
+  <si>
     <t>['hurs', 'pr', 'prw', 'psl', 'rlut', 'sfcWind', 'tas']</t>
   </si>
   <si>
-    <t>['hus1000', 'hus200', 'hus250', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta850', 'ua1000', 'ua200', 'ua250', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va1000', 'va200', 'va250', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zg500']</t>
-  </si>
-  <si>
-    <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snw', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
-  </si>
-  <si>
     <t>['orog', 'sftlaf', 'sftlf', 'sfturf']</t>
   </si>
   <si>
@@ -484,7 +559,16 @@
     <t>['pr', 'tas', 'clt', 'evspsbl', 'hfls', 'mrro', 'mrros', 'mrso', 'prsn', 'psl', 'rlds', 'rlut', 'rsds', 'rsut', 'sfcWind', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
   </si>
   <si>
-    <t>['pr', 'tas', 'zg500', 'clt', 'evspsbl', 'huss', 'psl', 'rlds', 'rsds', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+    <t>['hurs', 'tas', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['tasmax', 'tasmin', 'sfcWindmax']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftgif', 'sftlf', 'sftlaf', 'sfturf']</t>
+  </si>
+  <si>
+    <t>['pr', 'tas', 'zg500', 'clt', 'evspsbl', 'huss', 'psl', 'rlds', 'rsds', 'tasmax', 'tasmin', 'uas', 'vas', 'sfcWind', 'hurs']</t>
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'sfcWind']</t>
@@ -499,7 +583,10 @@
     <t>['orog', 'sftlf', 'sfturf', 'sftlaf']</t>
   </si>
   <si>
-    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'rsds', 'rlds', 'evspsbl', 'uas', 'vas', 'sfcWind']</t>
+    <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'rsds', 'rlds', 'evspsbl', 'uas', 'vas', 'sfcWind', 'clt']</t>
+  </si>
+  <si>
+    <t>['day']</t>
   </si>
 </sst>
 </file>
@@ -857,12 +944,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
@@ -919,40 +1006,40 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M2" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -964,22 +1051,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -988,31 +1075,31 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1024,22 +1111,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1048,31 +1135,31 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1087,13 +1174,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1106,19 +1193,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1133,13 +1220,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1148,31 +1235,31 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1187,13 +1274,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="M11" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1202,31 +1289,31 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1238,22 +1325,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1262,31 +1349,31 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M14" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1295,31 +1382,31 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="M15" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1334,13 +1421,13 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="M16" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1356,10 +1443,10 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M17" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1368,31 +1455,31 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M18" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1407,13 +1494,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M19" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1422,31 +1509,31 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M20" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1458,22 +1545,22 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M21" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1482,31 +1569,31 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M22" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1521,13 +1608,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1536,31 +1623,31 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1572,22 +1659,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M25" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1595,40 +1682,40 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M26" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1636,20 +1723,32 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M27" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1664,13 +1763,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M28" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1685,13 +1784,13 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1706,13 +1805,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1720,32 +1819,20 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M31" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1753,20 +1840,32 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K32" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M32" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1781,13 +1880,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M33" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1802,13 +1901,13 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M34" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1823,13 +1922,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M35" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1837,32 +1936,24 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M36" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1877,13 +1968,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M37" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1898,13 +1989,13 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M38" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1912,32 +2003,20 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M39" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1952,13 +2031,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M40" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -1966,28 +2045,32 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G41" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M41" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2002,13 +2085,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M42" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2017,29 +2100,19 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M43" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2047,20 +2120,32 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M44" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2075,13 +2160,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2091,18 +2176,26 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K46" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M46" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2117,10 +2210,10 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M47" t="s">
         <v>140</v>
@@ -2131,32 +2224,30 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M48" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2171,13 +2262,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M49" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2192,13 +2283,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M50" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2213,13 +2304,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M51" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2231,20 +2322,16 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M52" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2252,20 +2339,32 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K53" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M53" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2280,13 +2379,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M54" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2301,13 +2400,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="M55" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2319,20 +2418,16 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M56" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2344,16 +2439,20 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
+      <c r="I57" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K57" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M57" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2368,13 +2467,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M58" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2389,13 +2488,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M59" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2407,20 +2506,16 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M60" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2432,16 +2527,20 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
+      <c r="I61" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K61" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="M61" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2456,13 +2555,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="M62" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2477,13 +2576,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="M63" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2491,32 +2590,20 @@
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
-      <c r="E64" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M64" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2528,16 +2615,20 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="I65" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K65" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M65" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2552,13 +2643,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M66" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2568,26 +2659,18 @@
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M67" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2597,26 +2680,18 @@
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M68" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2624,20 +2699,32 @@
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="E69" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K69" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M69" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2652,13 +2739,13 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M70" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2666,32 +2753,20 @@
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M71" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2701,18 +2776,26 @@
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="G72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K72" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M72" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2722,18 +2805,26 @@
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="G73" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K73" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M73" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2743,26 +2834,18 @@
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M74" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2772,26 +2855,18 @@
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M75" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2799,20 +2874,32 @@
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="E76" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K76" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M76" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2827,13 +2914,13 @@
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M77" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2842,29 +2929,19 @@
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M78" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2874,18 +2951,26 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="G79" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K79" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M79" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2895,18 +2980,26 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="G80" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K80" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M80" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -2917,23 +3010,17 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M81" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -2948,13 +3035,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M82" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -2963,19 +3050,29 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K83" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M83" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -2986,23 +3083,17 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M84" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3017,13 +3108,13 @@
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M85" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3034,17 +3125,23 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
+      <c r="H86" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K86" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M86" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3054,26 +3151,18 @@
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M87" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3084,23 +3173,17 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
-      <c r="H88" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
       <c r="K88" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M88" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3112,22 +3195,22 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M89" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3137,26 +3220,18 @@
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
       <c r="K90" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M90" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3171,13 +3246,13 @@
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M91" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3187,18 +3262,26 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
+      <c r="G92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K92" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M92" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3210,22 +3293,22 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M93" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3236,17 +3319,23 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
+      <c r="H94" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K94" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M94" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3256,18 +3345,26 @@
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K95" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M95" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3278,23 +3375,17 @@
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
-      <c r="H96" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M96" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3309,13 +3400,13 @@
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M97" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3326,17 +3417,23 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
+      <c r="H98" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K98" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M98" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3345,29 +3442,19 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
       <c r="K99" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M99" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3382,13 +3469,13 @@
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M100" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3399,17 +3486,23 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
+      <c r="H101" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K101" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M101" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3424,13 +3517,13 @@
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M102" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3439,29 +3532,19 @@
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
       <c r="K103" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M103" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3470,19 +3553,29 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
+      <c r="F104" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K104" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M104" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3497,13 +3590,13 @@
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M105" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3513,26 +3606,18 @@
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="G106" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
       <c r="K106" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M106" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3542,26 +3627,18 @@
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M107" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3570,19 +3647,29 @@
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
+      <c r="F108" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K108" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M108" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3597,13 +3684,13 @@
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M109" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3612,29 +3699,19 @@
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
       <c r="K110" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M110" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3644,18 +3721,26 @@
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
+      <c r="G111" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K111" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M111" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -3665,18 +3750,26 @@
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
+      <c r="G112" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K112" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M112" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3686,26 +3779,18 @@
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
-      <c r="G113" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
       <c r="K113" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M113" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3715,26 +3800,18 @@
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
-      <c r="G114" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M114" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3743,19 +3820,29 @@
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
+      <c r="F115" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K115" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M115" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3770,13 +3857,13 @@
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M116" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3784,32 +3871,20 @@
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
-      <c r="E117" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
       <c r="K117" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M117" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3819,18 +3894,26 @@
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
+      <c r="G118" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K118" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M118" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3840,18 +3923,26 @@
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
+      <c r="G119" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K119" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M119" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3866,13 +3957,13 @@
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M120" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3887,13 +3978,13 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M121" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3902,31 +3993,31 @@
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="M122" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -3941,13 +4032,13 @@
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="M123" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -3957,26 +4048,18 @@
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
-      <c r="G124" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
       <c r="K124" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="M124" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -3991,13 +4074,13 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="M125" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4007,26 +4090,18 @@
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
       <c r="K126" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="M126" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4034,20 +4109,32 @@
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
+      <c r="E127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K127" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M127" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4056,29 +4143,19 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
       <c r="K128" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M128" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4093,13 +4170,13 @@
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M129" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4107,28 +4184,32 @@
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
+      <c r="E130" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G130" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M130" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4143,13 +4224,13 @@
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
       <c r="K131" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M131" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4160,25 +4241,25 @@
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M132" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4188,26 +4269,18 @@
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
-      <c r="G133" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
       <c r="K133" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M133" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4217,18 +4290,26 @@
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
+      <c r="G134" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K134" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M134" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4238,26 +4319,18 @@
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
-      <c r="G135" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
       <c r="K135" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M135" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4267,28 +4340,28 @@
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M136" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4303,13 +4376,13 @@
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
       <c r="K137" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M137" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4320,25 +4393,25 @@
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M138" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4348,26 +4421,18 @@
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
       <c r="K139" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M139" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4377,18 +4442,26 @@
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
+      <c r="G140" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K140" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M140" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4399,25 +4472,25 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M141" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4427,26 +4500,18 @@
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
-      <c r="G142" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
       <c r="K142" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M142" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4456,18 +4521,26 @@
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
-      <c r="G143" s="1"/>
-      <c r="H143" s="1"/>
-      <c r="I143" s="1"/>
-      <c r="J143" s="1"/>
+      <c r="G143" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K143" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M143" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4476,27 +4549,29 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="1"/>
+      <c r="F144" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="G144" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M144" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4505,29 +4580,19 @@
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
-      <c r="F145" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
       <c r="K145" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M145" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4537,18 +4602,26 @@
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
-      <c r="G146" s="1"/>
-      <c r="H146" s="1"/>
-      <c r="I146" s="1"/>
-      <c r="J146" s="1"/>
+      <c r="G146" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K146" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M146" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4558,18 +4631,26 @@
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
-      <c r="H147" s="1"/>
-      <c r="I147" s="1"/>
-      <c r="J147" s="1"/>
+      <c r="G147" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K147" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M147" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4578,29 +4659,19 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H148" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
       <c r="K148" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M148" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4610,18 +4681,26 @@
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
-      <c r="H149" s="1"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="1"/>
+      <c r="G149" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K149" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M149" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4632,25 +4711,25 @@
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M150" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4665,13 +4744,13 @@
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M151" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4682,25 +4761,25 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M152" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4709,19 +4788,29 @@
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
-      <c r="H153" s="1"/>
-      <c r="I153" s="1"/>
-      <c r="J153" s="1"/>
+      <c r="F153" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K153" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M153" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4730,29 +4819,19 @@
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+      <c r="J154" s="1"/>
       <c r="K154" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M154" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4767,13 +4846,13 @@
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
       <c r="K155" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M155" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -4782,27 +4861,29 @@
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
-      <c r="F156" s="1"/>
+      <c r="F156" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="G156" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M156" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -4817,13 +4898,13 @@
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
       <c r="K157" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M157" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -4834,25 +4915,25 @@
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M158" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -4867,13 +4948,13 @@
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
       <c r="K159" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="M159" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -4881,32 +4962,28 @@
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
-      <c r="E160" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M160" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -4921,13 +4998,13 @@
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
       <c r="K161" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M161" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -4936,19 +5013,29 @@
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
-      <c r="F162" s="1"/>
-      <c r="G162" s="1"/>
-      <c r="H162" s="1"/>
-      <c r="I162" s="1"/>
-      <c r="J162" s="1"/>
+      <c r="F162" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="K162" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M162" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -4963,25 +5050,909 @@
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M163" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+      <c r="G164" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M164" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L165" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M165" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K166" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L166" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M166" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L167" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M167" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L168" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M168" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L169" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M169" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+      <c r="G170" s="1"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+      <c r="J170" s="1"/>
+      <c r="K170" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L170" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M170" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+      <c r="G171" s="1"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+      <c r="J171" s="1"/>
+      <c r="K171" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L171" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M171" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13">
+      <c r="A172" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J172" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L163" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M163" t="s">
-        <v>161</v>
+      <c r="K172" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L172" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M172" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+      <c r="L173" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M173" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+      <c r="J174" s="1"/>
+      <c r="K174" s="1"/>
+      <c r="L174" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M174" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+      <c r="G175" s="1"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
+      <c r="L175" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M175" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M176" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+      <c r="G177" s="1"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+      <c r="J177" s="1"/>
+      <c r="K177" s="1"/>
+      <c r="L177" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M177" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+      <c r="L178" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M178" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+      <c r="L179" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M179" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
+      <c r="L180" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M180" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+      <c r="G181" s="1"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+      <c r="J181" s="1"/>
+      <c r="K181" s="1"/>
+      <c r="L181" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M181" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+      <c r="L182" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M182" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+      <c r="G183" s="1"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+      <c r="L183" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="M183" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K184" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L184" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M184" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+      <c r="G185" s="1"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+      <c r="L185" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M185" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="K186" s="1"/>
+      <c r="L186" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M186" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+      <c r="G187" s="1"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="K187" s="1"/>
+      <c r="L187" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M188" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M189" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+      <c r="G190" s="1"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+      <c r="L190" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M190" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+      <c r="L191" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M191" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+      <c r="G192" s="1"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+      <c r="J192" s="1"/>
+      <c r="K192" s="1"/>
+      <c r="L192" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M192" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="K193" s="1"/>
+      <c r="L193" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="M193" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+      <c r="G194" s="1"/>
+      <c r="H194" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K194" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L194" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M194" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M195" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+      <c r="J196" s="1"/>
+      <c r="K196" s="1"/>
+      <c r="L196" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M196" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="K197" s="1"/>
+      <c r="L197" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M197" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="K198" s="1"/>
+      <c r="L198" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M198" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="K199" s="1"/>
+      <c r="L199" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M199" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+      <c r="F200" s="1"/>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+      <c r="J200" s="1"/>
+      <c r="K200" s="1"/>
+      <c r="L200" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M200" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="K201" s="1"/>
+      <c r="L201" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M201" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+      <c r="J202" s="1"/>
+      <c r="K202" s="1"/>
+      <c r="L202" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M202" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+      <c r="F203" s="1"/>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+      <c r="J203" s="1"/>
+      <c r="K203" s="1"/>
+      <c r="L203" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M203" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+      <c r="J204" s="1"/>
+      <c r="K204" s="1"/>
+      <c r="L204" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M204" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+      <c r="J205" s="1"/>
+      <c r="K205" s="1"/>
+      <c r="L205" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="M205" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="249">
+  <mergeCells count="276">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A163"/>
+    <mergeCell ref="A26:A171"/>
+    <mergeCell ref="A172:A205"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B163"/>
+    <mergeCell ref="B26:B171"/>
+    <mergeCell ref="B172:B205"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C163"/>
+    <mergeCell ref="C26:C171"/>
+    <mergeCell ref="C172:C205"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D163"/>
+    <mergeCell ref="D26:D171"/>
+    <mergeCell ref="D172:D205"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -4992,16 +5963,18 @@
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E30"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E39:E47"/>
-    <mergeCell ref="E48:E63"/>
-    <mergeCell ref="E64:E70"/>
-    <mergeCell ref="E71:E116"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="E122:E159"/>
-    <mergeCell ref="E160:E163"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="E32:E40"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E44:E52"/>
+    <mergeCell ref="E53:E68"/>
+    <mergeCell ref="E69:E75"/>
+    <mergeCell ref="E76:E121"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="E127:E129"/>
+    <mergeCell ref="E130:E167"/>
+    <mergeCell ref="E168:E171"/>
+    <mergeCell ref="E172:E205"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -5012,26 +5985,28 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F26:F30"/>
-    <mergeCell ref="F31:F35"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="F43:F47"/>
-    <mergeCell ref="F48:F63"/>
-    <mergeCell ref="F64:F70"/>
-    <mergeCell ref="F71:F77"/>
-    <mergeCell ref="F78:F98"/>
-    <mergeCell ref="F99:F102"/>
-    <mergeCell ref="F103:F109"/>
-    <mergeCell ref="F110:F116"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="F122:F127"/>
-    <mergeCell ref="F128:F135"/>
-    <mergeCell ref="F136:F144"/>
-    <mergeCell ref="F145:F147"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="F154:F159"/>
-    <mergeCell ref="F160:F163"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="F32:F40"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="F44:F47"/>
+    <mergeCell ref="F48:F52"/>
+    <mergeCell ref="F53:F68"/>
+    <mergeCell ref="F69:F75"/>
+    <mergeCell ref="F76:F82"/>
+    <mergeCell ref="F83:F103"/>
+    <mergeCell ref="F104:F107"/>
+    <mergeCell ref="F108:F114"/>
+    <mergeCell ref="F115:F121"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="F127:F129"/>
+    <mergeCell ref="F130:F135"/>
+    <mergeCell ref="F136:F143"/>
+    <mergeCell ref="F144:F152"/>
+    <mergeCell ref="F153:F155"/>
+    <mergeCell ref="F156:F161"/>
+    <mergeCell ref="F162:F167"/>
+    <mergeCell ref="F168:F171"/>
+    <mergeCell ref="F172:F205"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -5042,187 +6017,206 @@
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="G48:G63"/>
-    <mergeCell ref="G64:G66"/>
-    <mergeCell ref="G68:G70"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="G75:G77"/>
-    <mergeCell ref="G78:G86"/>
-    <mergeCell ref="G87:G89"/>
-    <mergeCell ref="G90:G98"/>
-    <mergeCell ref="G99:G102"/>
-    <mergeCell ref="G103:G105"/>
-    <mergeCell ref="G107:G109"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="G114:G116"/>
-    <mergeCell ref="G117:G121"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="G32:G40"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="G48:G52"/>
+    <mergeCell ref="G53:G68"/>
+    <mergeCell ref="G69:G71"/>
+    <mergeCell ref="G73:G75"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="G83:G91"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="G95:G103"/>
+    <mergeCell ref="G104:G107"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="G112:G114"/>
+    <mergeCell ref="G115:G117"/>
+    <mergeCell ref="G119:G121"/>
+    <mergeCell ref="G122:G126"/>
+    <mergeCell ref="G127:G129"/>
     <mergeCell ref="G130:G131"/>
-    <mergeCell ref="G133:G134"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="G134:G135"/>
     <mergeCell ref="G136:G137"/>
-    <mergeCell ref="G139:G140"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="G145:G147"/>
-    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G141:G142"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="G147:G148"/>
     <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="G154:G155"/>
+    <mergeCell ref="G153:G155"/>
     <mergeCell ref="G156:G157"/>
     <mergeCell ref="G158:G159"/>
-    <mergeCell ref="G160:G163"/>
+    <mergeCell ref="G160:G161"/>
+    <mergeCell ref="G162:G163"/>
+    <mergeCell ref="G164:G165"/>
+    <mergeCell ref="G166:G167"/>
+    <mergeCell ref="G168:G171"/>
+    <mergeCell ref="G172:G205"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="H31:H35"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="H48:H63"/>
-    <mergeCell ref="H64:H66"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="H75:H77"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="H84:H86"/>
-    <mergeCell ref="H90:H92"/>
-    <mergeCell ref="H93:H95"/>
-    <mergeCell ref="H96:H98"/>
-    <mergeCell ref="H99:H102"/>
-    <mergeCell ref="H103:H105"/>
-    <mergeCell ref="H107:H109"/>
-    <mergeCell ref="H110:H112"/>
-    <mergeCell ref="H114:H116"/>
-    <mergeCell ref="H117:H121"/>
-    <mergeCell ref="H122:H123"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="H126:H127"/>
-    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="H32:H40"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="H48:H52"/>
+    <mergeCell ref="H53:H68"/>
+    <mergeCell ref="H69:H71"/>
+    <mergeCell ref="H73:H75"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="H83:H85"/>
+    <mergeCell ref="H86:H88"/>
+    <mergeCell ref="H89:H91"/>
+    <mergeCell ref="H95:H97"/>
+    <mergeCell ref="H98:H100"/>
+    <mergeCell ref="H101:H103"/>
+    <mergeCell ref="H104:H107"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="H112:H114"/>
+    <mergeCell ref="H115:H117"/>
+    <mergeCell ref="H119:H121"/>
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="H127:H129"/>
     <mergeCell ref="H130:H131"/>
-    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="H132:H133"/>
+    <mergeCell ref="H134:H135"/>
     <mergeCell ref="H136:H137"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="H142:H143"/>
-    <mergeCell ref="H145:H147"/>
-    <mergeCell ref="H148:H149"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="H144:H145"/>
+    <mergeCell ref="H147:H148"/>
     <mergeCell ref="H150:H151"/>
-    <mergeCell ref="H152:H153"/>
-    <mergeCell ref="H154:H155"/>
+    <mergeCell ref="H153:H155"/>
     <mergeCell ref="H156:H157"/>
     <mergeCell ref="H158:H159"/>
-    <mergeCell ref="H160:H163"/>
+    <mergeCell ref="H160:H161"/>
+    <mergeCell ref="H162:H163"/>
+    <mergeCell ref="H164:H165"/>
+    <mergeCell ref="H166:H167"/>
+    <mergeCell ref="H168:H171"/>
+    <mergeCell ref="H172:H183"/>
+    <mergeCell ref="H184:H193"/>
+    <mergeCell ref="H194:H205"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I26:I30"/>
-    <mergeCell ref="I31:I35"/>
-    <mergeCell ref="I36:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="I48:I51"/>
-    <mergeCell ref="I52:I55"/>
-    <mergeCell ref="I56:I59"/>
-    <mergeCell ref="I60:I63"/>
-    <mergeCell ref="I64:I66"/>
-    <mergeCell ref="I68:I70"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="I75:I77"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="I84:I86"/>
-    <mergeCell ref="I90:I92"/>
-    <mergeCell ref="I93:I95"/>
-    <mergeCell ref="I96:I98"/>
-    <mergeCell ref="I99:I102"/>
-    <mergeCell ref="I103:I105"/>
-    <mergeCell ref="I107:I109"/>
-    <mergeCell ref="I110:I112"/>
-    <mergeCell ref="I114:I116"/>
-    <mergeCell ref="I117:I121"/>
-    <mergeCell ref="I122:I123"/>
-    <mergeCell ref="I124:I125"/>
-    <mergeCell ref="I126:I127"/>
-    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="I32:I35"/>
+    <mergeCell ref="I36:I40"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="I48:I52"/>
+    <mergeCell ref="I53:I56"/>
+    <mergeCell ref="I57:I60"/>
+    <mergeCell ref="I61:I64"/>
+    <mergeCell ref="I65:I68"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="I73:I75"/>
+    <mergeCell ref="I76:I78"/>
+    <mergeCell ref="I80:I82"/>
+    <mergeCell ref="I83:I85"/>
+    <mergeCell ref="I86:I88"/>
+    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="I95:I97"/>
+    <mergeCell ref="I98:I100"/>
+    <mergeCell ref="I101:I103"/>
+    <mergeCell ref="I104:I107"/>
+    <mergeCell ref="I108:I110"/>
+    <mergeCell ref="I112:I114"/>
+    <mergeCell ref="I115:I117"/>
+    <mergeCell ref="I119:I121"/>
+    <mergeCell ref="I122:I126"/>
+    <mergeCell ref="I127:I129"/>
     <mergeCell ref="I130:I131"/>
-    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="I132:I133"/>
+    <mergeCell ref="I134:I135"/>
     <mergeCell ref="I136:I137"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="I142:I143"/>
-    <mergeCell ref="I145:I147"/>
-    <mergeCell ref="I148:I149"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="I141:I142"/>
+    <mergeCell ref="I144:I145"/>
+    <mergeCell ref="I147:I148"/>
     <mergeCell ref="I150:I151"/>
-    <mergeCell ref="I152:I153"/>
-    <mergeCell ref="I154:I155"/>
+    <mergeCell ref="I153:I155"/>
     <mergeCell ref="I156:I157"/>
     <mergeCell ref="I158:I159"/>
-    <mergeCell ref="I160:I163"/>
+    <mergeCell ref="I160:I161"/>
+    <mergeCell ref="I162:I163"/>
+    <mergeCell ref="I164:I165"/>
+    <mergeCell ref="I166:I167"/>
+    <mergeCell ref="I168:I171"/>
+    <mergeCell ref="I172:I183"/>
+    <mergeCell ref="I184:I193"/>
+    <mergeCell ref="I194:I205"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J26:J30"/>
-    <mergeCell ref="J31:J35"/>
-    <mergeCell ref="J36:J38"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="J48:J51"/>
-    <mergeCell ref="J52:J55"/>
-    <mergeCell ref="J56:J59"/>
-    <mergeCell ref="J60:J63"/>
-    <mergeCell ref="J64:J66"/>
-    <mergeCell ref="J68:J70"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="J75:J77"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="J84:J86"/>
-    <mergeCell ref="J90:J92"/>
-    <mergeCell ref="J93:J95"/>
-    <mergeCell ref="J96:J98"/>
-    <mergeCell ref="J99:J102"/>
-    <mergeCell ref="J103:J105"/>
-    <mergeCell ref="J107:J109"/>
-    <mergeCell ref="J110:J112"/>
-    <mergeCell ref="J114:J116"/>
-    <mergeCell ref="J117:J121"/>
-    <mergeCell ref="J122:J123"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="J126:J127"/>
-    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="J27:J31"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="J36:J40"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="J48:J52"/>
+    <mergeCell ref="J53:J56"/>
+    <mergeCell ref="J57:J60"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="J65:J68"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="J73:J75"/>
+    <mergeCell ref="J76:J78"/>
+    <mergeCell ref="J80:J82"/>
+    <mergeCell ref="J83:J85"/>
+    <mergeCell ref="J86:J88"/>
+    <mergeCell ref="J89:J91"/>
+    <mergeCell ref="J95:J97"/>
+    <mergeCell ref="J98:J100"/>
+    <mergeCell ref="J101:J103"/>
+    <mergeCell ref="J104:J107"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J112:J114"/>
+    <mergeCell ref="J115:J117"/>
+    <mergeCell ref="J119:J121"/>
+    <mergeCell ref="J122:J126"/>
+    <mergeCell ref="J127:J129"/>
     <mergeCell ref="J130:J131"/>
-    <mergeCell ref="J133:J134"/>
+    <mergeCell ref="J132:J133"/>
+    <mergeCell ref="J134:J135"/>
     <mergeCell ref="J136:J137"/>
-    <mergeCell ref="J139:J140"/>
-    <mergeCell ref="J142:J143"/>
-    <mergeCell ref="J145:J147"/>
-    <mergeCell ref="J148:J149"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="J141:J142"/>
+    <mergeCell ref="J144:J145"/>
+    <mergeCell ref="J147:J148"/>
     <mergeCell ref="J150:J151"/>
-    <mergeCell ref="J152:J153"/>
-    <mergeCell ref="J154:J155"/>
+    <mergeCell ref="J153:J155"/>
     <mergeCell ref="J156:J157"/>
     <mergeCell ref="J158:J159"/>
-    <mergeCell ref="J160:J163"/>
+    <mergeCell ref="J160:J161"/>
+    <mergeCell ref="J162:J163"/>
+    <mergeCell ref="J164:J165"/>
+    <mergeCell ref="J166:J167"/>
+    <mergeCell ref="J168:J171"/>
+    <mergeCell ref="J172:J183"/>
+    <mergeCell ref="J184:J193"/>
+    <mergeCell ref="J194:J205"/>
     <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K172:K183"/>
+    <mergeCell ref="K184:K193"/>
+    <mergeCell ref="K194:K205"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -454,7 +454,7 @@
     <t>['pr', 'tas']</t>
   </si>
   <si>
-    <t>['rsdscs', 'rldscs', 'zg250', 'rsds', 'rsut', 'zg1000', 'huss', 'zg925', 'hurs', 'snd', 'evspsbl']</t>
+    <t>['rsdscs', 'rldscs', 'zg250', 'rsds', 'rsut', 'zg1000', 'huss', 'zg925', 'hurs', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'zg600', 'rlutcs', 'sfcWind']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -454,7 +454,7 @@
     <t>['pr', 'tas']</t>
   </si>
   <si>
-    <t>['rsdscs', 'rldscs', 'zg250', 'rsds', 'rsut', 'zg1000', 'huss', 'zg925', 'hurs', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'zg600', 'rlutcs', 'sfcWind']</t>
+    <t>['rsdscs', 'rldscs', 'zg250', 'rsds', 'rsut', 'zg1000', 'huss', 'zg925', 'hurs', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'zg600', 'rlutcs', 'sfcWind', 'zg300', 'zg400', 'uas', 'tasmax', 'tas', 'zg700', 'rlds', 'zg750', 'psl', 'mrro', 'clt', 'zg850', 'zg200', 'tasmin', 'sfcWindmax', 'zg500', 'mrso', 'mrros', 'rlut', 'snc', 'pr', 'vas', 'snw']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
@@ -957,7 +957,7 @@
     <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="303.7109375" customWidth="1"/>
+    <col min="13" max="13" width="341.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="181">
   <si>
     <t>variable_id</t>
   </si>
@@ -61,9 +61,6 @@
     <t>CORDEX-CMIP6</t>
   </si>
   <si>
-    <t>sim_data</t>
-  </si>
-  <si>
     <t>CMIP5</t>
   </si>
   <si>
@@ -130,6 +127,9 @@
     <t>CNRM-MF</t>
   </si>
   <si>
+    <t>HCLIMcom-DMI</t>
+  </si>
+  <si>
     <t>HCLIMcom-METNo</t>
   </si>
   <si>
@@ -151,6 +151,9 @@
     <t>CNRM-ESM2-1</t>
   </si>
   <si>
+    <t>IPSL-CM6A-LR</t>
+  </si>
+  <si>
     <t>NorESM2-MM</t>
   </si>
   <si>
@@ -166,9 +169,6 @@
     <t>EC-Earth3</t>
   </si>
   <si>
-    <t>HCLIMcom-DMI</t>
-  </si>
-  <si>
     <t>evaluation</t>
   </si>
   <si>
@@ -190,9 +190,6 @@
     <t>ssp119</t>
   </si>
   <si>
-    <t>IPSL-CM6A-LR</t>
-  </si>
-  <si>
     <t>r0i0p0</t>
   </si>
   <si>
@@ -385,6 +382,9 @@
     <t>v20250515</t>
   </si>
   <si>
+    <t>v20250516</t>
+  </si>
+  <si>
     <t>v20241205</t>
   </si>
   <si>
@@ -400,42 +400,6 @@
     <t>v20241009</t>
   </si>
   <si>
-    <t>clt</t>
-  </si>
-  <si>
-    <t>evspsbl</t>
-  </si>
-  <si>
-    <t>huss</t>
-  </si>
-  <si>
-    <t>pr</t>
-  </si>
-  <si>
-    <t>psl</t>
-  </si>
-  <si>
-    <t>rlds</t>
-  </si>
-  <si>
-    <t>rsds</t>
-  </si>
-  <si>
-    <t>tas</t>
-  </si>
-  <si>
-    <t>tasmax</t>
-  </si>
-  <si>
-    <t>tasmin</t>
-  </si>
-  <si>
-    <t>uas</t>
-  </si>
-  <si>
-    <t>vas</t>
-  </si>
-  <si>
     <t>['orog', 'sftlf']</t>
   </si>
   <si>
@@ -457,6 +421,12 @@
     <t>['rsdscs', 'rldscs', 'zg250', 'rsds', 'rsut', 'zg1000', 'huss', 'zg925', 'hurs', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'zg600', 'rlutcs', 'sfcWind', 'zg300', 'zg400', 'uas', 'tasmax', 'tas', 'zg700', 'rlds', 'zg750', 'psl', 'mrro', 'clt', 'zg850', 'zg200', 'tasmin', 'sfcWindmax', 'zg500', 'mrso', 'mrros', 'rlut', 'snc', 'pr', 'vas', 'snw']</t>
   </si>
   <si>
+    <t>['sfturf', 'sftlf', 'sftlaf', 'orog', 'areacella']</t>
+  </si>
+  <si>
+    <t>['od550aer', 'rsdscs', 'rldscs', 'rsds', 'rsut', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'rlutcs', 'sfcWind', 'uas', 'tasmax', 'tas', 'rlds', 'psl', 'mrro', 'clt']</t>
+  </si>
+  <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
   </si>
   <si>
@@ -532,6 +502,9 @@
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
   </si>
   <si>
+    <t>['tasmin', 'tasmax', 'tas', 'pr', 'rsds', 'uas', 'vas', 'rlds', 'evspsbl', 'huss', 'psl', 'clt']</t>
+  </si>
+  <si>
     <t>['clt', 'evspsbl', 'huss', 'pr', 'psl', 'rlds', 'rsds', 'tas', 'tasmax', 'tasmin', 'uas', 'vas', 'zg500']</t>
   </si>
   <si>
@@ -584,9 +557,6 @@
   </si>
   <si>
     <t>['pr', 'psl', 'tas', 'tasmax', 'tasmin', 'rsds', 'rlds', 'evspsbl', 'uas', 'vas', 'sfcWind', 'clt']</t>
-  </si>
-  <si>
-    <t>['day']</t>
   </si>
 </sst>
 </file>
@@ -944,12 +914,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M205"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
@@ -1006,16 +976,16 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>42</v>
@@ -1024,22 +994,22 @@
         <v>51</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1051,22 +1021,22 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1075,7 +1045,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>42</v>
@@ -1084,22 +1054,22 @@
         <v>51</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1111,22 +1081,22 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M5" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1135,7 +1105,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>42</v>
@@ -1144,22 +1114,22 @@
         <v>51</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1174,13 +1144,13 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M7" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1193,19 +1163,19 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1220,13 +1190,13 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1235,7 +1205,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>42</v>
@@ -1244,22 +1214,22 @@
         <v>51</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M10" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1274,13 +1244,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M11" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1289,7 +1259,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>42</v>
@@ -1298,22 +1268,22 @@
         <v>51</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M12" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1325,22 +1295,22 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M13" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1349,7 +1319,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>42</v>
@@ -1358,22 +1328,22 @@
         <v>51</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M14" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1382,7 +1352,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>42</v>
@@ -1391,22 +1361,22 @@
         <v>51</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M15" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1421,13 +1391,13 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M16" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1443,10 +1413,10 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1455,7 +1425,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>42</v>
@@ -1464,22 +1434,22 @@
         <v>51</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M18" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1494,13 +1464,13 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M19" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1509,7 +1479,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>42</v>
@@ -1518,22 +1488,22 @@
         <v>51</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M20" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1545,22 +1515,22 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M21" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1569,7 +1539,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>42</v>
@@ -1578,22 +1548,22 @@
         <v>51</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M22" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1608,13 +1578,13 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M23" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1623,7 +1593,7 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>42</v>
@@ -1632,22 +1602,22 @@
         <v>51</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M24" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1659,22 +1629,22 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M25" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1682,16 +1652,16 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>43</v>
@@ -1700,22 +1670,22 @@
         <v>51</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M26" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1723,32 +1693,20 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M27" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1763,13 +1721,13 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M28" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1777,20 +1735,32 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K29" s="1" t="s">
         <v>95</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M29" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1805,13 +1775,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M30" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1829,10 +1799,10 @@
         <v>94</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M31" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1840,32 +1810,20 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M32" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1880,13 +1838,13 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M33" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1894,20 +1852,32 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K34" s="1" t="s">
         <v>95</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M34" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1922,13 +1892,13 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M35" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1940,20 +1910,16 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M36" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1968,13 +1934,13 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1986,16 +1952,20 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K38" s="1" t="s">
         <v>95</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M38" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2010,13 +1980,13 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M39" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2034,10 +2004,10 @@
         <v>94</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M40" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2045,32 +2015,20 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M41" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2088,10 +2046,10 @@
         <v>93</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M42" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2099,20 +2057,32 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K43" s="1" t="s">
         <v>94</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M43" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2120,32 +2090,20 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M44" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2163,10 +2121,10 @@
         <v>93</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M45" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2174,28 +2132,32 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M46" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2210,13 +2172,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M47" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2225,29 +2187,27 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>61</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M48" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2262,13 +2222,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M49" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2277,19 +2237,29 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K50" s="1" t="s">
         <v>95</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M50" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2304,13 +2274,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M51" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2328,10 +2298,10 @@
         <v>94</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M52" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2339,32 +2309,20 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M53" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2379,13 +2337,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M54" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2393,20 +2351,32 @@
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="E55" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K55" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M55" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -2424,10 +2394,10 @@
         <v>94</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M56" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -2439,20 +2409,16 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M57" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2467,13 +2433,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M58" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2485,16 +2451,20 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="I59" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K59" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M59" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -2512,10 +2482,10 @@
         <v>94</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M60" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -2527,20 +2497,16 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -2555,13 +2521,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M62" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -2573,16 +2539,20 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="I63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K63" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M63" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -2600,10 +2570,10 @@
         <v>94</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M64" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -2615,20 +2585,16 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M65" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2643,13 +2609,13 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M66" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -2661,16 +2627,20 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="I67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K67" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M67" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -2688,10 +2658,10 @@
         <v>94</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M68" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2699,32 +2669,20 @@
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M69" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2742,10 +2700,10 @@
         <v>93</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M70" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2753,20 +2711,32 @@
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="E71" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K71" s="1" t="s">
         <v>94</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M71" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2780,22 +2750,22 @@
         <v>54</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M72" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2809,22 +2779,22 @@
         <v>53</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M73" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2832,20 +2802,32 @@
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="E74" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K74" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M74" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2860,13 +2842,13 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M75" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -2874,32 +2856,20 @@
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
       <c r="K76" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M76" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2909,18 +2879,26 @@
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="G77" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K77" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M77" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -2930,10 +2908,18 @@
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="G78" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K78" s="1" t="s">
         <v>94</v>
       </c>
@@ -2941,7 +2927,7 @@
         <v>123</v>
       </c>
       <c r="M78" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2951,26 +2937,18 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M79" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -2980,26 +2958,18 @@
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M80" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -3007,20 +2977,32 @@
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="E81" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K81" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M81" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -3035,13 +3017,13 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M82" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -3050,29 +3032,19 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M83" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -3082,18 +3054,26 @@
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="G84" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K84" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M84" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -3103,10 +3083,18 @@
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="G85" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K85" s="1" t="s">
         <v>94</v>
       </c>
@@ -3114,7 +3102,7 @@
         <v>123</v>
       </c>
       <c r="M85" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3125,23 +3113,17 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
-      <c r="H86" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M86" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -3162,7 +3144,7 @@
         <v>123</v>
       </c>
       <c r="M87" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3171,11 +3153,21 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K88" s="1" t="s">
         <v>94</v>
       </c>
@@ -3183,7 +3175,7 @@
         <v>123</v>
       </c>
       <c r="M88" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3194,23 +3186,17 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-      <c r="H89" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
       <c r="K89" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M89" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -3231,7 +3217,7 @@
         <v>123</v>
       </c>
       <c r="M90" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3242,9 +3228,15 @@
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+      <c r="H91" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K91" s="1" t="s">
         <v>94</v>
       </c>
@@ -3252,7 +3244,7 @@
         <v>123</v>
       </c>
       <c r="M91" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3262,26 +3254,18 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
       <c r="K92" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M92" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -3292,15 +3276,9 @@
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
-      <c r="H93" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
       <c r="K93" s="1" t="s">
         <v>93</v>
       </c>
@@ -3308,7 +3286,7 @@
         <v>123</v>
       </c>
       <c r="M93" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3320,22 +3298,22 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M94" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3345,26 +3323,18 @@
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="G95" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
       <c r="K95" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M95" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -3385,7 +3355,7 @@
         <v>123</v>
       </c>
       <c r="M96" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3395,18 +3365,26 @@
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
+      <c r="G97" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K97" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M97" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -3418,22 +3396,22 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M98" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -3444,17 +3422,23 @@
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
+      <c r="H99" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K99" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M99" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -3464,10 +3448,18 @@
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
+      <c r="G100" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K100" s="1" t="s">
         <v>94</v>
       </c>
@@ -3475,7 +3467,7 @@
         <v>123</v>
       </c>
       <c r="M100" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3486,23 +3478,17 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
-      <c r="H101" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
       <c r="K101" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M101" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -3523,7 +3509,7 @@
         <v>123</v>
       </c>
       <c r="M102" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3534,9 +3520,15 @@
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+      <c r="H103" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K103" s="1" t="s">
         <v>94</v>
       </c>
@@ -3544,7 +3536,7 @@
         <v>123</v>
       </c>
       <c r="M103" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3553,29 +3545,19 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M104" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -3590,13 +3572,13 @@
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M105" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3607,17 +3589,23 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
+      <c r="H106" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K106" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M106" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3632,13 +3620,13 @@
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M107" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -3647,29 +3635,19 @@
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
       <c r="K108" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M108" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3678,19 +3656,29 @@
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
+      <c r="F109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K109" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M109" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3711,7 +3699,7 @@
         <v>123</v>
       </c>
       <c r="M110" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3721,20 +3709,12 @@
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
-      <c r="G111" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
       <c r="K111" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>123</v>
@@ -3750,26 +3730,18 @@
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
-      <c r="G112" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
       <c r="K112" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M112" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3778,19 +3750,29 @@
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
+      <c r="F113" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K113" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M113" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3805,13 +3787,13 @@
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M114" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -3820,29 +3802,19 @@
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
       <c r="K115" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M115" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3852,18 +3824,26 @@
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
+      <c r="G116" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K116" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M116" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -3873,10 +3853,18 @@
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
+      <c r="G117" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K117" s="1" t="s">
         <v>94</v>
       </c>
@@ -3884,7 +3872,7 @@
         <v>123</v>
       </c>
       <c r="M117" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3894,26 +3882,18 @@
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
       <c r="K118" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M118" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -3923,26 +3903,18 @@
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
       <c r="K119" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L119" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M119" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3951,19 +3923,29 @@
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
+      <c r="F120" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K120" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M120" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3978,13 +3960,13 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>123</v>
       </c>
       <c r="M121" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -3992,32 +3974,20 @@
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
-      <c r="E122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
       <c r="K122" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M122" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -4027,18 +3997,26 @@
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
+      <c r="G123" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K123" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M123" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -4048,18 +4026,26 @@
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
+      <c r="G124" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K124" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M124" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4074,13 +4060,13 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M125" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -4095,13 +4081,13 @@
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M126" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4110,7 +4096,7 @@
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>43</v>
@@ -4119,22 +4105,22 @@
         <v>51</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J127" s="1" t="s">
         <v>91</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M127" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4149,13 +4135,13 @@
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M128" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4170,13 +4156,13 @@
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M129" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4184,32 +4170,20 @@
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
-      <c r="E130" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
       <c r="K130" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M130" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4227,10 +4201,10 @@
         <v>93</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M131" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4238,25 +4212,29 @@
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
+      <c r="E132" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G132" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>95</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M132" t="s">
         <v>172</v>
@@ -4274,13 +4252,13 @@
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
       <c r="K133" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M133" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4290,26 +4268,18 @@
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
       <c r="K134" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M134" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4317,20 +4287,32 @@
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1"/>
+      <c r="E135" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K135" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L135" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M135" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4339,29 +4321,19 @@
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J136" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
       <c r="K136" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M136" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4371,18 +4343,26 @@
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
+      <c r="G137" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K137" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M137" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4392,26 +4372,18 @@
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
       <c r="K138" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M138" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4421,18 +4393,26 @@
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
+      <c r="G139" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K139" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M139" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4442,26 +4422,18 @@
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
       <c r="K140" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M140" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4470,27 +4442,29 @@
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
+      <c r="F141" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="G141" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M141" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4505,13 +4479,13 @@
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
       <c r="K142" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M142" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4522,25 +4496,25 @@
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L143" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M143" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4549,29 +4523,19 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
       <c r="K144" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M144" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4581,18 +4545,26 @@
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
-      <c r="H145" s="1"/>
-      <c r="I145" s="1"/>
-      <c r="J145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K145" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M145" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4603,25 +4575,25 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L146" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M146" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -4631,26 +4603,18 @@
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
-      <c r="G147" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J147" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
       <c r="K147" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L147" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M147" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -4660,18 +4624,26 @@
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
-      <c r="H148" s="1"/>
-      <c r="I148" s="1"/>
-      <c r="J148" s="1"/>
+      <c r="G148" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K148" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L148" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M148" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -4680,27 +4652,29 @@
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="1"/>
+      <c r="F149" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G149" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L149" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M149" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -4710,26 +4684,18 @@
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
-      <c r="G150" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
       <c r="K150" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L150" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M150" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -4739,18 +4705,26 @@
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="1"/>
+      <c r="G151" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K151" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L151" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M151" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -4761,25 +4735,25 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L152" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M152" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -4788,29 +4762,19 @@
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
       <c r="K153" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L153" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M153" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -4820,18 +4784,26 @@
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
-      <c r="G154" s="1"/>
-      <c r="H154" s="1"/>
-      <c r="I154" s="1"/>
-      <c r="J154" s="1"/>
+      <c r="G154" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K154" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M154" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -4841,10 +4813,18 @@
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
-      <c r="H155" s="1"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="1"/>
+      <c r="G155" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K155" s="1" t="s">
         <v>94</v>
       </c>
@@ -4852,7 +4832,7 @@
         <v>126</v>
       </c>
       <c r="M155" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -4861,29 +4841,19 @@
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
-      <c r="F156" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+      <c r="J156" s="1"/>
       <c r="K156" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L156" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M156" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -4893,18 +4863,26 @@
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="1"/>
-      <c r="H157" s="1"/>
-      <c r="I157" s="1"/>
-      <c r="J157" s="1"/>
+      <c r="G157" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J157" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K157" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L157" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M157" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -4913,27 +4891,29 @@
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
-      <c r="F158" s="1"/>
+      <c r="F158" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G158" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M158" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -4948,13 +4928,13 @@
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
       <c r="K159" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M159" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -4964,26 +4944,18 @@
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
-      <c r="G160" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
       <c r="K160" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L160" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M160" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -4992,19 +4964,29 @@
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
-      <c r="F161" s="1"/>
-      <c r="G161" s="1"/>
-      <c r="H161" s="1"/>
-      <c r="I161" s="1"/>
-      <c r="J161" s="1"/>
+      <c r="F161" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K161" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M161" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -5013,29 +4995,19 @@
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
-      <c r="F162" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J162" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
       <c r="K162" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M162" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -5045,18 +5017,26 @@
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
-      <c r="G163" s="1"/>
-      <c r="H163" s="1"/>
-      <c r="I163" s="1"/>
-      <c r="J163" s="1"/>
+      <c r="G163" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K163" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L163" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M163" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -5066,26 +5046,18 @@
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
-      <c r="G164" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+      <c r="J164" s="1"/>
       <c r="K164" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L164" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M164" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -5095,18 +5067,26 @@
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
-      <c r="H165" s="1"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="1"/>
+      <c r="G165" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K165" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L165" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M165" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -5116,26 +5096,18 @@
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
-      <c r="G166" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+      <c r="J166" s="1"/>
       <c r="K166" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L166" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M166" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -5144,19 +5116,29 @@
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="1"/>
-      <c r="G167" s="1"/>
-      <c r="H167" s="1"/>
-      <c r="I167" s="1"/>
-      <c r="J167" s="1"/>
+      <c r="F167" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K167" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L167" s="1" t="s">
         <v>126</v>
       </c>
       <c r="M167" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -5164,32 +5146,20 @@
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
-      <c r="E168" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H168" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I168" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+      <c r="J168" s="1"/>
       <c r="K168" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M168" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -5199,18 +5169,26 @@
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
-      <c r="H169" s="1"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="1"/>
+      <c r="G169" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K169" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M169" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -5225,13 +5203,13 @@
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
       <c r="K170" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M170" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -5241,59 +5219,47 @@
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
-      <c r="G171" s="1"/>
-      <c r="H171" s="1"/>
-      <c r="I171" s="1"/>
-      <c r="J171" s="1"/>
+      <c r="G171" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="K171" s="1" t="s">
         <v>94</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M171" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="172" spans="1:13">
-      <c r="A172" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H172" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I172" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="A172" s="1"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+      <c r="G172" s="1"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+      <c r="J172" s="1"/>
       <c r="K172" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M172" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -5301,18 +5267,32 @@
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
-      <c r="E173" s="1"/>
-      <c r="F173" s="1"/>
-      <c r="G173" s="1"/>
-      <c r="H173" s="1"/>
-      <c r="I173" s="1"/>
-      <c r="J173" s="1"/>
-      <c r="K173" s="1"/>
+      <c r="E173" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K173" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="L173" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M173" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -5326,12 +5306,14 @@
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
+      <c r="K174" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="L174" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M174" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -5345,12 +5327,14 @@
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
-      <c r="K175" s="1"/>
+      <c r="K175" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="L175" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M175" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -5364,595 +5348,26 @@
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
+      <c r="K176" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="L176" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="M176" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" s="1"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
-      <c r="E177" s="1"/>
-      <c r="F177" s="1"/>
-      <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
-      <c r="I177" s="1"/>
-      <c r="J177" s="1"/>
-      <c r="K177" s="1"/>
-      <c r="L177" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M177" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13">
-      <c r="A178" s="1"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
-      <c r="L178" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M178" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13">
-      <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
-      <c r="I179" s="1"/>
-      <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
-      <c r="L179" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M179" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13">
-      <c r="A180" s="1"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-      <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
-      <c r="G180" s="1"/>
-      <c r="H180" s="1"/>
-      <c r="I180" s="1"/>
-      <c r="J180" s="1"/>
-      <c r="K180" s="1"/>
-      <c r="L180" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="M180" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13">
-      <c r="A181" s="1"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
-      <c r="E181" s="1"/>
-      <c r="F181" s="1"/>
-      <c r="G181" s="1"/>
-      <c r="H181" s="1"/>
-      <c r="I181" s="1"/>
-      <c r="J181" s="1"/>
-      <c r="K181" s="1"/>
-      <c r="L181" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M181" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13">
-      <c r="A182" s="1"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
-      <c r="E182" s="1"/>
-      <c r="F182" s="1"/>
-      <c r="G182" s="1"/>
-      <c r="H182" s="1"/>
-      <c r="I182" s="1"/>
-      <c r="J182" s="1"/>
-      <c r="K182" s="1"/>
-      <c r="L182" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M182" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13">
-      <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
-      <c r="E183" s="1"/>
-      <c r="F183" s="1"/>
-      <c r="G183" s="1"/>
-      <c r="H183" s="1"/>
-      <c r="I183" s="1"/>
-      <c r="J183" s="1"/>
-      <c r="K183" s="1"/>
-      <c r="L183" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M183" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13">
-      <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
-      <c r="E184" s="1"/>
-      <c r="F184" s="1"/>
-      <c r="G184" s="1"/>
-      <c r="H184" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I184" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K184" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L184" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="M184" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13">
-      <c r="A185" s="1"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
-      <c r="F185" s="1"/>
-      <c r="G185" s="1"/>
-      <c r="H185" s="1"/>
-      <c r="I185" s="1"/>
-      <c r="J185" s="1"/>
-      <c r="K185" s="1"/>
-      <c r="L185" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M185" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13">
-      <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
-      <c r="H186" s="1"/>
-      <c r="I186" s="1"/>
-      <c r="J186" s="1"/>
-      <c r="K186" s="1"/>
-      <c r="L186" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="M186" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13">
-      <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
-      <c r="E187" s="1"/>
-      <c r="F187" s="1"/>
-      <c r="G187" s="1"/>
-      <c r="H187" s="1"/>
-      <c r="I187" s="1"/>
-      <c r="J187" s="1"/>
-      <c r="K187" s="1"/>
-      <c r="L187" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M187" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13">
-      <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
-      <c r="E188" s="1"/>
-      <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
-      <c r="H188" s="1"/>
-      <c r="I188" s="1"/>
-      <c r="J188" s="1"/>
-      <c r="K188" s="1"/>
-      <c r="L188" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M188" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13">
-      <c r="A189" s="1"/>
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
-      <c r="E189" s="1"/>
-      <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
-      <c r="H189" s="1"/>
-      <c r="I189" s="1"/>
-      <c r="J189" s="1"/>
-      <c r="K189" s="1"/>
-      <c r="L189" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M189" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="1"/>
-      <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
-      <c r="H190" s="1"/>
-      <c r="I190" s="1"/>
-      <c r="J190" s="1"/>
-      <c r="K190" s="1"/>
-      <c r="L190" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="M190" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13">
-      <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="1"/>
-      <c r="I191" s="1"/>
-      <c r="J191" s="1"/>
-      <c r="K191" s="1"/>
-      <c r="L191" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M191" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
-      <c r="I192" s="1"/>
-      <c r="J192" s="1"/>
-      <c r="K192" s="1"/>
-      <c r="L192" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M192" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13">
-      <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
-      <c r="E193" s="1"/>
-      <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
-      <c r="H193" s="1"/>
-      <c r="I193" s="1"/>
-      <c r="J193" s="1"/>
-      <c r="K193" s="1"/>
-      <c r="L193" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M193" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13">
-      <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J194" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K194" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L194" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="M194" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13">
-      <c r="A195" s="1"/>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
-      <c r="E195" s="1"/>
-      <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
-      <c r="H195" s="1"/>
-      <c r="I195" s="1"/>
-      <c r="J195" s="1"/>
-      <c r="K195" s="1"/>
-      <c r="L195" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="M195" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13">
-      <c r="A196" s="1"/>
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
-      <c r="E196" s="1"/>
-      <c r="F196" s="1"/>
-      <c r="G196" s="1"/>
-      <c r="H196" s="1"/>
-      <c r="I196" s="1"/>
-      <c r="J196" s="1"/>
-      <c r="K196" s="1"/>
-      <c r="L196" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M196" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13">
-      <c r="A197" s="1"/>
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
-      <c r="E197" s="1"/>
-      <c r="F197" s="1"/>
-      <c r="G197" s="1"/>
-      <c r="H197" s="1"/>
-      <c r="I197" s="1"/>
-      <c r="J197" s="1"/>
-      <c r="K197" s="1"/>
-      <c r="L197" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="M197" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13">
-      <c r="A198" s="1"/>
-      <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
-      <c r="E198" s="1"/>
-      <c r="F198" s="1"/>
-      <c r="G198" s="1"/>
-      <c r="H198" s="1"/>
-      <c r="I198" s="1"/>
-      <c r="J198" s="1"/>
-      <c r="K198" s="1"/>
-      <c r="L198" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="M198" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13">
-      <c r="A199" s="1"/>
-      <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
-      <c r="E199" s="1"/>
-      <c r="F199" s="1"/>
-      <c r="G199" s="1"/>
-      <c r="H199" s="1"/>
-      <c r="I199" s="1"/>
-      <c r="J199" s="1"/>
-      <c r="K199" s="1"/>
-      <c r="L199" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M199" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13">
-      <c r="A200" s="1"/>
-      <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
-      <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
-      <c r="H200" s="1"/>
-      <c r="I200" s="1"/>
-      <c r="J200" s="1"/>
-      <c r="K200" s="1"/>
-      <c r="L200" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M200" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13">
-      <c r="A201" s="1"/>
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
-      <c r="E201" s="1"/>
-      <c r="F201" s="1"/>
-      <c r="G201" s="1"/>
-      <c r="H201" s="1"/>
-      <c r="I201" s="1"/>
-      <c r="J201" s="1"/>
-      <c r="K201" s="1"/>
-      <c r="L201" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M201" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13">
-      <c r="A202" s="1"/>
-      <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
-      <c r="E202" s="1"/>
-      <c r="F202" s="1"/>
-      <c r="G202" s="1"/>
-      <c r="H202" s="1"/>
-      <c r="I202" s="1"/>
-      <c r="J202" s="1"/>
-      <c r="K202" s="1"/>
-      <c r="L202" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="M202" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="203" spans="1:13">
-      <c r="A203" s="1"/>
-      <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
-      <c r="F203" s="1"/>
-      <c r="G203" s="1"/>
-      <c r="H203" s="1"/>
-      <c r="I203" s="1"/>
-      <c r="J203" s="1"/>
-      <c r="K203" s="1"/>
-      <c r="L203" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M203" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13">
-      <c r="A204" s="1"/>
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
-      <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
-      <c r="G204" s="1"/>
-      <c r="H204" s="1"/>
-      <c r="I204" s="1"/>
-      <c r="J204" s="1"/>
-      <c r="K204" s="1"/>
-      <c r="L204" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M204" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13">
-      <c r="A205" s="1"/>
-      <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
-      <c r="E205" s="1"/>
-      <c r="F205" s="1"/>
-      <c r="G205" s="1"/>
-      <c r="H205" s="1"/>
-      <c r="I205" s="1"/>
-      <c r="J205" s="1"/>
-      <c r="K205" s="1"/>
-      <c r="L205" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M205" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="276">
+  <mergeCells count="265">
     <mergeCell ref="A2:A25"/>
-    <mergeCell ref="A26:A171"/>
-    <mergeCell ref="A172:A205"/>
+    <mergeCell ref="A26:A176"/>
     <mergeCell ref="B2:B25"/>
-    <mergeCell ref="B26:B171"/>
-    <mergeCell ref="B172:B205"/>
+    <mergeCell ref="B26:B176"/>
     <mergeCell ref="C2:C25"/>
-    <mergeCell ref="C26:C171"/>
-    <mergeCell ref="C172:C205"/>
+    <mergeCell ref="C26:C176"/>
     <mergeCell ref="D2:D25"/>
-    <mergeCell ref="D26:D171"/>
-    <mergeCell ref="D172:D205"/>
+    <mergeCell ref="D26:D176"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E6:E9"/>
@@ -5963,18 +5378,19 @@
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="E32:E40"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="E44:E52"/>
-    <mergeCell ref="E53:E68"/>
-    <mergeCell ref="E69:E75"/>
-    <mergeCell ref="E76:E121"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="E127:E129"/>
-    <mergeCell ref="E130:E167"/>
-    <mergeCell ref="E168:E171"/>
-    <mergeCell ref="E172:E205"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="E34:E42"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="E46:E54"/>
+    <mergeCell ref="E55:E70"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="E74:E80"/>
+    <mergeCell ref="E81:E126"/>
+    <mergeCell ref="E127:E131"/>
+    <mergeCell ref="E132:E134"/>
+    <mergeCell ref="E135:E172"/>
+    <mergeCell ref="E173:E176"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F6:F9"/>
@@ -5985,28 +5401,29 @@
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="F32:F40"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="F44:F47"/>
-    <mergeCell ref="F48:F52"/>
-    <mergeCell ref="F53:F68"/>
-    <mergeCell ref="F69:F75"/>
-    <mergeCell ref="F76:F82"/>
-    <mergeCell ref="F83:F103"/>
-    <mergeCell ref="F104:F107"/>
-    <mergeCell ref="F108:F114"/>
-    <mergeCell ref="F115:F121"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="F127:F129"/>
-    <mergeCell ref="F130:F135"/>
-    <mergeCell ref="F136:F143"/>
-    <mergeCell ref="F144:F152"/>
-    <mergeCell ref="F153:F155"/>
-    <mergeCell ref="F156:F161"/>
-    <mergeCell ref="F162:F167"/>
-    <mergeCell ref="F168:F171"/>
-    <mergeCell ref="F172:F205"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="F34:F42"/>
+    <mergeCell ref="F43:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="F55:F70"/>
+    <mergeCell ref="F71:F73"/>
+    <mergeCell ref="F74:F80"/>
+    <mergeCell ref="F81:F87"/>
+    <mergeCell ref="F88:F108"/>
+    <mergeCell ref="F109:F112"/>
+    <mergeCell ref="F113:F119"/>
+    <mergeCell ref="F120:F126"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="F132:F134"/>
+    <mergeCell ref="F135:F140"/>
+    <mergeCell ref="F141:F148"/>
+    <mergeCell ref="F149:F157"/>
+    <mergeCell ref="F158:F160"/>
+    <mergeCell ref="F161:F166"/>
+    <mergeCell ref="F167:F172"/>
+    <mergeCell ref="F173:F176"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G9"/>
@@ -6017,206 +5434,197 @@
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="G32:G40"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="G34:G42"/>
+    <mergeCell ref="G43:G45"/>
     <mergeCell ref="G46:G47"/>
-    <mergeCell ref="G48:G52"/>
-    <mergeCell ref="G53:G68"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="G73:G75"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="G83:G91"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="G95:G103"/>
-    <mergeCell ref="G104:G107"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="G112:G114"/>
-    <mergeCell ref="G115:G117"/>
-    <mergeCell ref="G119:G121"/>
-    <mergeCell ref="G122:G126"/>
-    <mergeCell ref="G127:G129"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="G55:G70"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="G81:G83"/>
+    <mergeCell ref="G85:G87"/>
+    <mergeCell ref="G88:G96"/>
+    <mergeCell ref="G97:G99"/>
+    <mergeCell ref="G100:G108"/>
+    <mergeCell ref="G109:G112"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="G117:G119"/>
+    <mergeCell ref="G120:G122"/>
+    <mergeCell ref="G124:G126"/>
+    <mergeCell ref="G127:G131"/>
+    <mergeCell ref="G132:G134"/>
+    <mergeCell ref="G135:G136"/>
+    <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G139:G140"/>
     <mergeCell ref="G141:G142"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="G153:G155"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="G158:G159"/>
-    <mergeCell ref="G160:G161"/>
-    <mergeCell ref="G162:G163"/>
-    <mergeCell ref="G164:G165"/>
-    <mergeCell ref="G166:G167"/>
-    <mergeCell ref="G168:G171"/>
-    <mergeCell ref="G172:G205"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="G149:G150"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="G155:G156"/>
+    <mergeCell ref="G158:G160"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="G163:G164"/>
+    <mergeCell ref="G165:G166"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="G169:G170"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="G173:G176"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H27:H31"/>
-    <mergeCell ref="H32:H40"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="H34:H42"/>
+    <mergeCell ref="H43:H45"/>
     <mergeCell ref="H46:H47"/>
-    <mergeCell ref="H48:H52"/>
-    <mergeCell ref="H53:H68"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="H73:H75"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="H83:H85"/>
-    <mergeCell ref="H86:H88"/>
-    <mergeCell ref="H89:H91"/>
-    <mergeCell ref="H95:H97"/>
-    <mergeCell ref="H98:H100"/>
-    <mergeCell ref="H101:H103"/>
-    <mergeCell ref="H104:H107"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="H112:H114"/>
-    <mergeCell ref="H115:H117"/>
-    <mergeCell ref="H119:H121"/>
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="H127:H129"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="H132:H133"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="H136:H137"/>
-    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="H55:H70"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="H85:H87"/>
+    <mergeCell ref="H88:H90"/>
+    <mergeCell ref="H91:H93"/>
+    <mergeCell ref="H94:H96"/>
+    <mergeCell ref="H100:H102"/>
+    <mergeCell ref="H103:H105"/>
+    <mergeCell ref="H106:H108"/>
+    <mergeCell ref="H109:H112"/>
+    <mergeCell ref="H113:H115"/>
+    <mergeCell ref="H117:H119"/>
+    <mergeCell ref="H120:H122"/>
+    <mergeCell ref="H124:H126"/>
+    <mergeCell ref="H127:H131"/>
+    <mergeCell ref="H132:H134"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
     <mergeCell ref="H141:H142"/>
-    <mergeCell ref="H144:H145"/>
-    <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H150:H151"/>
-    <mergeCell ref="H153:H155"/>
-    <mergeCell ref="H156:H157"/>
-    <mergeCell ref="H158:H159"/>
-    <mergeCell ref="H160:H161"/>
-    <mergeCell ref="H162:H163"/>
-    <mergeCell ref="H164:H165"/>
-    <mergeCell ref="H166:H167"/>
-    <mergeCell ref="H168:H171"/>
-    <mergeCell ref="H172:H183"/>
-    <mergeCell ref="H184:H193"/>
-    <mergeCell ref="H194:H205"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H152:H153"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="H158:H160"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H165:H166"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="H169:H170"/>
+    <mergeCell ref="H171:H172"/>
+    <mergeCell ref="H173:H176"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="I15:I17"/>
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="I22:I23"/>
-    <mergeCell ref="I27:I31"/>
-    <mergeCell ref="I32:I35"/>
-    <mergeCell ref="I36:I40"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="I26:I28"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="I38:I42"/>
+    <mergeCell ref="I43:I45"/>
     <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I52"/>
-    <mergeCell ref="I53:I56"/>
-    <mergeCell ref="I57:I60"/>
-    <mergeCell ref="I61:I64"/>
-    <mergeCell ref="I65:I68"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="I73:I75"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="I80:I82"/>
-    <mergeCell ref="I83:I85"/>
-    <mergeCell ref="I86:I88"/>
-    <mergeCell ref="I89:I91"/>
-    <mergeCell ref="I95:I97"/>
-    <mergeCell ref="I98:I100"/>
-    <mergeCell ref="I101:I103"/>
-    <mergeCell ref="I104:I107"/>
-    <mergeCell ref="I108:I110"/>
-    <mergeCell ref="I112:I114"/>
-    <mergeCell ref="I115:I117"/>
-    <mergeCell ref="I119:I121"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="I127:I129"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="I132:I133"/>
-    <mergeCell ref="I134:I135"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="I55:I58"/>
+    <mergeCell ref="I59:I62"/>
+    <mergeCell ref="I63:I66"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="I85:I87"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="I91:I93"/>
+    <mergeCell ref="I94:I96"/>
+    <mergeCell ref="I100:I102"/>
+    <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="I109:I112"/>
+    <mergeCell ref="I113:I115"/>
+    <mergeCell ref="I117:I119"/>
+    <mergeCell ref="I120:I122"/>
+    <mergeCell ref="I124:I126"/>
+    <mergeCell ref="I127:I131"/>
+    <mergeCell ref="I132:I134"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I139:I140"/>
     <mergeCell ref="I141:I142"/>
-    <mergeCell ref="I144:I145"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="I153:I155"/>
-    <mergeCell ref="I156:I157"/>
-    <mergeCell ref="I158:I159"/>
-    <mergeCell ref="I160:I161"/>
-    <mergeCell ref="I162:I163"/>
-    <mergeCell ref="I164:I165"/>
-    <mergeCell ref="I166:I167"/>
-    <mergeCell ref="I168:I171"/>
-    <mergeCell ref="I172:I183"/>
-    <mergeCell ref="I184:I193"/>
-    <mergeCell ref="I194:I205"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I152:I153"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="I158:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="I165:I166"/>
+    <mergeCell ref="I167:I168"/>
+    <mergeCell ref="I169:I170"/>
+    <mergeCell ref="I171:I172"/>
+    <mergeCell ref="I173:I176"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="J27:J31"/>
-    <mergeCell ref="J32:J35"/>
-    <mergeCell ref="J36:J40"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="J38:J42"/>
+    <mergeCell ref="J43:J45"/>
     <mergeCell ref="J46:J47"/>
-    <mergeCell ref="J48:J52"/>
-    <mergeCell ref="J53:J56"/>
-    <mergeCell ref="J57:J60"/>
-    <mergeCell ref="J61:J64"/>
-    <mergeCell ref="J65:J68"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="J73:J75"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="J80:J82"/>
-    <mergeCell ref="J83:J85"/>
-    <mergeCell ref="J86:J88"/>
-    <mergeCell ref="J89:J91"/>
-    <mergeCell ref="J95:J97"/>
-    <mergeCell ref="J98:J100"/>
-    <mergeCell ref="J101:J103"/>
-    <mergeCell ref="J104:J107"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J112:J114"/>
-    <mergeCell ref="J115:J117"/>
-    <mergeCell ref="J119:J121"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="J127:J129"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="J132:J133"/>
-    <mergeCell ref="J134:J135"/>
-    <mergeCell ref="J136:J137"/>
-    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="J48:J49"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="J55:J58"/>
+    <mergeCell ref="J59:J62"/>
+    <mergeCell ref="J63:J66"/>
+    <mergeCell ref="J67:J70"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="J85:J87"/>
+    <mergeCell ref="J88:J90"/>
+    <mergeCell ref="J91:J93"/>
+    <mergeCell ref="J94:J96"/>
+    <mergeCell ref="J100:J102"/>
+    <mergeCell ref="J103:J105"/>
+    <mergeCell ref="J106:J108"/>
+    <mergeCell ref="J109:J112"/>
+    <mergeCell ref="J113:J115"/>
+    <mergeCell ref="J117:J119"/>
+    <mergeCell ref="J120:J122"/>
+    <mergeCell ref="J124:J126"/>
+    <mergeCell ref="J127:J131"/>
+    <mergeCell ref="J132:J134"/>
+    <mergeCell ref="J135:J136"/>
+    <mergeCell ref="J137:J138"/>
+    <mergeCell ref="J139:J140"/>
     <mergeCell ref="J141:J142"/>
-    <mergeCell ref="J144:J145"/>
-    <mergeCell ref="J147:J148"/>
-    <mergeCell ref="J150:J151"/>
-    <mergeCell ref="J153:J155"/>
-    <mergeCell ref="J156:J157"/>
-    <mergeCell ref="J158:J159"/>
-    <mergeCell ref="J160:J161"/>
-    <mergeCell ref="J162:J163"/>
-    <mergeCell ref="J164:J165"/>
-    <mergeCell ref="J166:J167"/>
-    <mergeCell ref="J168:J171"/>
-    <mergeCell ref="J172:J183"/>
-    <mergeCell ref="J184:J193"/>
-    <mergeCell ref="J194:J205"/>
+    <mergeCell ref="J143:J144"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="J149:J150"/>
+    <mergeCell ref="J152:J153"/>
+    <mergeCell ref="J155:J156"/>
+    <mergeCell ref="J158:J160"/>
+    <mergeCell ref="J161:J162"/>
+    <mergeCell ref="J163:J164"/>
+    <mergeCell ref="J165:J166"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="J169:J170"/>
+    <mergeCell ref="J171:J172"/>
+    <mergeCell ref="J173:J176"/>
     <mergeCell ref="K16:K17"/>
-    <mergeCell ref="K172:K183"/>
-    <mergeCell ref="K184:K193"/>
-    <mergeCell ref="K194:K205"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="182">
   <si>
     <t>variable_id</t>
   </si>
@@ -424,7 +424,7 @@
     <t>['sfturf', 'sftlf', 'sftlaf', 'orog', 'areacella']</t>
   </si>
   <si>
-    <t>['od550aer', 'rsdscs', 'rldscs', 'rsds', 'rsut', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'rlutcs', 'sfcWind', 'uas', 'tasmax', 'tas', 'rlds', 'psl', 'mrro', 'clt']</t>
+    <t>['od550aer', 'rsdscs', 'rldscs', 'rsds', 'rsut', 'snd', 'evspsbl', 'rsutcs', 'prsn', 'rlutcs', 'sfcWind', 'uas', 'tasmax', 'tas', 'rlds', 'psl', 'mrro', 'clt', 'tasmin', 'zg500', 'mrso', 'mrros', 'rlut', 'snc', 'pr', 'vas', 'snw']</t>
   </si>
   <si>
     <t>['hurs', 'pr', 'prw', 'sfcWind', 'tas']</t>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>['clt', 'evspsbl', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'uas', 'vas']</t>
+  </si>
+  <si>
+    <t>['orog', 'sftlf', 'sftlaf']</t>
   </si>
   <si>
     <t>['tasmin', 'tasmax', 'tas', 'pr', 'rsds', 'uas', 'vas', 'rlds', 'evspsbl', 'huss', 'psl', 'clt']</t>
@@ -2594,7 +2597,7 @@
         <v>121</v>
       </c>
       <c r="M65" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -2682,7 +2685,7 @@
         <v>121</v>
       </c>
       <c r="M69" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2736,7 +2739,7 @@
         <v>122</v>
       </c>
       <c r="M71" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -2765,7 +2768,7 @@
         <v>122</v>
       </c>
       <c r="M72" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2794,7 +2797,7 @@
         <v>122</v>
       </c>
       <c r="M73" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2827,7 +2830,7 @@
         <v>123</v>
       </c>
       <c r="M74" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -2869,7 +2872,7 @@
         <v>123</v>
       </c>
       <c r="M76" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -2927,7 +2930,7 @@
         <v>123</v>
       </c>
       <c r="M78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -2969,7 +2972,7 @@
         <v>123</v>
       </c>
       <c r="M80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -3002,7 +3005,7 @@
         <v>123</v>
       </c>
       <c r="M81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -3044,7 +3047,7 @@
         <v>123</v>
       </c>
       <c r="M83" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -3102,7 +3105,7 @@
         <v>123</v>
       </c>
       <c r="M85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -3144,7 +3147,7 @@
         <v>123</v>
       </c>
       <c r="M87" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -3175,7 +3178,7 @@
         <v>123</v>
       </c>
       <c r="M88" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -3217,7 +3220,7 @@
         <v>123</v>
       </c>
       <c r="M90" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -3244,7 +3247,7 @@
         <v>123</v>
       </c>
       <c r="M91" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -3286,7 +3289,7 @@
         <v>123</v>
       </c>
       <c r="M93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -3313,7 +3316,7 @@
         <v>123</v>
       </c>
       <c r="M94" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -3355,7 +3358,7 @@
         <v>123</v>
       </c>
       <c r="M96" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -3467,7 +3470,7 @@
         <v>123</v>
       </c>
       <c r="M100" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -3509,7 +3512,7 @@
         <v>123</v>
       </c>
       <c r="M102" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -3536,7 +3539,7 @@
         <v>123</v>
       </c>
       <c r="M103" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -3578,7 +3581,7 @@
         <v>123</v>
       </c>
       <c r="M105" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -3605,7 +3608,7 @@
         <v>123</v>
       </c>
       <c r="M106" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -3647,7 +3650,7 @@
         <v>123</v>
       </c>
       <c r="M108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -3678,7 +3681,7 @@
         <v>123</v>
       </c>
       <c r="M109" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -3699,7 +3702,7 @@
         <v>123</v>
       </c>
       <c r="M110" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -3741,7 +3744,7 @@
         <v>123</v>
       </c>
       <c r="M112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -3772,7 +3775,7 @@
         <v>123</v>
       </c>
       <c r="M113" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -3814,7 +3817,7 @@
         <v>123</v>
       </c>
       <c r="M115" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -3872,7 +3875,7 @@
         <v>123</v>
       </c>
       <c r="M117" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -3914,7 +3917,7 @@
         <v>123</v>
       </c>
       <c r="M119" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -3945,7 +3948,7 @@
         <v>123</v>
       </c>
       <c r="M120" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -3987,7 +3990,7 @@
         <v>123</v>
       </c>
       <c r="M122" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -4045,7 +4048,7 @@
         <v>123</v>
       </c>
       <c r="M124" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -4087,7 +4090,7 @@
         <v>123</v>
       </c>
       <c r="M126" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -4120,7 +4123,7 @@
         <v>124</v>
       </c>
       <c r="M127" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -4141,7 +4144,7 @@
         <v>124</v>
       </c>
       <c r="M128" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -4162,7 +4165,7 @@
         <v>124</v>
       </c>
       <c r="M129" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -4183,7 +4186,7 @@
         <v>124</v>
       </c>
       <c r="M130" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -4204,7 +4207,7 @@
         <v>124</v>
       </c>
       <c r="M131" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -4237,7 +4240,7 @@
         <v>125</v>
       </c>
       <c r="M132" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -4258,7 +4261,7 @@
         <v>125</v>
       </c>
       <c r="M133" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -4279,7 +4282,7 @@
         <v>125</v>
       </c>
       <c r="M134" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -4312,7 +4315,7 @@
         <v>126</v>
       </c>
       <c r="M135" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -4333,7 +4336,7 @@
         <v>126</v>
       </c>
       <c r="M136" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -4362,7 +4365,7 @@
         <v>126</v>
       </c>
       <c r="M137" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -4383,7 +4386,7 @@
         <v>126</v>
       </c>
       <c r="M138" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -4412,7 +4415,7 @@
         <v>126</v>
       </c>
       <c r="M139" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -4433,7 +4436,7 @@
         <v>126</v>
       </c>
       <c r="M140" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -4464,7 +4467,7 @@
         <v>126</v>
       </c>
       <c r="M141" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -4485,7 +4488,7 @@
         <v>126</v>
       </c>
       <c r="M142" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -4514,7 +4517,7 @@
         <v>126</v>
       </c>
       <c r="M143" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -4535,7 +4538,7 @@
         <v>126</v>
       </c>
       <c r="M144" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -4564,7 +4567,7 @@
         <v>126</v>
       </c>
       <c r="M145" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -4593,7 +4596,7 @@
         <v>126</v>
       </c>
       <c r="M146" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
  